--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -82,9 +82,7 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -463,9 +461,9 @@
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
     <col width="58" customWidth="1" min="10" max="10"/>
     <col width="70" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
@@ -510,12 +508,12 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>N.º variantes</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Disponible</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Etiquetas</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -564,17 +562,17 @@
       <c r="F2" s="3" t="n">
         <v>807143</v>
       </c>
-      <c r="G2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Beige', 'Negro']</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>baby shower, BEBES, mas vendidos, paseo y descanso, todos lo</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -621,15 +619,17 @@
       <c r="F3" s="3" t="n">
         <v>620000</v>
       </c>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Púrpura', 'Beige', 'Azul marino']</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>alimentación, baby shower, mas vendidos, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -676,15 +676,17 @@
       <c r="F4" s="3" t="n">
         <v>728571</v>
       </c>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Rosa', 'Azul', 'Beige', 'Negro']</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>baby shower, BEBES, mas vendidos, paseo y descanso, todos lo</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -731,15 +733,13 @@
       <c r="F5" s="3" t="n">
         <v>678571</v>
       </c>
-      <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>baby shower, BEBES, paseo y descanso, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -786,15 +786,13 @@
       <c r="F6" s="3" t="n">
         <v>635714</v>
       </c>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>baby shower, lactancia, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -841,15 +839,13 @@
       <c r="F7" s="3" t="n">
         <v>520000</v>
       </c>
-      <c r="G7" s="2" t="n"/>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>baby shower, BEBES, mas vendidos, paseo y descanso, todos lo</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -896,15 +892,17 @@
       <c r="F8" s="3" t="n">
         <v>568571</v>
       </c>
-      <c r="G8" s="2" t="n"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Gris', 'Rosa', 'Azul']</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>baby shower, BEBES, mas vendidos, paseo y descanso, todos lo</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -951,15 +949,13 @@
       <c r="F9" s="3" t="n">
         <v>457143</v>
       </c>
-      <c r="G9" s="2" t="n"/>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>paseo y descanso</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1004,15 +1000,17 @@
         <v>302000</v>
       </c>
       <c r="F10" s="3" t="n"/>
-      <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['azul', 'Rosa', 'Marrón']</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>alimentación, baby shower, BEBES, mas vendidos, todos los pr</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1059,15 +1057,13 @@
       <c r="F11" s="3" t="n">
         <v>301429</v>
       </c>
-      <c r="G11" s="2" t="n"/>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>alimentación, baby shower, mas vendidos, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1114,15 +1110,13 @@
       <c r="F12" s="3" t="n">
         <v>285714</v>
       </c>
-      <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>BEBES, juguetes, mas vendidos, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1169,15 +1163,13 @@
       <c r="F13" s="3" t="n">
         <v>274286</v>
       </c>
-      <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>baby shower, BEBES, mas vendidos, paseo y descanso, todos lo</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1224,15 +1216,13 @@
       <c r="F14" s="3" t="n">
         <v>221429</v>
       </c>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>baby shower, BEBES, juguetes, mas vendidos, todos los produc</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1279,15 +1269,13 @@
       <c r="F15" s="3" t="n">
         <v>221429</v>
       </c>
-      <c r="G15" s="2" t="n"/>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>baby shower, Teteros, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1334,15 +1322,17 @@
       <c r="F16" s="3" t="n">
         <v>217143</v>
       </c>
-      <c r="G16" s="2" t="n"/>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Beige', 'Azul', 'Rosa']</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>baby shower, BEBES, pañaleras, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1389,15 +1379,13 @@
       <c r="F17" s="3" t="n">
         <v>208000</v>
       </c>
-      <c r="G17" s="2" t="n"/>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>pañaleras, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1444,15 +1432,17 @@
       <c r="F18" s="3" t="n">
         <v>207143</v>
       </c>
-      <c r="G18" s="2" t="n"/>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Rosa', 'Negro', 'Marrón']</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>baby shower, pañaleras, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1499,15 +1489,13 @@
       <c r="F19" s="3" t="n">
         <v>207143</v>
       </c>
-      <c r="G19" s="2" t="n"/>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>baby shower, BEBES, juguetes, mas vendidos, todos los produc</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1554,15 +1542,17 @@
       <c r="F20" s="3" t="n">
         <v>197143</v>
       </c>
-      <c r="G20" s="2" t="n"/>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Talla: ['Recién nacido', '0-3 meses', '3-6 meses']</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>baby shower, BEBES, recién nacido, ropa, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1609,15 +1599,13 @@
       <c r="F21" s="3" t="n">
         <v>189286</v>
       </c>
-      <c r="G21" s="2" t="n"/>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>mas vendidos, paseo y descanso, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1664,15 +1652,13 @@
       <c r="F22" s="3" t="n">
         <v>161429</v>
       </c>
-      <c r="G22" s="2" t="n"/>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>BEBES, juguetes, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1719,15 +1705,17 @@
       <c r="F23" s="3" t="n">
         <v>161429</v>
       </c>
-      <c r="G23" s="2" t="n"/>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Rosa', 'azul', 'Blanco']</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>bacinillas, mas comprados, mas vendidos, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1774,15 +1762,13 @@
       <c r="F24" s="3" t="n">
         <v>160000</v>
       </c>
-      <c r="G24" s="2" t="n"/>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>baby shower, BEBES, mas vendidos, paseo y descanso, todos lo</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1829,15 +1815,13 @@
       <c r="F25" s="3" t="n">
         <v>150000</v>
       </c>
-      <c r="G25" s="2" t="n"/>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>baby shower, bacinillas, BEBES, mas comprados, mas vendidos,</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -1884,15 +1868,13 @@
       <c r="F26" s="3" t="n">
         <v>148571</v>
       </c>
-      <c r="G26" s="2" t="n"/>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>juguetes, mas vendidos, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -1939,15 +1921,13 @@
       <c r="F27" s="3" t="n">
         <v>142857</v>
       </c>
-      <c r="G27" s="2" t="n"/>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>BEBES, recién nacido, ropa, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -1994,15 +1974,13 @@
       <c r="F28" s="3" t="n">
         <v>137143</v>
       </c>
-      <c r="G28" s="2" t="n"/>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>recién nacido, ropa, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2049,15 +2027,13 @@
       <c r="F29" s="3" t="n">
         <v>135000</v>
       </c>
-      <c r="G29" s="2" t="n"/>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>BEBES, juguetes, mas vendidos, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2104,15 +2080,17 @@
       <c r="F30" s="3" t="n">
         <v>124000</v>
       </c>
-      <c r="G30" s="2" t="n"/>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Azul', 'Blanco', 'Rosa']</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>baby shower, lactancia, mas vendidos, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2157,15 +2135,17 @@
         <v>93400</v>
       </c>
       <c r="F31" s="3" t="n"/>
-      <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Rosa', 'azul']</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>accesorios, baby shower, BEBES, mas comprados, mas vendidos,</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2212,15 +2192,13 @@
       <c r="F32" s="3" t="n">
         <v>131429</v>
       </c>
-      <c r="G32" s="2" t="n"/>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>BEBES, juguetes, mas vendidos, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2267,15 +2245,13 @@
       <c r="F33" s="3" t="n">
         <v>130000</v>
       </c>
-      <c r="G33" s="2" t="n"/>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>baby shower, BEBES, mas vendidos, ropa, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2322,15 +2298,13 @@
       <c r="F34" s="3" t="n">
         <v>11000</v>
       </c>
-      <c r="G34" s="2" t="n"/>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>baby shower, mas vendidos, pañaleras, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2377,15 +2351,13 @@
       <c r="F35" s="3" t="n">
         <v>127000</v>
       </c>
-      <c r="G35" s="2" t="n"/>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>BEBES, Teteros, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2432,15 +2404,13 @@
       <c r="F36" s="3" t="n">
         <v>127143</v>
       </c>
-      <c r="G36" s="2" t="n"/>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>BEBES, juguetes, mas vendidos, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -2485,15 +2455,13 @@
         <v>88000</v>
       </c>
       <c r="F37" s="3" t="n"/>
-      <c r="G37" s="2" t="n"/>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>accesorios, baby shower, BEBES, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2540,15 +2508,13 @@
       <c r="F38" s="3" t="n">
         <v>122857</v>
       </c>
-      <c r="G38" s="2" t="n"/>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>baby shower, BEBES, cobijas y toallas, mas vendidos, todos l</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2595,15 +2561,17 @@
       <c r="F39" s="3" t="n">
         <v>121429</v>
       </c>
-      <c r="G39" s="2" t="n"/>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Rosado', 'Blanco', 'Verde']</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>baby shower, BEBES, lactancia, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -2650,15 +2618,13 @@
       <c r="F40" s="3" t="n">
         <v>117143</v>
       </c>
-      <c r="G40" s="2" t="n"/>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>baby shower, BEBES, ropa, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2705,15 +2671,13 @@
       <c r="F41" s="3" t="n">
         <v>115000</v>
       </c>
-      <c r="G41" s="2" t="n"/>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>baby shower, BEBES, mas vendidos, paseo y descanso, recién n</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -2760,15 +2724,13 @@
       <c r="F42" s="3" t="n">
         <v>114143</v>
       </c>
-      <c r="G42" s="2" t="n"/>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>juguetes, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -2815,15 +2777,13 @@
       <c r="F43" s="3" t="n">
         <v>111429</v>
       </c>
-      <c r="G43" s="2" t="n"/>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>baby shower, BEBES, juguetes, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -2870,15 +2830,13 @@
       <c r="F44" s="3" t="n">
         <v>111000</v>
       </c>
-      <c r="G44" s="2" t="n"/>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>BEBES, juguetes, mas vendidos, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -2925,15 +2883,13 @@
       <c r="F45" s="3" t="n">
         <v>102857</v>
       </c>
-      <c r="G45" s="2" t="n"/>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>BEBES, mas vendidos, pañaleras, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -2978,15 +2934,17 @@
         <v>71000</v>
       </c>
       <c r="F46" s="3" t="n"/>
-      <c r="G46" s="2" t="n"/>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Verde', 'Rosa', 'Beige']</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>lactancia, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -3033,15 +2991,13 @@
       <c r="F47" s="3" t="n">
         <v>100000</v>
       </c>
-      <c r="G47" s="2" t="n"/>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>baby shower, mas vendidos, pañaleras, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -3088,15 +3044,13 @@
       <c r="F48" s="3" t="n">
         <v>95714</v>
       </c>
-      <c r="G48" s="2" t="n"/>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>bacinillas, BEBES, mas vendidos, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -3143,15 +3097,13 @@
       <c r="F49" s="3" t="n">
         <v>92900</v>
       </c>
-      <c r="G49" s="2" t="n"/>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>mas vendidos, todos los productos, top-ventas</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -3198,15 +3150,17 @@
       <c r="F50" s="3" t="n">
         <v>92857</v>
       </c>
-      <c r="G50" s="2" t="n"/>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Azul', 'Rosa', 'Verde']</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>baby shower, mas vendidos, pañaleras, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -3253,15 +3207,17 @@
       <c r="F51" s="3" t="n">
         <v>79900</v>
       </c>
-      <c r="G51" s="2" t="n"/>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Azul', 'Rosa']</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>aseo, BEBES, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -3308,15 +3264,13 @@
       <c r="F52" s="3" t="n">
         <v>88571</v>
       </c>
-      <c r="G52" s="2" t="n"/>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>aseo, baby shower, mas vendidos, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -3363,15 +3317,13 @@
       <c r="F53" s="3" t="n">
         <v>85714</v>
       </c>
-      <c r="G53" s="2" t="n"/>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>baby shower, BEBES, ropa, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -3418,15 +3370,13 @@
       <c r="F54" s="3" t="n">
         <v>29900</v>
       </c>
-      <c r="G54" s="2" t="n"/>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>BEBES, ropa, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -3471,15 +3421,13 @@
         <v>59900</v>
       </c>
       <c r="F55" s="3" t="n"/>
-      <c r="G55" s="2" t="n"/>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>alimentación, BEBES, Teteros, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -3524,15 +3472,13 @@
         <v>59000</v>
       </c>
       <c r="F56" s="3" t="n"/>
-      <c r="G56" s="2" t="n"/>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">baby shower, BEBES, cobijas y toallas, mas comprados, todos </t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -3579,15 +3525,13 @@
       <c r="F57" s="3" t="n">
         <v>84000</v>
       </c>
-      <c r="G57" s="2" t="n"/>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>juguetes, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -3634,15 +3578,13 @@
       <c r="F58" s="3" t="n">
         <v>80000</v>
       </c>
-      <c r="G58" s="2" t="n"/>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>BEBES, juguetes, mas vendidos, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -3689,15 +3631,13 @@
       <c r="F59" s="3" t="n">
         <v>63000</v>
       </c>
-      <c r="G59" s="2" t="n"/>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>accesorios, baby shower, BEBES, mas comprados, todos los pro</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -3744,15 +3684,13 @@
       <c r="F60" s="3" t="n">
         <v>40000</v>
       </c>
-      <c r="G60" s="2" t="n"/>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>BEBES, mas vendidos, Teteros, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -3799,15 +3737,13 @@
       <c r="F61" s="3" t="n">
         <v>78571</v>
       </c>
-      <c r="G61" s="2" t="n"/>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>alimentación, baby shower, BEBES, mas comprados, mas vendido</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -3854,15 +3790,13 @@
       <c r="F62" s="3" t="n">
         <v>77000</v>
       </c>
-      <c r="G62" s="2" t="n"/>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>juguetes, mas vendidos, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -3909,15 +3843,13 @@
       <c r="F63" s="3" t="n">
         <v>72143</v>
       </c>
-      <c r="G63" s="2" t="n"/>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>bacinillas, BEBES, mas comprados, mas vendidos, todos los pr</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -3964,15 +3896,13 @@
       <c r="F64" s="3" t="n">
         <v>71000</v>
       </c>
-      <c r="G64" s="2" t="n"/>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>alimentación, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -4019,15 +3949,17 @@
       <c r="F65" s="3" t="n">
         <v>67000</v>
       </c>
-      <c r="G65" s="2" t="n"/>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Azul', 'Verde', 'Rosa']</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">baby shower, bacinillas, mas comprados, mas vendidos, todos </t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -4074,15 +4006,17 @@
       <c r="F66" s="3" t="n">
         <v>71000</v>
       </c>
-      <c r="G66" s="2" t="n"/>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Púrpura', 'Rosa']</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>BEBES, teteros, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -4129,15 +4063,13 @@
       <c r="F67" s="3" t="n">
         <v>70000</v>
       </c>
-      <c r="G67" s="2" t="n"/>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>alimentación, aseo, BEBES, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -4184,15 +4116,13 @@
       <c r="F68" s="3" t="n">
         <v>71286</v>
       </c>
-      <c r="G68" s="2" t="n"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
         <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>baby shower, BEBES, juguetes, mas comprados, mas vendidos, t</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -4239,15 +4169,13 @@
       <c r="F69" s="3" t="n">
         <v>70000</v>
       </c>
-      <c r="G69" s="2" t="n"/>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>BEBES, juguetes, mas comprados, mas vendidos, todos los prod</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -4294,15 +4222,13 @@
       <c r="F70" s="3" t="n">
         <v>70000</v>
       </c>
-      <c r="G70" s="2" t="n"/>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>baby shower, juguetes, mas vendidos, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -4349,15 +4275,13 @@
       <c r="F71" s="3" t="n">
         <v>68571</v>
       </c>
-      <c r="G71" s="2" t="n"/>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>baby shower, BEBES, juguetes, mas vendidos, todos los produc</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -4404,15 +4328,13 @@
       <c r="F72" s="3" t="n">
         <v>67143</v>
       </c>
-      <c r="G72" s="2" t="n"/>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>aseo, BEBES, mas vendidos, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -4459,15 +4381,13 @@
       <c r="F73" s="3" t="n">
         <v>67143</v>
       </c>
-      <c r="G73" s="2" t="n"/>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>baby shower, juguetes, mas vendidos, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -4514,15 +4434,13 @@
       <c r="F74" s="3" t="n">
         <v>66000</v>
       </c>
-      <c r="G74" s="2" t="n"/>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>alimentación, baby shower, BEBES, mas vendidos, todos los pr</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -4569,15 +4487,13 @@
       <c r="F75" s="3" t="n">
         <v>65714</v>
       </c>
-      <c r="G75" s="2" t="n"/>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>baby shower, BEBES, juguetes, mas vendidos, todos los produc</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -4624,15 +4540,13 @@
       <c r="F76" s="3" t="n">
         <v>64000</v>
       </c>
-      <c r="G76" s="2" t="n"/>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>alimentación, aseo, BEBES, todos los productos, top-ventas</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -4677,15 +4591,13 @@
         <v>43000</v>
       </c>
       <c r="F77" s="3" t="n"/>
-      <c r="G77" s="2" t="n"/>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>baby shower, BEBES, mas comprados, mas vendidos, recién naci</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -4732,15 +4644,13 @@
       <c r="F78" s="3" t="n">
         <v>60000</v>
       </c>
-      <c r="G78" s="2" t="n"/>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>baby shower, BEBES, cobijas y toallas, mas comprados, recién</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -4787,15 +4697,13 @@
       <c r="F79" s="3" t="n">
         <v>58429</v>
       </c>
-      <c r="G79" s="2" t="n"/>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>aseo, baby shower, mas vendidos, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -4842,15 +4750,13 @@
       <c r="F80" s="3" t="n">
         <v>57143</v>
       </c>
-      <c r="G80" s="2" t="n"/>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>BEBES, juguetes, mas vendidos, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -4897,15 +4803,13 @@
       <c r="F81" s="3" t="n">
         <v>57143</v>
       </c>
-      <c r="G81" s="2" t="n"/>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>alimentación, BEBES, mas vendidos, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -4952,15 +4856,17 @@
       <c r="F82" s="3" t="n">
         <v>55000</v>
       </c>
-      <c r="G82" s="2" t="n"/>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Transparente', 'Rosa', 'Verde', 'Azul']</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">baby shower, BEBES, lactancia, mas comprados, mas vendidos, </t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -5007,15 +4913,13 @@
       <c r="F83" s="3" t="n">
         <v>54286</v>
       </c>
-      <c r="G83" s="2" t="n"/>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>baby shower, juguetes, mas vendidos, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -5062,15 +4966,13 @@
       <c r="F84" s="3" t="n">
         <v>53571</v>
       </c>
-      <c r="G84" s="2" t="n"/>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>bacinillas, BEBES, mas vendidos, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -5117,15 +5019,13 @@
       <c r="F85" s="3" t="n">
         <v>51429</v>
       </c>
-      <c r="G85" s="2" t="n"/>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>baby shower, BEBES, cobijas y toallas, mas comprados, mas ve</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -5172,15 +5072,13 @@
       <c r="F86" s="3" t="n">
         <v>50000</v>
       </c>
-      <c r="G86" s="2" t="n"/>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>baby shower, juguetes, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -5227,15 +5125,13 @@
       <c r="F87" s="3" t="n">
         <v>50000</v>
       </c>
-      <c r="G87" s="2" t="n"/>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>BEBES, juguetes, mas comprados, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -5282,15 +5178,13 @@
       <c r="F88" s="3" t="n">
         <v>50000</v>
       </c>
-      <c r="G88" s="2" t="n"/>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>BEBES, lactancia, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -5337,15 +5231,13 @@
       <c r="F89" s="3" t="n">
         <v>50000</v>
       </c>
-      <c r="G89" s="2" t="n"/>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>accesorios, baby shower, BEBES, mas vendidos, todos los prod</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
@@ -5392,15 +5284,17 @@
       <c r="F90" s="3" t="n">
         <v>47600</v>
       </c>
-      <c r="G90" s="2" t="n"/>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Rosa', 'Amarillo', 'Verde', 'Azul']</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>aseo, baby shower, mas vendidos, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -5447,15 +5341,13 @@
       <c r="F91" s="3" t="n">
         <v>47857</v>
       </c>
-      <c r="G91" s="2" t="n"/>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>bacinillas, mas vendidos, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -5502,15 +5394,13 @@
       <c r="F92" s="3" t="n">
         <v>47143</v>
       </c>
-      <c r="G92" s="2" t="n"/>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>baby shower, BEBES, cobijas y toallas, mas comprados, mas ve</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -5557,15 +5447,17 @@
       <c r="F93" s="3" t="n">
         <v>43857</v>
       </c>
-      <c r="G93" s="2" t="n"/>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Rojo', 'azul']</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>mas comprados, mas vendidos, teteros, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -5612,15 +5504,13 @@
       <c r="F94" s="3" t="n">
         <v>40714</v>
       </c>
-      <c r="G94" s="2" t="n"/>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>baby shower, BEBES, cobijas y toallas, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -5667,15 +5557,13 @@
       <c r="F95" s="3" t="n">
         <v>36900</v>
       </c>
-      <c r="G95" s="2" t="n"/>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>aseo, baby shower, BEBES, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -5720,15 +5608,13 @@
         <v>28000</v>
       </c>
       <c r="F96" s="3" t="n"/>
-      <c r="G96" s="2" t="n"/>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>baby shower, BEBES, mas vendidos, recién nacido, ropa, todos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -5775,15 +5661,13 @@
       <c r="F97" s="3" t="n">
         <v>38571</v>
       </c>
-      <c r="G97" s="2" t="n"/>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>aseo, BEBES, mas vendidos, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -5830,15 +5714,13 @@
       <c r="F98" s="3" t="n">
         <v>38571</v>
       </c>
-      <c r="G98" s="2" t="n"/>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>aseo, baby shower, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -5885,15 +5767,17 @@
       <c r="F99" s="3" t="n">
         <v>27000</v>
       </c>
-      <c r="G99" s="2" t="n"/>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Rosa', 'Azul']</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>aseo, baby shower, mas comprados, mas vendidos, todos los pr</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
@@ -5940,15 +5824,13 @@
       <c r="F100" s="3" t="n">
         <v>34900</v>
       </c>
-      <c r="G100" s="2" t="n"/>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>aseo, baby shower, BEBES, mas comprados, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -5995,15 +5877,13 @@
       <c r="F101" s="3" t="n">
         <v>34286</v>
       </c>
-      <c r="G101" s="2" t="n"/>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>baby shower, BEBES, cobijas y toallas, mas comprados, mas ve</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -6050,15 +5930,13 @@
       <c r="F102" s="3" t="n">
         <v>31429</v>
       </c>
-      <c r="G102" s="2" t="n"/>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>baby shower, BEBES, juguetes, mas vendidos, todos los produc</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -6105,15 +5983,13 @@
       <c r="F103" s="3" t="n">
         <v>31429</v>
       </c>
-      <c r="G103" s="2" t="n"/>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>baby shower, BEBES, cobijas y toallas, mas comprados, mas ve</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
@@ -6160,15 +6036,17 @@
       <c r="F104" s="3" t="n">
         <v>31000</v>
       </c>
-      <c r="G104" s="2" t="n"/>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Blanco', 'Verde', 'azul']</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>alimentación, mas vendidos, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -6215,15 +6093,17 @@
       <c r="F105" s="3" t="n">
         <v>31000</v>
       </c>
-      <c r="G105" s="2" t="n"/>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Púrpura', 'Rosa']</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>alimentación, baby shower, mas vendidos, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
@@ -6270,15 +6150,17 @@
       <c r="F106" s="3" t="n">
         <v>27600</v>
       </c>
-      <c r="G106" s="2" t="n"/>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Azul', 'Rosa']</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>alimentación, baby shower, mas vendidos, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
@@ -6325,15 +6207,17 @@
       <c r="F107" s="3" t="n">
         <v>27600</v>
       </c>
-      <c r="G107" s="2" t="n"/>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Frutas', 'Números', 'Letras']</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>baby shower, juguetes, mas vendidos, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
@@ -6380,15 +6264,13 @@
       <c r="F108" s="3" t="n">
         <v>27143</v>
       </c>
-      <c r="G108" s="2" t="n"/>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>BEBES, mas vendidos, Teteros, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
@@ -6435,15 +6317,17 @@
       <c r="F109" s="3" t="n">
         <v>27143</v>
       </c>
-      <c r="G109" s="2" t="n"/>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Aguamarina', 'Negro']</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>bacinillas, BEBES, mas comprados, mas vendidos, todos los pr</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
@@ -6490,15 +6374,13 @@
       <c r="F110" s="3" t="n">
         <v>25714</v>
       </c>
-      <c r="G110" s="2" t="n"/>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>baby shower, BEBES, lactancia, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
@@ -6545,15 +6427,17 @@
       <c r="F111" s="3" t="n">
         <v>22600</v>
       </c>
-      <c r="G111" s="2" t="n"/>
-      <c r="H111" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Rosa', 'Azul', 'Transparente']</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>baby shower, mas comprados, mas vendidos, Teteros, todos los</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
@@ -6598,15 +6482,17 @@
         <v>17500</v>
       </c>
       <c r="F112" s="3" t="n"/>
-      <c r="G112" s="2" t="n"/>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Azul', 'Rosa']</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>BEBES, mas vendidos, teteros, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
@@ -6653,15 +6539,17 @@
       <c r="F113" s="3" t="n">
         <v>22000</v>
       </c>
-      <c r="G113" s="2" t="n"/>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Rosa', 'Azul', 'Transparente']</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>baby shower, mas comprados, mas vendidos, Teteros, todos los</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
@@ -6708,15 +6596,13 @@
       <c r="F114" s="3" t="n">
         <v>23571</v>
       </c>
-      <c r="G114" s="2" t="n"/>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>lactancia, mas comprados, mas vendidos, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
@@ -6763,15 +6649,13 @@
       <c r="F115" s="3" t="n">
         <v>22857</v>
       </c>
-      <c r="G115" s="2" t="n"/>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>aseo, baby shower, BEBES, mas comprados, mas vendidos, todos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
@@ -6818,15 +6702,13 @@
       <c r="F116" s="3" t="n">
         <v>19900</v>
       </c>
-      <c r="G116" s="2" t="n"/>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>baby shower, BEBES, ropa, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
@@ -6873,15 +6755,13 @@
       <c r="F117" s="3" t="n">
         <v>20000</v>
       </c>
-      <c r="G117" s="2" t="n"/>
-      <c r="H117" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>aseo, baby shower, BEBES, mas vendidos, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
@@ -6928,15 +6808,13 @@
       <c r="F118" s="3" t="n">
         <v>17857</v>
       </c>
-      <c r="G118" s="2" t="n"/>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>aseo, baby shower, mas vendidos, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
@@ -6983,15 +6861,17 @@
       <c r="F119" s="3" t="n">
         <v>17143</v>
       </c>
-      <c r="G119" s="2" t="n"/>
-      <c r="H119" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Aguamarina', 'Azul', 'fucsia']</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>bacinillas, BEBES, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
@@ -7038,15 +6918,13 @@
       <c r="F120" s="3" t="n">
         <v>15714</v>
       </c>
-      <c r="G120" s="2" t="n"/>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>baby shower, BEBES, juguetes, mas comprados, mas vendidos, t</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
@@ -7093,15 +6971,13 @@
       <c r="F121" s="3" t="n">
         <v>15714</v>
       </c>
-      <c r="G121" s="2" t="n"/>
-      <c r="H121" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>baby shower, BEBES, juguetes, mas vendidos, todos los produc</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J121" s="2" t="inlineStr">
@@ -7148,15 +7024,13 @@
       <c r="F122" s="3" t="n">
         <v>15714</v>
       </c>
-      <c r="G122" s="2" t="n"/>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>baby shower, juguetes, mas vendidos, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
@@ -7203,15 +7077,17 @@
       <c r="F123" s="3" t="n">
         <v>13600</v>
       </c>
-      <c r="G123" s="2" t="n"/>
-      <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Azul', 'Rosa', 'Transparente']</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>baby shower, mas vendidos, Teteros, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
@@ -7258,15 +7134,17 @@
       <c r="F124" s="3" t="n">
         <v>15000</v>
       </c>
-      <c r="G124" s="2" t="n"/>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Rosa', 'Azul', 'Verde']</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>accesorios, baby shower, juguetes, mas comprados, mas vendid</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
@@ -7313,15 +7191,13 @@
       <c r="F125" s="3" t="n">
         <v>14857</v>
       </c>
-      <c r="G125" s="2" t="n"/>
-      <c r="H125" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>aseo, baby shower, mas vendidos, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
@@ -7368,15 +7244,17 @@
       <c r="F126" s="3" t="n">
         <v>14000</v>
       </c>
-      <c r="G126" s="2" t="n"/>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Amarillo', 'Rosa', 'Verde']</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>baby shower, BEBES, juguetes, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
@@ -7423,15 +7301,13 @@
       <c r="F127" s="3" t="n">
         <v>14286</v>
       </c>
-      <c r="G127" s="2" t="n"/>
-      <c r="H127" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>alimentación, baby shower, BEBES, mas vendidos, todos los pr</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
@@ -7478,15 +7354,13 @@
       <c r="F128" s="3" t="n">
         <v>14143</v>
       </c>
-      <c r="G128" s="2" t="n"/>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>baby shower, BEBES, juguetes, mas comprados, mas vendidos, t</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
@@ -7533,15 +7407,13 @@
       <c r="F129" s="3" t="n">
         <v>12857</v>
       </c>
-      <c r="G129" s="2" t="n"/>
-      <c r="H129" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">alimentación, BEBES, mas comprados, mas vendidos, todos los </t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
@@ -7588,15 +7460,13 @@
       <c r="F130" s="3" t="n">
         <v>12143</v>
       </c>
-      <c r="G130" s="2" t="n"/>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>aseo, baby shower, BEBES, mas comprados, mas vendidos, todos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
@@ -7643,15 +7513,17 @@
       <c r="F131" s="3" t="n">
         <v>9000</v>
       </c>
-      <c r="G131" s="2" t="n"/>
-      <c r="H131" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Verde', 'Naranja', 'Azul', 'Aguamarina']</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>alimentación, baby shower, mas vendidos, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
@@ -7696,15 +7568,13 @@
         <v>7500</v>
       </c>
       <c r="F132" s="3" t="n"/>
-      <c r="G132" s="2" t="n"/>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>aseo, BEBES, mas comprados, mas vendidos, todos los producto</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
@@ -7751,15 +7621,17 @@
       <c r="F133" s="3" t="n">
         <v>7000</v>
       </c>
-      <c r="G133" s="2" t="n"/>
-      <c r="H133" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Azul', 'Rosa']</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>aseo, baby shower, mas vendidos, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
@@ -7806,15 +7678,13 @@
       <c r="F134" s="3" t="n">
         <v>9286</v>
       </c>
-      <c r="G134" s="2" t="n"/>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>aseo, BEBES, mas vendidos, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
@@ -7861,15 +7731,13 @@
       <c r="F135" s="3" t="n">
         <v>8571</v>
       </c>
-      <c r="G135" s="2" t="n"/>
-      <c r="H135" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>aseo, baby shower, BEBES, mas comprados, mas vendidos, todos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J135" s="2" t="inlineStr">
@@ -7916,15 +7784,13 @@
       <c r="F136" s="3" t="n">
         <v>6714</v>
       </c>
-      <c r="G136" s="2" t="n"/>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>aseo, baby shower, mas vendidos, todos los productos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
@@ -8016,108 +7882,108 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-12 20:40</t>
+          <t>2026-10-12 22:46</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>En colección Baby shower</t>
+          <t>En colección Accesorios</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>85</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>En colección Más vendidos</t>
+          <t>En colección Alimentación</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>En colección Juguetes</t>
+          <t>En colección Aseo y cuidado</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>En colección Aseo y cuidado</t>
+          <t>En colección Baby shower</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>En colección Alimentación</t>
+          <t>En colección Bacinillas</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>En colección Teteros</t>
+          <t>En colección Cobijas y toallas</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>En colección Recién nacido</t>
+          <t>En colección Combos</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>En colección Accesorios</t>
+          <t>En colección Juguetes</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>En colección Combos</t>
+          <t>En colección Lactancia</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>En colección Ropa</t>
+          <t>En colección Más vendidos</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16">
@@ -8133,41 +7999,41 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>En colección Bacinillas</t>
+          <t>En colección Pañaleras</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>En colección Cobijas y toallas</t>
+          <t>En colección Recién nacido</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>En colección Lactancia</t>
+          <t>En colección Ropa</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>En colección Pañaleras</t>
+          <t>En colección Teteros</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$M$136</definedName>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-12 22:46</t>
+          <t>2026-10-13 06:25</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$M$136</definedName>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-13 06:25</t>
+          <t>2026-10-13 02:14</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7882,7 +7882,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:14</t>
+          <t>2026-10-13 03:45</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7882,7 +7882,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-13 03:45</t>
+          <t>2026-10-13 04:26</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7882,7 +7882,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-13 04:26</t>
+          <t>2026-10-13 04:46</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$M$136</definedName>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-13 04:46</t>
+          <t>2026-10-13 12:24</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$M$136</definedName>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-13 12:24</t>
+          <t>2026-10-13 08:42</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7882,7 +7882,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-13 08:42</t>
+          <t>2026-10-13 09:42</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7882,7 +7882,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-13 09:42</t>
+          <t>2026-10-13 13:17</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$M$136</definedName>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-13 13:17</t>
+          <t>2026-10-13 18:24</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$M$136</definedName>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-13 18:24</t>
+          <t>2026-10-13 14:49</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7882,7 +7882,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-13 14:49</t>
+          <t>2026-10-13 15:46</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$M$136</definedName>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-13 15:46</t>
+          <t>2026-10-14 00:35</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7882,7 +7882,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 00:35</t>
+          <t>2026-10-14 06:33</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7882,7 +7882,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 06:33</t>
+          <t>2026-10-14 12:35</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7882,7 +7882,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 12:35</t>
+          <t>2026-10-14 18:34</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7882,7 +7882,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 18:34</t>
+          <t>2026-10-15 00:34</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7882,7 +7882,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-15 00:34</t>
+          <t>2026-10-15 06:34</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$M$136</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$M$137</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M136"/>
+  <dimension ref="A1:M137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1810,7 +1810,7 @@
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>105000</v>
+        <v>110000</v>
       </c>
       <c r="F25" s="3" t="n">
         <v>150000</v>
@@ -5371,11 +5371,11 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>10649163104566</v>
+        <v>15420728574262</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Cobija capota animales Modelo CL1006</t>
+          <t>Perrito Superhéroe Musical con Luces | Super Electric Dog</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -5385,14 +5385,14 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Recién nacido, Cobijas y toallas, Baby shower, Más vendidos</t>
+          <t>Juguetes</t>
         </is>
       </c>
       <c r="E92" s="3" t="n">
         <v>33000</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>47143</v>
+        <v>47000</v>
       </c>
       <c r="G92" s="2" t="inlineStr"/>
       <c r="H92" s="2" t="n">
@@ -5405,30 +5405,30 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/cobija-capota-animales-modelo-cl1006</t>
+          <t>https://www.solobabys.com/products/perrito-superheroe-musical-con-luces-super-electric-dog</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-03-21at4.46.17PM_1.jpg?v=1774733372</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/super-electric-dog-2.webp?v=1792063802</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-title { font-family: 'Fraunces', serif; font-size: 38px; line-height: 1.1; color: #00afba; margin: 0 0 15px 0; letter-spacin</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>10721369522486</v>
+        <v>10649163104566</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Cepillo Lava Teteros | MST6608</t>
+          <t>Cobija capota animales Modelo CL1006</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -5438,22 +5438,18 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Teteros, Más vendidos</t>
+          <t>Recién nacido, Cobijas y toallas, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E93" s="3" t="n">
-        <v>30700</v>
+        <v>33000</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>43857</v>
-      </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Rojo', 'azul']</t>
-        </is>
-      </c>
+        <v>47143</v>
+      </c>
+      <c r="G93" s="2" t="inlineStr"/>
       <c r="H93" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
@@ -5462,12 +5458,12 @@
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/cepillo-lava-teteros-mst6608</t>
+          <t>https://www.solobabys.com/products/cobija-capota-animales-modelo-cl1006</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_17.webp?v=1779418188</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-03-21at4.46.17PM_1.jpg?v=1774733372</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
@@ -5481,11 +5477,11 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>10643571310902</v>
+        <v>10721369522486</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Toalla suave y absorbente para bebé</t>
+          <t>Cepillo Lava Teteros | MST6608</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -5495,18 +5491,22 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Cobijas y toallas, Baby shower</t>
+          <t>Teteros, Más vendidos</t>
         </is>
       </c>
       <c r="E94" s="3" t="n">
-        <v>28500</v>
+        <v>30700</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>40714</v>
-      </c>
-      <c r="G94" s="2" t="inlineStr"/>
+        <v>43857</v>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Rojo', 'azul']</t>
+        </is>
+      </c>
       <c r="H94" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
@@ -5515,12 +5515,12 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/toalla-suave-y-absorbente-para-bebe</t>
+          <t>https://www.solobabys.com/products/cepillo-lava-teteros-mst6608</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-03-21at5.41.21PM_3.jpg?v=1774569011</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_17.webp?v=1779418188</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
@@ -5534,11 +5534,11 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>10643571573046</v>
+        <v>10643571310902</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Set de Aseo Kokibebe</t>
+          <t>Toalla suave y absorbente para bebé</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -5548,14 +5548,14 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower</t>
+          <t>Cobijas y toallas, Baby shower</t>
         </is>
       </c>
       <c r="E95" s="3" t="n">
         <v>28500</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>36900</v>
+        <v>40714</v>
       </c>
       <c r="G95" s="2" t="inlineStr"/>
       <c r="H95" s="2" t="n">
@@ -5568,16 +5568,16 @@
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/set-de-aseo-kokibebe</t>
+          <t>https://www.solobabys.com/products/toalla-suave-y-absorbente-para-bebe</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla-2026-03-27T110341.589_a2241f01-ac70-4d1e-a938-52f6eaddf13d.webp?v=1774627574</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-03-21at5.41.21PM_3.jpg?v=1774569011</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
@@ -5587,11 +5587,11 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>10837689532726</v>
+        <v>10643571573046</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Ajuar prematuro para Bebé 5 Piezas – My Best Friends</t>
+          <t>Set de Aseo Kokibebe</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -5601,13 +5601,15 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Recién nacido, Ropa, Baby shower</t>
+          <t>Aseo y cuidado, Baby shower</t>
         </is>
       </c>
       <c r="E96" s="3" t="n">
-        <v>28000</v>
-      </c>
-      <c r="F96" s="3" t="n"/>
+        <v>28500</v>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>36900</v>
+      </c>
       <c r="G96" s="2" t="inlineStr"/>
       <c r="H96" s="2" t="n">
         <v>1</v>
@@ -5619,12 +5621,12 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/ajuar-para-bebe-5-piezas-my-best-friends</t>
+          <t>https://www.solobabys.com/products/set-de-aseo-kokibebe</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-03at11.35.47AM_2.webp?v=1788819715</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla-2026-03-27T110341.589_a2241f01-ac70-4d1e-a938-52f6eaddf13d.webp?v=1774627574</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
@@ -5638,11 +5640,11 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>10837681799478</v>
+        <v>10837689532726</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Lima Eléctrica para Uñas de Bebé</t>
+          <t>Ajuar prematuro para Bebé 5 Piezas – My Best Friends</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -5652,15 +5654,13 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Juguetes</t>
+          <t>Recién nacido, Ropa, Baby shower</t>
         </is>
       </c>
       <c r="E97" s="3" t="n">
-        <v>27000</v>
-      </c>
-      <c r="F97" s="3" t="n">
-        <v>38571</v>
-      </c>
+        <v>28000</v>
+      </c>
+      <c r="F97" s="3" t="n"/>
       <c r="G97" s="2" t="inlineStr"/>
       <c r="H97" s="2" t="n">
         <v>1</v>
@@ -5672,16 +5672,16 @@
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/set-de-manicure-para-bebe</t>
+          <t>https://www.solobabys.com/products/ajuar-para-bebe-5-piezas-my-best-friends</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage7sept2026_17_09_49.webp?v=1788819099</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-03at11.35.47AM_2.webp?v=1788819715</t>
         </is>
       </c>
       <c r="L97" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
@@ -5691,11 +5691,11 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>10650935755062</v>
+        <v>10837681799478</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Crema Protectora Happy Soft 250gr | Cuidado y Protección para Bebé</t>
+          <t>Lima Eléctrica para Uñas de Bebé</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower</t>
+          <t>Aseo y cuidado, Juguetes</t>
         </is>
       </c>
       <c r="E98" s="3" t="n">
@@ -5725,16 +5725,16 @@
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/crema-protectora-happy-soft-250gr-cuidado-y-proteccion-para-bebe</t>
+          <t>https://www.solobabys.com/products/set-de-manicure-para-bebe</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-01T022000.472.webp?v=1780298415</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage7sept2026_17_09_49.webp?v=1788819099</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
@@ -5744,11 +5744,11 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>10642900058422</v>
+        <v>10650935755062</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Lima Eléctrica Only Baby | Cuidado Seguro de Uñas para Bebé</t>
+          <t>Crema Protectora Happy Soft 250gr | Cuidado y Protección para Bebé</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -5758,22 +5758,18 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Accesorios, Baby shower, Más vendidos</t>
+          <t>Aseo y cuidado, Baby shower</t>
         </is>
       </c>
       <c r="E99" s="3" t="n">
-        <v>25500</v>
+        <v>27000</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>27000</v>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Rosa', 'Azul']</t>
-        </is>
-      </c>
+        <v>38571</v>
+      </c>
+      <c r="G99" s="2" t="inlineStr"/>
       <c r="H99" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
@@ -5782,16 +5778,16 @@
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/lima-electrica-only-baby-cuidado-seguro-de-unas-para-bebe</t>
+          <t>https://www.solobabys.com/products/crema-protectora-happy-soft-250gr-cuidado-y-proteccion-para-bebe</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/limaelectrica_1000x_b8a0febc-3486-42a7-a3cf-8a61cc5b6601.webp?v=1774036791</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-01T022000.472.webp?v=1780298415</t>
         </is>
       </c>
       <c r="L99" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
@@ -5801,11 +5797,11 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>10643572031798</v>
+        <v>10642900058422</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Set Manicure Baby Care</t>
+          <t>Lima Eléctrica Only Baby | Cuidado Seguro de Uñas para Bebé</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -5819,14 +5815,18 @@
         </is>
       </c>
       <c r="E100" s="3" t="n">
-        <v>25000</v>
+        <v>25500</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>34900</v>
-      </c>
-      <c r="G100" s="2" t="inlineStr"/>
+        <v>27000</v>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Rosa', 'Azul']</t>
+        </is>
+      </c>
       <c r="H100" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
@@ -5835,12 +5835,12 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/set-manicure-baby-care</t>
+          <t>https://www.solobabys.com/products/lima-electrica-only-baby-cuidado-seguro-de-unas-para-bebe</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla-2026-03-27T143126.593_2c7a959d-f5cc-459d-81e2-3ea14b4df0ba.webp?v=1774640025</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/limaelectrica_1000x_b8a0febc-3486-42a7-a3cf-8a61cc5b6601.webp?v=1774036791</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
@@ -5854,11 +5854,11 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>10651062665526</v>
+        <v>10643572031798</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Cobija TG 08 burbuja Diseños surtidos</t>
+          <t>Set Manicure Baby Care</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -5868,14 +5868,14 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Cobijas y toallas, Baby shower, Más vendidos</t>
+          <t>Aseo y cuidado, Accesorios, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E101" s="3" t="n">
-        <v>24000</v>
+        <v>25000</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>34286</v>
+        <v>34900</v>
       </c>
       <c r="G101" s="2" t="inlineStr"/>
       <c r="H101" s="2" t="n">
@@ -5888,16 +5888,16 @@
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/cobija-tg-08-burbuja-disenos-surtidos</t>
+          <t>https://www.solobabys.com/products/set-manicure-baby-care</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_-_2026-06-03T163734.732.webp?v=1780522748</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla-2026-03-27T143126.593_2c7a959d-f5cc-459d-81e2-3ea14b4df0ba.webp?v=1774640025</t>
         </is>
       </c>
       <c r="L101" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
@@ -5907,11 +5907,11 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>10762511089974</v>
+        <v>10651062665526</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>MORDEDOR CON CADENA ONLY| HLW-040</t>
+          <t>Cobija TG 08 burbuja Diseños surtidos</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -5921,14 +5921,14 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Baby shower</t>
+          <t>Cobijas y toallas, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E102" s="3" t="n">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>31429</v>
+        <v>34286</v>
       </c>
       <c r="G102" s="2" t="inlineStr"/>
       <c r="H102" s="2" t="n">
@@ -5941,30 +5941,30 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/mordedor-con-sujetador-para-bebe</t>
+          <t>https://www.solobabys.com/products/cobija-tg-08-burbuja-disenos-surtidos</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage2jul2026_07_37_12a.m.webp?v=1782995871</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_-_2026-06-03T163734.732.webp?v=1780522748</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container{font-family:'Quicksand',sans-serif;max-width:480px;margin:0 auto;color:#4a5568;padding:26px;background:#fff;} .b-rating{display:flex;align-items:center;gap:8px;margin-bottom:12px;font-size:14px;font-weight:700;color:#c8d431;flex-wrap:wrap;} .b-rating-text</t>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>10651054637366</v>
+        <v>10762511089974</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Cobija vilu cinta estampada Diseños surtidos</t>
+          <t>MORDEDOR CON CADENA ONLY| HLW-040</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Cobijas y toallas, Baby shower, Más vendidos</t>
+          <t>Juguetes, Baby shower</t>
         </is>
       </c>
       <c r="E103" s="3" t="n">
@@ -5994,30 +5994,30 @@
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/cobija-vilu-cinta-estampada-disenos-surtidos</t>
+          <t>https://www.solobabys.com/products/mordedor-con-sujetador-para-bebe</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_-_2026-06-02T212801.807.webp?v=1780453770</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage2jul2026_07_37_12a.m.webp?v=1782995871</t>
         </is>
       </c>
       <c r="L103" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container{font-family:'Quicksand',sans-serif;max-width:480px;margin:0 auto;color:#4a5568;padding:26px;background:#fff;} .b-rating{display:flex;align-items:center;gap:8px;margin-bottom:12px;font-size:14px;font-weight:700;color:#c8d431;flex-wrap:wrap;} .b-rating-text</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>10721360019766</v>
+        <v>10651054637366</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Termo Plegable Infantil Balón | JS-8</t>
+          <t>Cobija vilu cinta estampada Diseños surtidos</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -6027,22 +6027,18 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Alimentación</t>
+          <t>Cobijas y toallas, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E104" s="3" t="n">
         <v>22000</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>31000</v>
-      </c>
-      <c r="G104" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Blanco', 'Verde', 'azul']</t>
-        </is>
-      </c>
+        <v>31429</v>
+      </c>
+      <c r="G104" s="2" t="inlineStr"/>
       <c r="H104" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
@@ -6051,12 +6047,12 @@
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/termo-plegable-infantil-balon-js-8</t>
+          <t>https://www.solobabys.com/products/cobija-vilu-cinta-estampada-disenos-surtidos</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_14.webp?v=1779414355</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_-_2026-06-02T212801.807.webp?v=1780453770</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
@@ -6070,11 +6066,11 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>10721353236790</v>
+        <v>10721360019766</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Termo Plegable Infantil | JS-9</t>
+          <t>Termo Plegable Infantil Balón | JS-8</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -6084,7 +6080,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Alimentación, Baby shower</t>
+          <t>Alimentación</t>
         </is>
       </c>
       <c r="E105" s="3" t="n">
@@ -6095,11 +6091,11 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Color: ['Púrpura', 'Rosa']</t>
+          <t>Color: ['Blanco', 'Verde', 'azul']</t>
         </is>
       </c>
       <c r="H105" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
@@ -6108,16 +6104,16 @@
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/termo-plegable-infantil-js-9</t>
+          <t>https://www.solobabys.com/products/termo-plegable-infantil-balon-js-8</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_8.webp?v=1779411444</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_14.webp?v=1779414355</t>
         </is>
       </c>
       <c r="L105" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
@@ -6127,11 +6123,11 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>10643064684854</v>
+        <v>10721353236790</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Vaso Amazing Baby | MON1035</t>
+          <t>Termo Plegable Infantil | JS-9</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -6145,14 +6141,14 @@
         </is>
       </c>
       <c r="E106" s="3" t="n">
-        <v>21000</v>
+        <v>22000</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>27600</v>
+        <v>31000</v>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Color: ['Azul', 'Rosa']</t>
+          <t>Color: ['Púrpura', 'Rosa']</t>
         </is>
       </c>
       <c r="H106" s="2" t="n">
@@ -6165,16 +6161,16 @@
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/vaso-amazing-baby-vaso-entrenador-con-asas</t>
+          <t>https://www.solobabys.com/products/termo-plegable-infantil-js-9</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/sbproductos_3_1.webp?v=1774046605</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_8.webp?v=1779411444</t>
         </is>
       </c>
       <c r="L106" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
@@ -6184,11 +6180,11 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>10642009358646</v>
+        <v>10643064684854</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Tapete Foamy Rompecabezas Infantil | Piso Didáctico para Bebé y Niños</t>
+          <t>Vaso Amazing Baby | MON1035</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -6198,22 +6194,22 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Baby shower</t>
+          <t>Alimentación, Baby shower</t>
         </is>
       </c>
       <c r="E107" s="3" t="n">
-        <v>20500</v>
+        <v>21000</v>
       </c>
       <c r="F107" s="3" t="n">
         <v>27600</v>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Color: ['Frutas', 'Números', 'Letras']</t>
+          <t>Color: ['Azul', 'Rosa']</t>
         </is>
       </c>
       <c r="H107" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
@@ -6222,16 +6218,16 @@
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/tapete-foamy-rompecabezas-infantil-piso-didactico-para-bebe-y-ninos</t>
+          <t>https://www.solobabys.com/products/vaso-amazing-baby-vaso-entrenador-con-asas</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/D_NQ_NP_2X_812378-CBT91060493341_082025-F.webp?v=1773965161</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/sbproductos_3_1.webp?v=1774046605</t>
         </is>
       </c>
       <c r="L107" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
@@ -6241,11 +6237,11 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>10729673720118</v>
+        <v>10642009358646</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Tetero Only 8 Onzas | A2DJ</t>
+          <t>Tapete Foamy Rompecabezas Infantil | Piso Didáctico para Bebé y Niños</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -6255,18 +6251,22 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Teteros</t>
+          <t>Juguetes, Baby shower</t>
         </is>
       </c>
       <c r="E108" s="3" t="n">
-        <v>19000</v>
+        <v>20500</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>27143</v>
-      </c>
-      <c r="G108" s="2" t="inlineStr"/>
+        <v>27600</v>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Frutas', 'Números', 'Letras']</t>
+        </is>
+      </c>
       <c r="H108" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
@@ -6275,16 +6275,16 @@
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/tetero-only-8-onzas-a2dj</t>
+          <t>https://www.solobabys.com/products/tapete-foamy-rompecabezas-infantil-piso-didactico-para-bebe-y-ninos</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_88.webp?v=1780097838</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/D_NQ_NP_2X_812378-CBT91060493341_082025-F.webp?v=1773965161</t>
         </is>
       </c>
       <c r="L108" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
@@ -6294,11 +6294,11 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>10651909718326</v>
+        <v>10729673720118</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Orinal infantil Praktiplas Pingüino</t>
+          <t>Tetero Only 8 Onzas | A2DJ</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Bacinillas, Más vendidos</t>
+          <t>Teteros</t>
         </is>
       </c>
       <c r="E109" s="3" t="n">
@@ -6317,13 +6317,9 @@
       <c r="F109" s="3" t="n">
         <v>27143</v>
       </c>
-      <c r="G109" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Aguamarina', 'Negro']</t>
-        </is>
-      </c>
+      <c r="G109" s="2" t="inlineStr"/>
       <c r="H109" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
@@ -6332,12 +6328,12 @@
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/orinal-infantil-praktiplas-pinguino</t>
+          <t>https://www.solobabys.com/products/tetero-only-8-onzas-a2dj</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_51.webp?v=1779814860</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_88.webp?v=1780097838</t>
         </is>
       </c>
       <c r="L109" s="2" t="n">
@@ -6351,11 +6347,11 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>10649149767990</v>
+        <v>10651909718326</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Bolsas de almacenamiento de leche materna | ONBY-1</t>
+          <t>Orinal infantil Praktiplas Pingüino</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -6365,18 +6361,22 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Recién nacido, Lactancia, Baby shower</t>
+          <t>Bacinillas, Más vendidos</t>
         </is>
       </c>
       <c r="E110" s="3" t="n">
-        <v>18000</v>
+        <v>19000</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>25714</v>
-      </c>
-      <c r="G110" s="2" t="inlineStr"/>
+        <v>27143</v>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Aguamarina', 'Negro']</t>
+        </is>
+      </c>
       <c r="H110" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
@@ -6385,16 +6385,16 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/bolsas-de-almacenamiento-de-leche-materna-250-ml-x-30-unidades</t>
+          <t>https://www.solobabys.com/products/orinal-infantil-praktiplas-pinguino</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_-_2026-06-02T205506.029.webp?v=1780451739</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_51.webp?v=1779814860</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
@@ -6404,11 +6404,11 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>10642865127734</v>
+        <v>10649149767990</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Tetero Only Baby Natural 9oz / 260ml | Alimentación para Bebé</t>
+          <t>Bolsas de almacenamiento de leche materna | ONBY-1</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -6418,22 +6418,18 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Teteros, Baby shower, Más vendidos</t>
+          <t>Recién nacido, Lactancia, Baby shower</t>
         </is>
       </c>
       <c r="E111" s="3" t="n">
-        <v>17500</v>
+        <v>18000</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>22600</v>
-      </c>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Rosa', 'Azul', 'Transparente']</t>
-        </is>
-      </c>
+        <v>25714</v>
+      </c>
+      <c r="G111" s="2" t="inlineStr"/>
       <c r="H111" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
@@ -6442,12 +6438,12 @@
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/tetero-only-baby-natural-8oz-260ml-alimentacion-para-bebe</t>
+          <t>https://www.solobabys.com/products/bolsas-de-almacenamiento-de-leche-materna-250-ml-x-30-unidades</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_74.webp?v=1779927570</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_-_2026-06-02T205506.029.webp?v=1780451739</t>
         </is>
       </c>
       <c r="L111" s="2" t="n">
@@ -6461,11 +6457,11 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>10727775371574</v>
+        <v>10642865127734</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Cepillo Lava Tetero Only Baby A-71</t>
+          <t>Tetero Only Baby Natural 9oz / 260ml | Alimentación para Bebé</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -6475,20 +6471,22 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Teteros</t>
+          <t>Teteros, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E112" s="3" t="n">
         <v>17500</v>
       </c>
-      <c r="F112" s="3" t="n"/>
+      <c r="F112" s="3" t="n">
+        <v>22600</v>
+      </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Color: ['Azul', 'Rosa']</t>
+          <t>Color: ['Rosa', 'Azul', 'Transparente']</t>
         </is>
       </c>
       <c r="H112" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
@@ -6497,12 +6495,12 @@
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/cepillo-lava-tetero-only-baby-a-71</t>
+          <t>https://www.solobabys.com/products/tetero-only-baby-natural-8oz-260ml-alimentacion-para-bebe</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_71.webp?v=1779925711</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_74.webp?v=1779927570</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
@@ -6516,11 +6514,11 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>10642845761846</v>
+        <v>10727775371574</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Tetero Only Baby Natural 4oz / 125ml | Anticólicos con Asas</t>
+          <t>Cepillo Lava Tetero Only Baby A-71</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -6530,22 +6528,20 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Teteros, Baby shower, Más vendidos</t>
+          <t>Teteros</t>
         </is>
       </c>
       <c r="E113" s="3" t="n">
-        <v>17000</v>
-      </c>
-      <c r="F113" s="3" t="n">
-        <v>22000</v>
-      </c>
+        <v>17500</v>
+      </c>
+      <c r="F113" s="3" t="n"/>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Color: ['Rosa', 'Azul', 'Transparente']</t>
+          <t>Color: ['Azul', 'Rosa']</t>
         </is>
       </c>
       <c r="H113" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
@@ -6554,12 +6550,12 @@
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/tetero-only-baby-natural-4oz-125ml-anticolicos-con-asas</t>
+          <t>https://www.solobabys.com/products/cepillo-lava-tetero-only-baby-a-71</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/sbproductos_1_2.webp?v=1774025676</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_71.webp?v=1779925711</t>
         </is>
       </c>
       <c r="L113" s="2" t="n">
@@ -6573,11 +6569,11 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>10643479331126</v>
+        <v>10642845761846</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Copa recolectora de leche materna</t>
+          <t>Tetero Only Baby Natural 4oz / 125ml | Anticólicos con Asas</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -6587,18 +6583,22 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Recién nacido, Lactancia, Más vendidos</t>
+          <t>Teteros, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E114" s="3" t="n">
-        <v>16500</v>
+        <v>17000</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>23571</v>
-      </c>
-      <c r="G114" s="2" t="inlineStr"/>
+        <v>22000</v>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Rosa', 'Azul', 'Transparente']</t>
+        </is>
+      </c>
       <c r="H114" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
@@ -6607,12 +6607,12 @@
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/fular-cole-portabebe-ergonomico</t>
+          <t>https://www.solobabys.com/products/tetero-only-baby-natural-4oz-125ml-anticolicos-con-asas</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla_55.webp?v=1774162492</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/sbproductos_1_2.webp?v=1774025676</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
@@ -6626,11 +6626,11 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>10741795520822</v>
+        <v>10643479331126</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Lima eléctrica para Bebé | V168</t>
+          <t>Copa recolectora de leche materna</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -6640,14 +6640,14 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower, Más vendidos</t>
+          <t>Recién nacido, Lactancia, Más vendidos</t>
         </is>
       </c>
       <c r="E115" s="3" t="n">
-        <v>16000</v>
+        <v>16500</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>22857</v>
+        <v>23571</v>
       </c>
       <c r="G115" s="2" t="inlineStr"/>
       <c r="H115" s="2" t="n">
@@ -6660,12 +6660,12 @@
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/cortaunas-electrico-para-bebe-v168</t>
+          <t>https://www.solobabys.com/products/fular-cole-portabebe-ergonomico</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-09T172638.946.webp?v=1781044015</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla_55.webp?v=1774162492</t>
         </is>
       </c>
       <c r="L115" s="2" t="n">
@@ -6679,11 +6679,11 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>10643571147062</v>
+        <v>10741795520822</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Medias estilo española para bebé</t>
+          <t>Lima eléctrica para Bebé | V168</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -6693,14 +6693,14 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Ropa, Baby shower</t>
+          <t>Aseo y cuidado, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E116" s="3" t="n">
-        <v>14500</v>
+        <v>16000</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>19900</v>
+        <v>22857</v>
       </c>
       <c r="G116" s="2" t="inlineStr"/>
       <c r="H116" s="2" t="n">
@@ -6713,12 +6713,12 @@
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/medias-estilo-espanola-para-bebe</t>
+          <t>https://www.solobabys.com/products/cortaunas-electrico-para-bebe-v168</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_-_2026-08-14T185137.710.webp?v=1786751525</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-09T172638.946.webp?v=1781044015</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
@@ -6732,11 +6732,11 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>10730172449078</v>
+        <v>10643571147062</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Aspirador Nasal Boogy | 20931</t>
+          <t>Medias estilo española para bebé</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -6746,14 +6746,14 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower</t>
+          <t>Ropa, Baby shower</t>
         </is>
       </c>
       <c r="E117" s="3" t="n">
-        <v>14000</v>
+        <v>14500</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>20000</v>
+        <v>19900</v>
       </c>
       <c r="G117" s="2" t="inlineStr"/>
       <c r="H117" s="2" t="n">
@@ -6766,12 +6766,12 @@
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/aspirador-nasal-boogy-20931</t>
+          <t>https://www.solobabys.com/products/medias-estilo-espanola-para-bebe</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_99.webp?v=1780185614</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_-_2026-08-14T185137.710.webp?v=1786751525</t>
         </is>
       </c>
       <c r="L117" s="2" t="n">
@@ -6785,11 +6785,11 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>10650919108918</v>
+        <v>10730172449078</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Crema Protectora Happy Soft 60gr | Cuidado y Protección para Bebé</t>
+          <t>Aspirador Nasal Boogy | 20931</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -6803,10 +6803,10 @@
         </is>
       </c>
       <c r="E118" s="3" t="n">
-        <v>12500</v>
+        <v>14000</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>17857</v>
+        <v>20000</v>
       </c>
       <c r="G118" s="2" t="inlineStr"/>
       <c r="H118" s="2" t="n">
@@ -6819,16 +6819,16 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/crema-protectora-happy-soft-60gr-cuidado-y-proteccion-para-bebe</t>
+          <t>https://www.solobabys.com/products/aspirador-nasal-boogy-20931</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-01T022221.997.webp?v=1780299053</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_99.webp?v=1780185614</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
@@ -6838,11 +6838,11 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>10651924660534</v>
+        <v>10650919108918</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Bacín infantil Praktiplas Rana</t>
+          <t>Crema Protectora Happy Soft 60gr | Cuidado y Protección para Bebé</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -6852,22 +6852,18 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Bacinillas</t>
+          <t>Aseo y cuidado, Baby shower</t>
         </is>
       </c>
       <c r="E119" s="3" t="n">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>17143</v>
-      </c>
-      <c r="G119" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Aguamarina', 'Azul', 'fucsia']</t>
-        </is>
-      </c>
+        <v>17857</v>
+      </c>
+      <c r="G119" s="2" t="inlineStr"/>
       <c r="H119" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
@@ -6876,16 +6872,16 @@
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/bacin-infantil-praktiplas-rana</t>
+          <t>https://www.solobabys.com/products/crema-protectora-happy-soft-60gr-cuidado-y-proteccion-para-bebe</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_44.webp?v=1779577786</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-01T022221.997.webp?v=1780299053</t>
         </is>
       </c>
       <c r="L119" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
@@ -6895,11 +6891,11 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>10762017669430</v>
+        <v>10651924660534</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Mordedor Control Silicona para Bebé</t>
+          <t>Bacín infantil Praktiplas Rana</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -6909,18 +6905,22 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Baby shower, Más vendidos</t>
+          <t>Bacinillas</t>
         </is>
       </c>
       <c r="E120" s="3" t="n">
-        <v>11000</v>
+        <v>12000</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>15714</v>
-      </c>
-      <c r="G120" s="2" t="inlineStr"/>
+        <v>17143</v>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Aguamarina', 'Azul', 'fucsia']</t>
+        </is>
+      </c>
       <c r="H120" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
@@ -6929,30 +6929,30 @@
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/mordedor-control-silicona-para-bebe</t>
+          <t>https://www.solobabys.com/products/bacin-infantil-praktiplas-rana</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage1jul2026_12_40_34p.m.webp?v=1782927688</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_44.webp?v=1779577786</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>```html @import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color</t>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>10736632987958</v>
+        <v>10762017669430</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Mordedor Only Baby Dino</t>
+          <t>Mordedor Control Silicona para Bebé</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Baby shower</t>
+          <t>Juguetes, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E121" s="3" t="n">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/mordedor-only-baby-dino</t>
+          <t>https://www.solobabys.com/products/mordedor-control-silicona-para-bebe</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-05T183301.061.webp?v=1780702402</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage1jul2026_12_40_34p.m.webp?v=1782927688</t>
         </is>
       </c>
       <c r="L121" s="2" t="n">
@@ -6995,17 +6995,17 @@
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
+          <t>```html @import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>10652006547766</v>
+        <v>10736632987958</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Rascaencias Figuras AB-27 | Alivio para la Dentición del Bebé</t>
+          <t>Mordedor Only Baby Dino</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -7035,16 +7035,16 @@
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/rascaencias-figuras-ab-27-alivio-para-la-denticion-del-bebe</t>
+          <t>https://www.solobabys.com/products/mordedor-only-baby-dino</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/D_NQ_NP_900595-MLA91560968768_092025-O_EmbellecedordeProducto.webp?v=1775076453</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-05T183301.061.webp?v=1780702402</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
@@ -7054,11 +7054,11 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>10642154062134</v>
+        <v>10652006547766</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Tetero Only Baby Natural 2oz / 60ml | Alimentación para Bebé</t>
+          <t>Rascaencias Figuras AB-27 | Alivio para la Dentición del Bebé</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -7068,22 +7068,18 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Teteros, Baby shower</t>
+          <t>Juguetes, Baby shower</t>
         </is>
       </c>
       <c r="E123" s="3" t="n">
-        <v>10500</v>
+        <v>11000</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>13600</v>
-      </c>
-      <c r="G123" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Azul', 'Rosa', 'Transparente']</t>
-        </is>
-      </c>
+        <v>15714</v>
+      </c>
+      <c r="G123" s="2" t="inlineStr"/>
       <c r="H123" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
@@ -7092,30 +7088,30 @@
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/tetero-only-baby-natural-2oz-60ml-alimentacion-para-bebe</t>
+          <t>https://www.solobabys.com/products/rascaencias-figuras-ab-27-alivio-para-la-denticion-del-bebe</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_Image_5_may_2026_10_26_07_a.m..webp?v=1777995497</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/D_NQ_NP_900595-MLA91560968768_092025-O_EmbellecedordeProducto.webp?v=1775076453</t>
         </is>
       </c>
       <c r="L123" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #ffb80</t>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>10642902548790</v>
+        <v>10642154062134</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Guante Mordedor para Bebé | Alivio para Encías</t>
+          <t>Tetero Only Baby Natural 2oz / 60ml | Alimentación para Bebé</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -7125,18 +7121,18 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Accesorios, Baby shower, Más vendidos</t>
+          <t>Teteros, Baby shower</t>
         </is>
       </c>
       <c r="E124" s="3" t="n">
         <v>10500</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>15000</v>
+        <v>13600</v>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Color: ['Rosa', 'Azul', 'Verde']</t>
+          <t>Color: ['Azul', 'Rosa', 'Transparente']</t>
         </is>
       </c>
       <c r="H124" s="2" t="n">
@@ -7149,30 +7145,30 @@
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/guante-mordedor-para-bebe-alivio-para-encias</t>
+          <t>https://www.solobabys.com/products/tetero-only-baby-natural-2oz-60ml-alimentacion-para-bebe</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_64.webp?v=1779828393</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_Image_5_may_2026_10_26_07_a.m..webp?v=1777995497</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #ffb80</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>10643478675766</v>
+        <v>10642902548790</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Pañitos Happy y Soft x100 | Limpieza Suave para Bebé</t>
+          <t>Guante Mordedor para Bebé | Alivio para Encías</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -7182,18 +7178,22 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower</t>
+          <t>Juguetes, Accesorios, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E125" s="3" t="n">
-        <v>10400</v>
+        <v>10500</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>14857</v>
-      </c>
-      <c r="G125" s="2" t="inlineStr"/>
+        <v>15000</v>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Rosa', 'Azul', 'Verde']</t>
+        </is>
+      </c>
       <c r="H125" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
@@ -7202,16 +7202,16 @@
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/panitos-happy-y-soft-x100-limpieza-suave-para-bebe</t>
+          <t>https://www.solobabys.com/products/guante-mordedor-para-bebe-alivio-para-encias</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/55.webp?v=1774123726</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_64.webp?v=1779828393</t>
         </is>
       </c>
       <c r="L125" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
@@ -7221,11 +7221,11 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>10651904344374</v>
+        <v>10643478675766</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Rascaencias Jirafa LW3 | Alivio para la Dentición del Bebé</t>
+          <t>Pañitos Happy y Soft x100 | Limpieza Suave para Bebé</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -7235,22 +7235,18 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Accesorios, Baby shower</t>
+          <t>Aseo y cuidado, Baby shower</t>
         </is>
       </c>
       <c r="E126" s="3" t="n">
-        <v>10000</v>
+        <v>10400</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>14000</v>
-      </c>
-      <c r="G126" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Amarillo', 'Rosa', 'Verde']</t>
-        </is>
-      </c>
+        <v>14857</v>
+      </c>
+      <c r="G126" s="2" t="inlineStr"/>
       <c r="H126" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
@@ -7259,16 +7255,16 @@
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/rascaencias-jirafa-lw3-alivio-para-la-denticion-del-bebe</t>
+          <t>https://www.solobabys.com/products/panitos-happy-y-soft-x100-limpieza-suave-para-bebe</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/1740126304665_1.webp?v=1775065667</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/55.webp?v=1774123726</t>
         </is>
       </c>
       <c r="L126" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
@@ -7278,11 +7274,11 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>10762342793526</v>
+        <v>10651904344374</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Babero Siliconado Ajustable</t>
+          <t>Rascaencias Jirafa LW3 | Alivio para la Dentición del Bebé</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -7292,18 +7288,22 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Alimentación, Baby shower</t>
+          <t>Juguetes, Accesorios, Baby shower</t>
         </is>
       </c>
       <c r="E127" s="3" t="n">
         <v>10000</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>14286</v>
-      </c>
-      <c r="G127" s="2" t="inlineStr"/>
+        <v>14000</v>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Amarillo', 'Rosa', 'Verde']</t>
+        </is>
+      </c>
       <c r="H127" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
@@ -7312,16 +7312,16 @@
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/babero-siliconado-ajustable</t>
+          <t>https://www.solobabys.com/products/rascaencias-jirafa-lw3-alivio-para-la-denticion-del-bebe</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage1jul2026_10_45_36p.m.webp?v=1782964027</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/1740126304665_1.webp?v=1775065667</t>
         </is>
       </c>
       <c r="L127" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
@@ -7331,11 +7331,11 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>10762507878710</v>
+        <v>10762342793526</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Mordedor Control Only Baby</t>
+          <t>Babero Siliconado Ajustable</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -7345,14 +7345,14 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Baby shower, Más vendidos</t>
+          <t>Alimentación, Baby shower</t>
         </is>
       </c>
       <c r="E128" s="3" t="n">
-        <v>9900</v>
+        <v>10000</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>14143</v>
+        <v>14286</v>
       </c>
       <c r="G128" s="2" t="inlineStr"/>
       <c r="H128" s="2" t="n">
@@ -7365,16 +7365,16 @@
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/mordedor-control-only-baby</t>
+          <t>https://www.solobabys.com/products/babero-siliconado-ajustable</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage2jul2026_07_10_28a.m.webp?v=1782994278</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage1jul2026_10_45_36p.m.webp?v=1782964027</t>
         </is>
       </c>
       <c r="L128" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
@@ -7384,11 +7384,11 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>10742260891958</v>
+        <v>10762507878710</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>CHUPA FRUTA ONLY BABY | C-40</t>
+          <t>Mordedor Control Only Baby</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -7398,14 +7398,14 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Alimentación, Más vendidos</t>
+          <t>Juguetes, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E129" s="3" t="n">
-        <v>9000</v>
+        <v>9900</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>12857</v>
+        <v>14143</v>
       </c>
       <c r="G129" s="2" t="inlineStr"/>
       <c r="H129" s="2" t="n">
@@ -7418,16 +7418,16 @@
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/chupa-fruta-only-baby-c-40</t>
+          <t>https://www.solobabys.com/products/mordedor-control-only-baby</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-09T215325.108.webp?v=1781060037</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage2jul2026_07_10_28a.m.webp?v=1782994278</t>
         </is>
       </c>
       <c r="L129" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
@@ -7437,11 +7437,11 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>10762510303542</v>
+        <v>10742260891958</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Termómetro Digital Infantil</t>
+          <t>CHUPA FRUTA ONLY BABY | C-40</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -7451,14 +7451,14 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower, Más vendidos</t>
+          <t>Alimentación, Más vendidos</t>
         </is>
       </c>
       <c r="E130" s="3" t="n">
-        <v>8500</v>
+        <v>9000</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>12143</v>
+        <v>12857</v>
       </c>
       <c r="G130" s="2" t="inlineStr"/>
       <c r="H130" s="2" t="n">
@@ -7471,16 +7471,16 @@
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/termometro-digital-infantil</t>
+          <t>https://www.solobabys.com/products/chupa-fruta-only-baby-c-40</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage2jul2026_07_22_20a.m.webp?v=1782994980</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-09T215325.108.webp?v=1781060037</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
@@ -7490,11 +7490,11 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>10642922602806</v>
+        <v>10762510303542</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Vajilla Love With para Bebé | 939BB</t>
+          <t>Termómetro Digital Infantil</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -7504,22 +7504,18 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Alimentación, Baby shower</t>
+          <t>Aseo y cuidado, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E131" s="3" t="n">
-        <v>7500</v>
+        <v>8500</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>9000</v>
-      </c>
-      <c r="G131" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Verde', 'Naranja', 'Azul', 'Aguamarina']</t>
-        </is>
-      </c>
+        <v>12143</v>
+      </c>
+      <c r="G131" s="2" t="inlineStr"/>
       <c r="H131" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
@@ -7528,12 +7524,12 @@
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/vajilla-love-with-para-bebe-plato-infantil-con-diseno-divertido</t>
+          <t>https://www.solobabys.com/products/termometro-digital-infantil</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/39.webp?v=1774040907</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage2jul2026_07_22_20a.m.webp?v=1782994980</t>
         </is>
       </c>
       <c r="L131" s="2" t="n">
@@ -7547,11 +7543,11 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>10726877331766</v>
+        <v>10642922602806</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Cepillo Dental Siliconado 360° para Bebés</t>
+          <t>Vajilla Love With para Bebé | 939BB</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -7561,16 +7557,22 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Más vendidos</t>
+          <t>Alimentación, Baby shower</t>
         </is>
       </c>
       <c r="E132" s="3" t="n">
         <v>7500</v>
       </c>
-      <c r="F132" s="3" t="n"/>
-      <c r="G132" s="2" t="inlineStr"/>
+      <c r="F132" s="3" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Verde', 'Naranja', 'Azul', 'Aguamarina']</t>
+        </is>
+      </c>
       <c r="H132" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
@@ -7579,16 +7581,16 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/cepillo-dental-siliconado-360-para-bebes</t>
+          <t>https://www.solobabys.com/products/vajilla-love-with-para-bebe-plato-infantil-con-diseno-divertido</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_62.webp?v=1779825817</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/39.webp?v=1774040907</t>
         </is>
       </c>
       <c r="L132" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
@@ -7598,11 +7600,11 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>10643440664886</v>
+        <v>10726877331766</v>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Aspirador Nasal Only Baby | HENFZ11</t>
+          <t>Cepillo Dental Siliconado 360° para Bebés</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -7612,22 +7614,16 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower</t>
+          <t>Aseo y cuidado, Más vendidos</t>
         </is>
       </c>
       <c r="E133" s="3" t="n">
-        <v>6500</v>
-      </c>
-      <c r="F133" s="3" t="n">
-        <v>7000</v>
-      </c>
-      <c r="G133" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Azul', 'Rosa']</t>
-        </is>
-      </c>
+        <v>7500</v>
+      </c>
+      <c r="F133" s="3" t="n"/>
+      <c r="G133" s="2" t="inlineStr"/>
       <c r="H133" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
@@ -7636,16 +7632,16 @@
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/aspirador-nasal-only-baby-limpieza-suave-para-bebe</t>
+          <t>https://www.solobabys.com/products/cepillo-dental-siliconado-360-para-bebes</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/aspirador-nasal-azul-para-bebe.webp?v=1774108168</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_62.webp?v=1779825817</t>
         </is>
       </c>
       <c r="L133" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
@@ -7655,11 +7651,11 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>10728210792758</v>
+        <v>10643440664886</v>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Set Manicure Bebé | JJ250347</t>
+          <t>Aspirador Nasal Only Baby | HENFZ11</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -7669,18 +7665,22 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado</t>
+          <t>Aseo y cuidado, Baby shower</t>
         </is>
       </c>
       <c r="E134" s="3" t="n">
         <v>6500</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>9286</v>
-      </c>
-      <c r="G134" s="2" t="inlineStr"/>
+        <v>7000</v>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Azul', 'Rosa']</t>
+        </is>
+      </c>
       <c r="H134" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
@@ -7689,16 +7689,16 @@
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/set-manicure-bebe-jj250347</t>
+          <t>https://www.solobabys.com/products/aspirador-nasal-only-baby-limpieza-suave-para-bebe</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_81.webp?v=1780001979</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/aspirador-nasal-azul-para-bebe.webp?v=1774108168</t>
         </is>
       </c>
       <c r="L134" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
@@ -7708,11 +7708,11 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>10743245766966</v>
+        <v>10728210792758</v>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Cepillo Lengua Only Baby | FZ-121</t>
+          <t>Set Manicure Bebé | JJ250347</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -7722,14 +7722,14 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower, Más vendidos</t>
+          <t>Aseo y cuidado</t>
         </is>
       </c>
       <c r="E135" s="3" t="n">
-        <v>6000</v>
+        <v>6500</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>8571</v>
+        <v>9286</v>
       </c>
       <c r="G135" s="2" t="inlineStr"/>
       <c r="H135" s="2" t="n">
@@ -7742,16 +7742,16 @@
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/cepillo-lengua-only-baby-fz-121</t>
+          <t>https://www.solobabys.com/products/set-manicure-bebe-jj250347</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-10T193401.800.webp?v=1781138064</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_81.webp?v=1780001979</t>
         </is>
       </c>
       <c r="L135" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
@@ -7761,11 +7761,11 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>10643473727798</v>
+        <v>10743245766966</v>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Pañitos Happy y Soft x40 | Limpieza Suave para Bebé</t>
+          <t>Cepillo Lengua Only Baby | FZ-121</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -7775,14 +7775,14 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower</t>
+          <t>Aseo y cuidado, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E136" s="3" t="n">
-        <v>4700</v>
+        <v>6000</v>
       </c>
       <c r="F136" s="3" t="n">
-        <v>6714</v>
+        <v>8571</v>
       </c>
       <c r="G136" s="2" t="inlineStr"/>
       <c r="H136" s="2" t="n">
@@ -7795,25 +7795,78 @@
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
+          <t>https://www.solobabys.com/products/cepillo-lengua-only-baby-fz-121</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-10T193401.800.webp?v=1781138064</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>10643473727798</v>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>Pañitos Happy y Soft x40 | Limpieza Suave para Bebé</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Sin categoría</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Aseo y cuidado, Baby shower</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="n">
+        <v>4700</v>
+      </c>
+      <c r="F137" s="3" t="n">
+        <v>6714</v>
+      </c>
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
           <t>https://www.solobabys.com/products/panitos-happy-y-soft-x40-limpieza-suave-para-bebe</t>
         </is>
       </c>
-      <c r="K136" s="2" t="inlineStr">
+      <c r="K137" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/53.webp?v=1774121918</t>
         </is>
       </c>
-      <c r="L136" s="2" t="n">
+      <c r="L137" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M136" s="2" t="inlineStr">
+      <c r="M137" s="2" t="inlineStr">
         <is>
           <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M136"/>
+  <autoFilter ref="A1:M137"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7859,7 +7912,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C3" s="5" t="n"/>
       <c r="D3" s="5" t="n"/>
@@ -7871,7 +7924,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5">
@@ -7882,7 +7935,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-15 06:34</t>
+          <t>2026-10-15 12:35</t>
         </is>
       </c>
     </row>
@@ -7963,7 +8016,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7935,7 +7935,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-15 12:35</t>
+          <t>2026-10-15 18:30</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7935,7 +7935,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-15 18:30</t>
+          <t>2026-10-16 00:33</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7935,7 +7935,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-16 00:33</t>
+          <t>2026-10-16 06:33</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7935,7 +7935,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-16 06:33</t>
+          <t>2026-10-16 12:34</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7935,7 +7935,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-16 12:34</t>
+          <t>2026-10-16 18:28</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7935,7 +7935,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-16 18:28</t>
+          <t>2026-10-17 00:33</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7935,7 +7935,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-17 00:33</t>
+          <t>2026-10-17 06:29</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7935,7 +7935,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-17 06:29</t>
+          <t>2026-10-17 12:27</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7935,7 +7935,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-17 12:27</t>
+          <t>2026-10-17 18:24</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7935,7 +7935,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-17 18:24</t>
+          <t>2026-10-18 00:33</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7935,7 +7935,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-18 00:33</t>
+          <t>2026-10-18 06:29</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7935,7 +7935,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-18 06:29</t>
+          <t>2026-10-18 12:27</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7935,7 +7935,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-18 12:27</t>
+          <t>2026-10-18 18:24</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7935,7 +7935,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-18 18:24</t>
+          <t>2026-10-19 00:34</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7935,7 +7935,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-19 00:34</t>
+          <t>2026-10-19 06:39</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7935,7 +7935,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-19 06:39</t>
+          <t>2026-10-19 12:37</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7935,7 +7935,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-19 12:37</t>
+          <t>2026-10-19 18:30</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7935,7 +7935,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-19 18:30</t>
+          <t>2026-10-20 00:36</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7935,7 +7935,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20 00:36</t>
+          <t>2026-10-20 07:00</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7935,7 +7935,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20 07:00</t>
+          <t>2026-10-20 12:34</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7935,7 +7935,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20 12:34</t>
+          <t>2026-10-20 18:31</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7935,7 +7935,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20 18:31</t>
+          <t>2026-10-21 00:34</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7935,7 +7935,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-21 00:34</t>
+          <t>2026-10-21 06:35</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$M$137</definedName>
@@ -7935,7 +7935,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-21 06:35</t>
+          <t>2026-10-21 01:57</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7935,7 +7935,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-21 01:57</t>
+          <t>2026-10-21 02:48</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7935,7 +7935,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-21 02:48</t>
+          <t>2026-10-21 03:31</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7935,7 +7935,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-21 03:31</t>
+          <t>2026-10-21 04:22</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$M$137</definedName>
@@ -7935,7 +7935,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-21 04:22</t>
+          <t>2026-10-21 12:35</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$M$137</definedName>
@@ -7935,7 +7935,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-21 12:35</t>
+          <t>2026-10-21 08:02</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$M$137</definedName>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -7924,7 +7924,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5">
@@ -7935,7 +7935,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-21 08:02</t>
+          <t>2026-10-21 18:30</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -1376,9 +1376,7 @@
       <c r="E17" s="3" t="n">
         <v>145900</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>208000</v>
-      </c>
+      <c r="F17" s="3" t="n"/>
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="n">
         <v>1</v>
@@ -2505,9 +2503,7 @@
       <c r="E38" s="3" t="n">
         <v>86000</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>122857</v>
-      </c>
+      <c r="F38" s="3" t="n"/>
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="n">
         <v>1</v>
@@ -3628,9 +3624,7 @@
       <c r="E59" s="3" t="n">
         <v>56000</v>
       </c>
-      <c r="F59" s="3" t="n">
-        <v>63000</v>
-      </c>
+      <c r="F59" s="3" t="n"/>
       <c r="G59" s="2" t="inlineStr"/>
       <c r="H59" s="2" t="n">
         <v>1</v>
@@ -3893,9 +3887,7 @@
       <c r="E64" s="3" t="n">
         <v>50000</v>
       </c>
-      <c r="F64" s="3" t="n">
-        <v>71000</v>
-      </c>
+      <c r="F64" s="3" t="n"/>
       <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="n">
         <v>1</v>
@@ -4060,9 +4052,7 @@
       <c r="E67" s="3" t="n">
         <v>49900</v>
       </c>
-      <c r="F67" s="3" t="n">
-        <v>70000</v>
-      </c>
+      <c r="F67" s="3" t="n"/>
       <c r="G67" s="2" t="inlineStr"/>
       <c r="H67" s="2" t="n">
         <v>1</v>
@@ -4537,9 +4527,7 @@
       <c r="E76" s="3" t="n">
         <v>45000</v>
       </c>
-      <c r="F76" s="3" t="n">
-        <v>64000</v>
-      </c>
+      <c r="F76" s="3" t="n"/>
       <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="2" t="n">
         <v>1</v>
@@ -7935,7 +7923,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-21 18:30</t>
+          <t>2026-10-22 00:35</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7923,7 +7923,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-22 00:35</t>
+          <t>2026-10-22 06:35</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7923,7 +7923,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-22 06:35</t>
+          <t>2026-10-22 12:36</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -1320,7 +1320,7 @@
         <v>152000</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>217143</v>
+        <v>249900</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-22 12:36</t>
+          <t>2026-10-22 18:30</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7923,7 +7923,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-22 18:30</t>
+          <t>2026-10-23 00:37</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7923,7 +7923,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-23 00:37</t>
+          <t>2026-10-23 06:34</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7923,7 +7923,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-23 06:34</t>
+          <t>2026-10-23 12:32</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7923,7 +7923,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-23 12:32</t>
+          <t>2026-10-23 18:30</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -3237,11 +3237,11 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>10817874559286</v>
+        <v>10812588589366</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Bañera para Bebé con Soporte Anatómico</t>
+          <t>Abejita Bailarina Dancing Bee</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3251,14 +3251,14 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower</t>
+          <t>Juguetes, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>62000</v>
+        <v>63000</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>88571</v>
+        <v>90000</v>
       </c>
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="n">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/banera-para-bebe-con-soporte-anatomico</t>
+          <t>https://www.solobabys.com/products/abejita-bailarina-dancing-bee</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-08-19T190108.179.webp?v=1787184104</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsApp_32.webp?v=1786662172</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
@@ -3290,11 +3290,11 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>10643571212598</v>
+        <v>10817874559286</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Pack x12 de medias con sonajero para bebé</t>
+          <t>Bañera para Bebé con Soporte Anatómico</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3304,14 +3304,14 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Ropa, Baby shower</t>
+          <t>Aseo y cuidado, Baby shower</t>
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>60000</v>
+        <v>62000</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>85714</v>
+        <v>88571</v>
       </c>
       <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="2" t="n">
@@ -3324,16 +3324,16 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/pack-de-medias-con-sonajero-para-bebe</t>
+          <t>https://www.solobabys.com/products/banera-para-bebe-con-soporte-anatomico</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla_91.webp?v=1774567784</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-08-19T190108.179.webp?v=1787184104</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
@@ -3343,11 +3343,11 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>10643570426166</v>
+        <v>10643571212598</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Media Tejido BB MX3-627</t>
+          <t>Pack x12 de medias con sonajero para bebé</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3357,14 +3357,14 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Ropa, Baby shower</t>
         </is>
       </c>
       <c r="E54" s="3" t="n">
         <v>60000</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>29900</v>
+        <v>85714</v>
       </c>
       <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="n">
@@ -3377,30 +3377,30 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/media-tejido-bb-mx3-627</t>
+          <t>https://www.solobabys.com/products/pack-de-medias-con-sonajero-para-bebe</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsApp_Image_2026-03-21_at_6.55.04_PM_1.jpg?v=1774564952</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla_91.webp?v=1774567784</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container{ font-family:'Quicksand',sans-serif; max-width:480px; margin:0 auto; color:#4a5568; padding:26px; background:#ffffff; } .b-rating{ display:flex; align-items:center; gap:8px; margin-bottom:12px; font-size:14px; font-weight:700; color:#c8d431; flex-wrap:wra</t>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>15407949349174</v>
+        <v>10643570426166</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Combo Lactancia Materna Only Baby</t>
+          <t>Media Tejido BB MX3-627</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3410,13 +3410,15 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Teteros, Alimentación, Combos</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>59900</v>
-      </c>
-      <c r="F55" s="3" t="n"/>
+        <v>60000</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>29900</v>
+      </c>
       <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="n">
         <v>1</v>
@@ -3428,30 +3430,30 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/combo-lactancia-materna-only-baby</t>
+          <t>https://www.solobabys.com/products/media-tejido-bb-mx3-627</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-10-01at11.33.07AM.webp?v=1791314681</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsApp_Image_2026-03-21_at_6.55.04_PM_1.jpg?v=1774564952</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container{ font-family:'Quicksand',sans-serif; max-width:480px; margin:0 auto; color:#4a5568; padding:26px; background:#ffffff; } .b-rating{ display:flex; align-items:center; gap:8px; margin-bottom:12px; font-size:14px; font-weight:700; color:#c8d431; flex-wrap:wra</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>10813212197174</v>
+        <v>15407949349174</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>COBIJA BURBUJA ESTAMPADA Y ALMOHADAS</t>
+          <t>Combo Lactancia Materna Only Baby</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3461,11 +3463,11 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Cobijas y toallas, Baby shower, Más vendidos</t>
+          <t>Teteros, Alimentación, Combos</t>
         </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v>59000</v>
+        <v>59900</v>
       </c>
       <c r="F56" s="3" t="n"/>
       <c r="G56" s="2" t="inlineStr"/>
@@ -3479,16 +3481,16 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/cobija-burbuja-stpada-y-almohadas</t>
+          <t>https://www.solobabys.com/products/combo-lactancia-materna-only-baby</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-08-14T175108.874.webp?v=1786747890</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-10-01at11.33.07AM.webp?v=1791314681</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
@@ -3498,11 +3500,11 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>15397792940342</v>
+        <v>10813212197174</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Elefante Musical con Luces y Pelotas Flotantes</t>
+          <t>COBIJA BURBUJA ESTAMPADA Y ALMOHADAS</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3512,15 +3514,13 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Juguetes</t>
+          <t>Cobijas y toallas, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>58900</v>
-      </c>
-      <c r="F57" s="3" t="n">
-        <v>84000</v>
-      </c>
+        <v>59000</v>
+      </c>
+      <c r="F57" s="3" t="n"/>
       <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="2" t="n">
         <v>1</v>
@@ -3532,16 +3532,16 @@
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/elefante-musical-con-luces-y-pelotas-flotantes</t>
+          <t>https://www.solobabys.com/products/cobija-burbuja-stpada-y-almohadas</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-26at5.27.17PM.webp?v=1790596404</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-08-14T175108.874.webp?v=1786747890</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
@@ -3551,11 +3551,11 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>10871389880630</v>
+        <v>15397792940342</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Piano Didáctico Mariposa con Luces y Sonidos</t>
+          <t>Elefante Musical con Luces y Pelotas Flotantes</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="E58" s="3" t="n">
-        <v>56000</v>
+        <v>58900</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>80000</v>
+        <v>84000</v>
       </c>
       <c r="G58" s="2" t="inlineStr"/>
       <c r="H58" s="2" t="n">
@@ -3585,16 +3585,16 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/piano-didactico-mariposa-con-luces-y-sonidos</t>
+          <t>https://www.solobabys.com/products/elefante-musical-con-luces-y-pelotas-flotantes</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-24at5.47.49PM.webp?v=1790363588</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-26at5.27.17PM.webp?v=1790596404</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
@@ -3604,11 +3604,11 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>10746777862454</v>
+        <v>10871389880630</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Combo Protección y Seguridad para Bebé</t>
+          <t>Piano Didáctico Mariposa con Luces y Sonidos</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3618,34 +3618,36 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Accesorios, Combos, Baby shower, Más vendidos</t>
+          <t>Juguetes</t>
         </is>
       </c>
       <c r="E59" s="3" t="n">
         <v>56000</v>
       </c>
-      <c r="F59" s="3" t="n"/>
+      <c r="F59" s="3" t="n">
+        <v>80000</v>
+      </c>
       <c r="G59" s="2" t="inlineStr"/>
       <c r="H59" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/combo-proteccion-y-seguridad-para-bebe</t>
+          <t>https://www.solobabys.com/products/piano-didactico-mariposa-con-luces-y-sonidos</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/9943c8dc-e899-4b4f-9743-01890aeaf845.webp?v=1781635738</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-24at5.47.49PM.webp?v=1790363588</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
@@ -3655,11 +3657,11 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>10730141974838</v>
+        <v>10746777862454</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Tetero Only 11 Onzas | A1DJ</t>
+          <t>Combo Protección y Seguridad para Bebé</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3669,36 +3671,34 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Teteros</t>
+          <t>Accesorios, Combos, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>55000</v>
-      </c>
-      <c r="F60" s="3" t="n">
-        <v>40000</v>
-      </c>
+        <v>56000</v>
+      </c>
+      <c r="F60" s="3" t="n"/>
       <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/tetero-only-11-onzas-a1dj</t>
+          <t>https://www.solobabys.com/products/combo-proteccion-y-seguridad-para-bebe</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_93.webp?v=1780178551</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/9943c8dc-e899-4b4f-9743-01890aeaf845.webp?v=1781635738</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
@@ -3708,11 +3708,11 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>10762038378806</v>
+        <v>10730141974838</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Vajilla en Silicona para Bebé</t>
+          <t>Tetero Only 11 Onzas | A1DJ</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3722,14 +3722,14 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Alimentación, Baby shower, Más vendidos</t>
+          <t>Teteros</t>
         </is>
       </c>
       <c r="E61" s="3" t="n">
         <v>55000</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>78571</v>
+        <v>40000</v>
       </c>
       <c r="G61" s="2" t="inlineStr"/>
       <c r="H61" s="2" t="n">
@@ -3742,30 +3742,30 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/vajilla-en-silicona-para-bebe</t>
+          <t>https://www.solobabys.com/products/tetero-only-11-onzas-a1dj</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage1jul2026_01_13_14p.m.webp?v=1782929663</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_93.webp?v=1780178551</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>```html @import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color</t>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>15397818728758</v>
+        <v>10762038378806</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Delfín Musical con Pelota Flotante</t>
+          <t>Vajilla en Silicona para Bebé</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3775,14 +3775,14 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Juguetes</t>
+          <t>Alimentación, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E62" s="3" t="n">
-        <v>54000</v>
+        <v>55000</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>77000</v>
+        <v>78571</v>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="n">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/delfin-musical-con-pelota-flotante</t>
+          <t>https://www.solobabys.com/products/vajilla-en-silicona-para-bebe</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-26at5.11.21PM_1.webp?v=1790597093</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage1jul2026_01_13_14p.m.webp?v=1782929663</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
@@ -3808,17 +3808,17 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
+          <t>```html @import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>10800174727478</v>
+        <v>15397818728758</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>BACIN PRAKTIPLAS TRONO</t>
+          <t>Delfín Musical con Pelota Flotante</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3828,14 +3828,14 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Bacinillas, Más vendidos</t>
+          <t>Juguetes</t>
         </is>
       </c>
       <c r="E63" s="3" t="n">
-        <v>50500</v>
+        <v>54000</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>72143</v>
+        <v>77000</v>
       </c>
       <c r="G63" s="2" t="inlineStr"/>
       <c r="H63" s="2" t="n">
@@ -3848,16 +3848,16 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/bacin-praktiplas-trono</t>
+          <t>https://www.solobabys.com/products/delfin-musical-con-pelota-flotante</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-08-05T163918.997.webp?v=1785966083</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-26at5.11.21PM_1.webp?v=1790597093</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
@@ -3867,11 +3867,11 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>15397872009526</v>
+        <v>10800174727478</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Combo Lonchera Infantil + Termo</t>
+          <t>BACIN PRAKTIPLAS TRONO</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3881,13 +3881,15 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Alimentación, Combos</t>
+          <t>Bacinillas, Más vendidos</t>
         </is>
       </c>
       <c r="E64" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="F64" s="3" t="n"/>
+        <v>50500</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>72143</v>
+      </c>
       <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="n">
         <v>1</v>
@@ -3899,16 +3901,16 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/combo-lonchera-infantil-termo</t>
+          <t>https://www.solobabys.com/products/bacin-praktiplas-trono</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ImagendeCodex28sept2026_07_26_32.webp?v=1790598866</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-08-05T163918.997.webp?v=1785966083</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
@@ -3918,11 +3920,11 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>10642848547126</v>
+        <v>15397872009526</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>BACIN PRAKTIPLAS LOCO</t>
+          <t>Combo Lonchera Infantil + Termo</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3932,22 +3934,16 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Bacinillas, Accesorios, Baby shower, Más vendidos</t>
+          <t>Alimentación, Combos</t>
         </is>
       </c>
       <c r="E65" s="3" t="n">
         <v>50000</v>
       </c>
-      <c r="F65" s="3" t="n">
-        <v>67000</v>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Azul', 'Verde', 'Rosa']</t>
-        </is>
-      </c>
+      <c r="F65" s="3" t="n"/>
+      <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
@@ -3956,16 +3952,16 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/bacin-loco-2-en-1-prakti-plas-linea-infantil</t>
+          <t>https://www.solobabys.com/products/combo-lonchera-infantil-termo</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/D_Q_NP_2X_753134-MCO90831803976_082025-P.webp?v=1774026320</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ImagendeCodex28sept2026_07_26_32.webp?v=1790598866</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
@@ -3975,11 +3971,11 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>15404831867190</v>
+        <v>10642848547126</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Set Lavateros + Tetero Only Baby 10 oz</t>
+          <t>BACIN PRAKTIPLAS LOCO</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3989,22 +3985,22 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Teteros, Combos</t>
+          <t>Bacinillas, Accesorios, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E66" s="3" t="n">
-        <v>49900</v>
+        <v>50000</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>71000</v>
+        <v>67000</v>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Color: ['Púrpura', 'Rosa']</t>
+          <t>Color: ['Azul', 'Verde', 'Rosa']</t>
         </is>
       </c>
       <c r="H66" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
@@ -4013,12 +4009,12 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/set-lavateros-tetero-only-baby-10-oz</t>
+          <t>https://www.solobabys.com/products/bacin-loco-2-en-1-prakti-plas-linea-infantil</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-10-01at11.08.04AM.webp?v=1790975971</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/D_Q_NP_2X_753134-MCO90831803976_082025-P.webp?v=1774026320</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
@@ -4032,11 +4028,11 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>15401647800630</v>
+        <v>15404831867190</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Combo Lonchera Completa + Pañitos Húmedos</t>
+          <t>Set Lavateros + Tetero Only Baby 10 oz</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -4046,16 +4042,22 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Alimentación, Combos</t>
+          <t>Teteros, Combos</t>
         </is>
       </c>
       <c r="E67" s="3" t="n">
         <v>49900</v>
       </c>
-      <c r="F67" s="3" t="n"/>
-      <c r="G67" s="2" t="inlineStr"/>
+      <c r="F67" s="3" t="n">
+        <v>71000</v>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Púrpura', 'Rosa']</t>
+        </is>
+      </c>
       <c r="H67" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
@@ -4064,16 +4066,16 @@
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/combo-lonchera-completa-panitos-humedos</t>
+          <t>https://www.solobabys.com/products/set-lavateros-tetero-only-baby-10-oz</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-29at3.06.15PM.webp?v=1790716209</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-10-01at11.08.04AM.webp?v=1790975971</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
@@ -4083,11 +4085,11 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>10812588589366</v>
+        <v>15401647800630</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Abejita Bailarina Dancing Bee</t>
+          <t>Combo Lonchera Completa + Pañitos Húmedos</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -4097,32 +4099,30 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Baby shower, Más vendidos</t>
+          <t>Aseo y cuidado, Alimentación, Combos</t>
         </is>
       </c>
       <c r="E68" s="3" t="n">
         <v>49900</v>
       </c>
-      <c r="F68" s="3" t="n">
-        <v>71286</v>
-      </c>
+      <c r="F68" s="3" t="n"/>
       <c r="G68" s="2" t="inlineStr"/>
       <c r="H68" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/abejita-bailarina-dancing-bee</t>
+          <t>https://www.solobabys.com/products/combo-lonchera-completa-panitos-humedos</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsApp_32.webp?v=1786662172</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-29at3.06.15PM.webp?v=1790716209</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
@@ -7912,7 +7912,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-23 18:30</t>
+          <t>2026-10-24 00:40</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7923,7 +7923,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-24 00:40</t>
+          <t>2026-10-24 06:29</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7923,7 +7923,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-24 06:29</t>
+          <t>2026-10-24 12:28</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$M$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$M$138</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M137"/>
+  <dimension ref="A1:M138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4454,11 +4454,11 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>10819653271862</v>
+        <v>15439275786550</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Camión Transformable en Robot 2 en 1 | Super Change Truck</t>
+          <t>Perrito con Movimiento, Luz y Sonido | Camina Solito</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -4468,14 +4468,14 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Baby shower</t>
+          <t>Juguetes</t>
         </is>
       </c>
       <c r="E75" s="3" t="n">
         <v>46000</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>65714</v>
+        <v>66000</v>
       </c>
       <c r="G75" s="2" t="inlineStr"/>
       <c r="H75" s="2" t="n">
@@ -4488,30 +4488,30 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/camion-transformable-en-robot-2-en-1-super-change-truck</t>
+          <t>https://www.solobabys.com/products/perrito-con-movimiento-luz-y-sonido-camina-solito</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-08-21T172546.714.webp?v=1787351184</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/perrito-luz-sonido-1.jpg?v=1792866073</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-title { font-family: 'Fraunces', serif; font-size: 38px; line-height: 1.1; color: #00afba; margin: 0 0 15px 0; letter-spacin</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>15407841476918</v>
+        <v>10819653271862</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Combo Plato 360° Antiderrames + Babero de Silicona</t>
+          <t>Camión Transformable en Robot 2 en 1 | Super Change Truck</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4521,13 +4521,15 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Alimentación, Combos</t>
+          <t>Juguetes, Baby shower</t>
         </is>
       </c>
       <c r="E76" s="3" t="n">
-        <v>45000</v>
-      </c>
-      <c r="F76" s="3" t="n"/>
+        <v>46000</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>65714</v>
+      </c>
       <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="2" t="n">
         <v>1</v>
@@ -4539,16 +4541,16 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/combo-plato-360-antiderrames-babero-de-silicona</t>
+          <t>https://www.solobabys.com/products/camion-transformable-en-robot-2-en-1-super-change-truck</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-29at3.32.35PM.webp?v=1791307237</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-08-21T172546.714.webp?v=1787351184</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
@@ -4558,11 +4560,11 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>10735539552566</v>
+        <v>15407841476918</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Semanario Mi Ropita 322-002 Sacos</t>
+          <t>Combo Plato 360° Antiderrames + Babero de Silicona</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -4572,11 +4574,11 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Recién nacido, Ropa, Baby shower, Más vendidos</t>
+          <t>Aseo y cuidado, Alimentación, Combos</t>
         </is>
       </c>
       <c r="E77" s="3" t="n">
-        <v>43000</v>
+        <v>45000</v>
       </c>
       <c r="F77" s="3" t="n"/>
       <c r="G77" s="2" t="inlineStr"/>
@@ -4590,16 +4592,16 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/semanario-mi-ropita-322-002-sacos-1</t>
+          <t>https://www.solobabys.com/products/combo-plato-360-antiderrames-babero-de-silicona</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-03T183144.604.webp?v=1780529685</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-29at3.32.35PM.webp?v=1791307237</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
@@ -4609,11 +4611,11 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>10810924826934</v>
+        <v>10735539552566</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Set Toalla con Capucha + 6 Babitas</t>
+          <t>Semanario Mi Ropita 322-002 Sacos</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -4623,15 +4625,13 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Recién nacido, Cobijas y toallas, Baby shower, Más vendidos</t>
+          <t>Recién nacido, Ropa, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E78" s="3" t="n">
-        <v>42000</v>
-      </c>
-      <c r="F78" s="3" t="n">
-        <v>60000</v>
-      </c>
+        <v>43000</v>
+      </c>
+      <c r="F78" s="3" t="n"/>
       <c r="G78" s="2" t="inlineStr"/>
       <c r="H78" s="2" t="n">
         <v>1</v>
@@ -4643,16 +4643,16 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/set-toalla-con-capucha-6-babitas</t>
+          <t>https://www.solobabys.com/products/semanario-mi-ropita-322-002-sacos-1</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-08-11T175525.349.webp?v=1786488969</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-03T183144.604.webp?v=1780529685</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
@@ -4662,11 +4662,11 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>10650947977526</v>
+        <v>10810924826934</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Crema Protectora Happy Soft 500gr | Cuidado y Protección para Bebé</t>
+          <t>Set Toalla con Capucha + 6 Babitas</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -4676,14 +4676,14 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower</t>
+          <t>Recién nacido, Cobijas y toallas, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>40900</v>
+        <v>42000</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>58429</v>
+        <v>60000</v>
       </c>
       <c r="G79" s="2" t="inlineStr"/>
       <c r="H79" s="2" t="n">
@@ -4696,16 +4696,16 @@
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/crema-protectora-happy-soft-500gr-cuidado-y-proteccion-para-bebe</t>
+          <t>https://www.solobabys.com/products/set-toalla-con-capucha-6-babitas</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_100.webp?v=1780298213</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-08-11T175525.349.webp?v=1786488969</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
@@ -4715,11 +4715,11 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>10829223625014</v>
+        <v>10650947977526</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Set de Bloques Didácticos de Construcción 37 Piezas</t>
+          <t>Crema Protectora Happy Soft 500gr | Cuidado y Protección para Bebé</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4729,14 +4729,14 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Juguetes</t>
+          <t>Aseo y cuidado, Baby shower</t>
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>40000</v>
+        <v>40900</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>57143</v>
+        <v>58429</v>
       </c>
       <c r="G80" s="2" t="inlineStr"/>
       <c r="H80" s="2" t="n">
@@ -4749,16 +4749,16 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/set-de-bloques-didacticos-de-construccion-37-piezas</t>
+          <t>https://www.solobabys.com/products/crema-protectora-happy-soft-500gr-cuidado-y-proteccion-para-bebe</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-08-31T182839.165.webp?v=1788218975</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_100.webp?v=1780298213</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
@@ -4768,11 +4768,11 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>10762350395702</v>
+        <v>10829223625014</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Licuadora Portátil Juice Cup</t>
+          <t>Set de Bloques Didácticos de Construcción 37 Piezas</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Alimentación</t>
+          <t>Juguetes</t>
         </is>
       </c>
       <c r="E81" s="3" t="n">
@@ -4802,16 +4802,16 @@
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/licuadora-portatil-juice-cup</t>
+          <t>https://www.solobabys.com/products/set-de-bloques-didacticos-de-construccion-37-piezas</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage1jul2026_11_02_29p.m.webp?v=1782965026</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-08-31T182839.165.webp?v=1788218975</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
@@ -4821,11 +4821,11 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>10651068825910</v>
+        <v>10762350395702</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Extractor manual de leche materna Only Baby</t>
+          <t>Licuadora Portátil Juice Cup</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -4835,22 +4835,18 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Recién nacido, Teteros, Lactancia, Baby shower, Más vendidos</t>
+          <t>Alimentación</t>
         </is>
       </c>
       <c r="E82" s="3" t="n">
-        <v>38500</v>
+        <v>40000</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>55000</v>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Transparente', 'Rosa', 'Verde', 'Azul']</t>
-        </is>
-      </c>
+        <v>57143</v>
+      </c>
+      <c r="G82" s="2" t="inlineStr"/>
       <c r="H82" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
@@ -4859,16 +4855,16 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/extractor-manual-de-leche-materna-only-baby</t>
+          <t>https://www.solobabys.com/products/licuadora-portatil-juice-cup</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla-2026-03-30T174249.061.webp?v=1774910588</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage1jul2026_11_02_29p.m.webp?v=1782965026</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
@@ -4878,11 +4874,11 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>10812587344182</v>
+        <v>10651068825910</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Set de Bloques Didácticos Infantil con Molino y Figuras</t>
+          <t>Extractor manual de leche materna Only Baby</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -4892,18 +4888,22 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Baby shower</t>
+          <t>Recién nacido, Teteros, Lactancia, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E83" s="3" t="n">
-        <v>38000</v>
+        <v>38500</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>54286</v>
-      </c>
-      <c r="G83" s="2" t="inlineStr"/>
+        <v>55000</v>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Transparente', 'Rosa', 'Verde', 'Azul']</t>
+        </is>
+      </c>
       <c r="H83" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
@@ -4912,16 +4912,16 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/set-de-bloques-didacticos-infantil-con-molino-y-figuras</t>
+          <t>https://www.solobabys.com/products/extractor-manual-de-leche-materna-only-baby</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsApp_27.webp?v=1786661794</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla-2026-03-30T174249.061.webp?v=1774910588</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
@@ -4931,11 +4931,11 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>10649160843574</v>
+        <v>10812587344182</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Bacin Prakiplas 7337 Tortuga | 7709412827917</t>
+          <t>Set de Bloques Didácticos Infantil con Molino y Figuras</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -4945,14 +4945,14 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Bacinillas</t>
+          <t>Juguetes, Baby shower</t>
         </is>
       </c>
       <c r="E84" s="3" t="n">
-        <v>37500</v>
+        <v>38000</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>53571</v>
+        <v>54286</v>
       </c>
       <c r="G84" s="2" t="inlineStr"/>
       <c r="H84" s="2" t="n">
@@ -4965,16 +4965,16 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/adaptador-reductor-de-bano-infantil-diseno-tipo-carro</t>
+          <t>https://www.solobabys.com/products/set-de-bloques-didacticos-infantil-con-molino-y-figuras</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla-2026-03-28T160638.235.webp?v=1774732117</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsApp_27.webp?v=1786661794</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
@@ -4984,11 +4984,11 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>10762339385654</v>
+        <v>10649160843574</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Set Toalla con Capota + Babitas WaKid's</t>
+          <t>Bacin Prakiplas 7337 Tortuga | 7709412827917</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -4998,14 +4998,14 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Recién nacido, Cobijas y toallas, Baby shower, Más vendidos</t>
+          <t>Bacinillas</t>
         </is>
       </c>
       <c r="E85" s="3" t="n">
-        <v>36000</v>
+        <v>37500</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>51429</v>
+        <v>53571</v>
       </c>
       <c r="G85" s="2" t="inlineStr"/>
       <c r="H85" s="2" t="n">
@@ -5018,16 +5018,16 @@
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/set-toalla-con-capota-babitas-wakids</t>
+          <t>https://www.solobabys.com/products/adaptador-reductor-de-bano-infantil-diseno-tipo-carro</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage1jul2026_10_34_42p.m.webp?v=1782963320</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla-2026-03-28T160638.235.webp?v=1774732117</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
@@ -5037,11 +5037,11 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>10861984448822</v>
+        <v>10762339385654</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Tapete Didáctico Plegable con Bolso de Transporte</t>
+          <t>Set Toalla con Capota + Babitas WaKid's</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -5051,14 +5051,14 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Baby shower</t>
+          <t>Recién nacido, Cobijas y toallas, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E86" s="3" t="n">
-        <v>35000</v>
+        <v>36000</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>50000</v>
+        <v>51429</v>
       </c>
       <c r="G86" s="2" t="inlineStr"/>
       <c r="H86" s="2" t="n">
@@ -5071,16 +5071,16 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/tapete-didactico-plegable-con-bolso-de-transporte</t>
+          <t>https://www.solobabys.com/products/set-toalla-con-capota-babitas-wakids</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-21at3.35.30PM_2.webp?v=1790029328</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage1jul2026_10_34_42p.m.webp?v=1782963320</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
@@ -5090,11 +5090,11 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>10645594538294</v>
+        <v>10861984448822</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Tapete inflable con agua para bebé</t>
+          <t>Tapete Didáctico Plegable con Bolso de Transporte</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Más vendidos</t>
+          <t>Juguetes, Baby shower</t>
         </is>
       </c>
       <c r="E87" s="3" t="n">
@@ -5124,16 +5124,16 @@
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/tapete-inflable-con-agua-para-bebe</t>
+          <t>https://www.solobabys.com/products/tapete-didactico-plegable-con-bolso-de-transporte</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla-2026-03-27T144417.793.webp?v=1774640713</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-21at3.35.30PM_2.webp?v=1790029328</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
@@ -5143,11 +5143,11 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>10643504759094</v>
+        <v>10645594538294</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Extractor Eléctrico Portátil de Leche</t>
+          <t>Tapete inflable con agua para bebé</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Lactancia</t>
+          <t>Juguetes, Más vendidos</t>
         </is>
       </c>
       <c r="E88" s="3" t="n">
@@ -5177,12 +5177,12 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/extractor-manual-de-leche-materna</t>
+          <t>https://www.solobabys.com/products/tapete-inflable-con-agua-para-bebe</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla_87.webp?v=1774564344</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla-2026-03-27T144417.793.webp?v=1774640713</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
@@ -5196,11 +5196,11 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>10762503979318</v>
+        <v>10643504759094</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Chaleco para Moto Bebé</t>
+          <t>Extractor Eléctrico Portátil de Leche</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Accesorios, Baby shower</t>
+          <t>Lactancia</t>
         </is>
       </c>
       <c r="E89" s="3" t="n">
@@ -5230,16 +5230,16 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/chaleco-para-moto-bebe</t>
+          <t>https://www.solobabys.com/products/extractor-manual-de-leche-materna</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage2jul2026_06_52_50a.m.webp?v=1782993218</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla_87.webp?v=1774564344</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
@@ -5249,11 +5249,11 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>10650894762294</v>
+        <v>10762503979318</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Aspirador Nasal Eléctrico HENHR1228 | Limpieza Suave y Práctica para Bebé</t>
+          <t>Chaleco para Moto Bebé</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5263,22 +5263,18 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower</t>
+          <t>Accesorios, Baby shower</t>
         </is>
       </c>
       <c r="E90" s="3" t="n">
-        <v>34000</v>
+        <v>35000</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>47600</v>
-      </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Rosa', 'Amarillo', 'Verde', 'Azul']</t>
-        </is>
-      </c>
+        <v>50000</v>
+      </c>
+      <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
@@ -5287,16 +5283,16 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/aspirador-nasal-electrico-henhr1228-limpieza-suave-y-practica-para-bebe</t>
+          <t>https://www.solobabys.com/products/chaleco-para-moto-bebe</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_41.webp?v=1779576241</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage2jul2026_06_52_50a.m.webp?v=1782993218</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
@@ -5306,11 +5302,11 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>10651903099190</v>
+        <v>10650894762294</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Bacín infantil Praktiplas Oso</t>
+          <t>Aspirador Nasal Eléctrico HENHR1228 | Limpieza Suave y Práctica para Bebé</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -5320,18 +5316,22 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Bacinillas</t>
+          <t>Aseo y cuidado, Baby shower</t>
         </is>
       </c>
       <c r="E91" s="3" t="n">
-        <v>33500</v>
+        <v>34000</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>47857</v>
-      </c>
-      <c r="G91" s="2" t="inlineStr"/>
+        <v>47600</v>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Rosa', 'Amarillo', 'Verde', 'Azul']</t>
+        </is>
+      </c>
       <c r="H91" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
@@ -5340,16 +5340,16 @@
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/bacin-infantil-praktiplas-oso</t>
+          <t>https://www.solobabys.com/products/aspirador-nasal-electrico-henhr1228-limpieza-suave-y-practica-para-bebe</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla-2026-04-01T122700.534.webp?v=1775064763</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_41.webp?v=1779576241</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
@@ -5359,11 +5359,11 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>15420728574262</v>
+        <v>10651903099190</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Perrito Superhéroe Musical con Luces | Super Electric Dog</t>
+          <t>Bacín infantil Praktiplas Oso</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -5373,14 +5373,14 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Juguetes</t>
+          <t>Bacinillas</t>
         </is>
       </c>
       <c r="E92" s="3" t="n">
-        <v>33000</v>
+        <v>33500</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>47000</v>
+        <v>47857</v>
       </c>
       <c r="G92" s="2" t="inlineStr"/>
       <c r="H92" s="2" t="n">
@@ -5393,30 +5393,30 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/perrito-superheroe-musical-con-luces-super-electric-dog</t>
+          <t>https://www.solobabys.com/products/bacin-infantil-praktiplas-oso</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/super-electric-dog-2.webp?v=1792063802</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla-2026-04-01T122700.534.webp?v=1775064763</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-title { font-family: 'Fraunces', serif; font-size: 38px; line-height: 1.1; color: #00afba; margin: 0 0 15px 0; letter-spacin</t>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>10649163104566</v>
+        <v>15420728574262</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Cobija capota animales Modelo CL1006</t>
+          <t>Perrito Superhéroe Musical con Luces | Super Electric Dog</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -5426,14 +5426,14 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Recién nacido, Cobijas y toallas, Baby shower, Más vendidos</t>
+          <t>Juguetes</t>
         </is>
       </c>
       <c r="E93" s="3" t="n">
         <v>33000</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>47143</v>
+        <v>47000</v>
       </c>
       <c r="G93" s="2" t="inlineStr"/>
       <c r="H93" s="2" t="n">
@@ -5446,30 +5446,30 @@
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/cobija-capota-animales-modelo-cl1006</t>
+          <t>https://www.solobabys.com/products/perrito-superheroe-musical-con-luces-super-electric-dog</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-03-21at4.46.17PM_1.jpg?v=1774733372</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/super-electric-dog-2.webp?v=1792063802</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-title { font-family: 'Fraunces', serif; font-size: 38px; line-height: 1.1; color: #00afba; margin: 0 0 15px 0; letter-spacin</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>10721369522486</v>
+        <v>10649163104566</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Cepillo Lava Teteros | MST6608</t>
+          <t>Cobija capota animales Modelo CL1006</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -5479,22 +5479,18 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Teteros, Más vendidos</t>
+          <t>Recién nacido, Cobijas y toallas, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E94" s="3" t="n">
-        <v>30700</v>
+        <v>33000</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>43857</v>
-      </c>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Rojo', 'azul']</t>
-        </is>
-      </c>
+        <v>47143</v>
+      </c>
+      <c r="G94" s="2" t="inlineStr"/>
       <c r="H94" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
@@ -5503,12 +5499,12 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/cepillo-lava-teteros-mst6608</t>
+          <t>https://www.solobabys.com/products/cobija-capota-animales-modelo-cl1006</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_17.webp?v=1779418188</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-03-21at4.46.17PM_1.jpg?v=1774733372</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
@@ -5522,11 +5518,11 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>10643571310902</v>
+        <v>10721369522486</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Toalla suave y absorbente para bebé</t>
+          <t>Cepillo Lava Teteros | MST6608</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -5536,18 +5532,22 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Cobijas y toallas, Baby shower</t>
+          <t>Teteros, Más vendidos</t>
         </is>
       </c>
       <c r="E95" s="3" t="n">
-        <v>28500</v>
+        <v>30700</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>40714</v>
-      </c>
-      <c r="G95" s="2" t="inlineStr"/>
+        <v>43857</v>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Rojo', 'azul']</t>
+        </is>
+      </c>
       <c r="H95" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
@@ -5556,12 +5556,12 @@
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/toalla-suave-y-absorbente-para-bebe</t>
+          <t>https://www.solobabys.com/products/cepillo-lava-teteros-mst6608</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-03-21at5.41.21PM_3.jpg?v=1774569011</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_17.webp?v=1779418188</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
@@ -5575,11 +5575,11 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>10643571573046</v>
+        <v>10643571310902</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Set de Aseo Kokibebe</t>
+          <t>Toalla suave y absorbente para bebé</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -5589,14 +5589,14 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower</t>
+          <t>Cobijas y toallas, Baby shower</t>
         </is>
       </c>
       <c r="E96" s="3" t="n">
         <v>28500</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>36900</v>
+        <v>40714</v>
       </c>
       <c r="G96" s="2" t="inlineStr"/>
       <c r="H96" s="2" t="n">
@@ -5609,16 +5609,16 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/set-de-aseo-kokibebe</t>
+          <t>https://www.solobabys.com/products/toalla-suave-y-absorbente-para-bebe</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla-2026-03-27T110341.589_a2241f01-ac70-4d1e-a938-52f6eaddf13d.webp?v=1774627574</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-03-21at5.41.21PM_3.jpg?v=1774569011</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
@@ -5628,11 +5628,11 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>10837689532726</v>
+        <v>10643571573046</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Ajuar prematuro para Bebé 5 Piezas – My Best Friends</t>
+          <t>Set de Aseo Kokibebe</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -5642,30 +5642,32 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Recién nacido, Ropa, Baby shower</t>
+          <t>Aseo y cuidado, Baby shower</t>
         </is>
       </c>
       <c r="E97" s="3" t="n">
-        <v>28000</v>
-      </c>
-      <c r="F97" s="3" t="n"/>
+        <v>28500</v>
+      </c>
+      <c r="F97" s="3" t="n">
+        <v>36900</v>
+      </c>
       <c r="G97" s="2" t="inlineStr"/>
       <c r="H97" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/ajuar-para-bebe-5-piezas-my-best-friends</t>
+          <t>https://www.solobabys.com/products/set-de-aseo-kokibebe</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-03at11.35.47AM_2.webp?v=1788819715</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla-2026-03-27T110341.589_a2241f01-ac70-4d1e-a938-52f6eaddf13d.webp?v=1774627574</t>
         </is>
       </c>
       <c r="L97" s="2" t="n">
@@ -5679,11 +5681,11 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>10837681799478</v>
+        <v>10837689532726</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Lima Eléctrica para Uñas de Bebé</t>
+          <t>Ajuar prematuro para Bebé 5 Piezas – My Best Friends</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -5693,36 +5695,34 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Juguetes</t>
+          <t>Recién nacido, Ropa, Baby shower</t>
         </is>
       </c>
       <c r="E98" s="3" t="n">
-        <v>27000</v>
-      </c>
-      <c r="F98" s="3" t="n">
-        <v>38571</v>
-      </c>
+        <v>28000</v>
+      </c>
+      <c r="F98" s="3" t="n"/>
       <c r="G98" s="2" t="inlineStr"/>
       <c r="H98" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/set-de-manicure-para-bebe</t>
+          <t>https://www.solobabys.com/products/ajuar-para-bebe-5-piezas-my-best-friends</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage7sept2026_17_09_49.webp?v=1788819099</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-03at11.35.47AM_2.webp?v=1788819715</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
@@ -5732,11 +5732,11 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>10650935755062</v>
+        <v>10837681799478</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Crema Protectora Happy Soft 250gr | Cuidado y Protección para Bebé</t>
+          <t>Lima Eléctrica para Uñas de Bebé</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower</t>
+          <t>Aseo y cuidado, Juguetes</t>
         </is>
       </c>
       <c r="E99" s="3" t="n">
@@ -5766,16 +5766,16 @@
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/crema-protectora-happy-soft-250gr-cuidado-y-proteccion-para-bebe</t>
+          <t>https://www.solobabys.com/products/set-de-manicure-para-bebe</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-01T022000.472.webp?v=1780298415</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage7sept2026_17_09_49.webp?v=1788819099</t>
         </is>
       </c>
       <c r="L99" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
@@ -5785,11 +5785,11 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>10642900058422</v>
+        <v>10650935755062</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Lima Eléctrica Only Baby | Cuidado Seguro de Uñas para Bebé</t>
+          <t>Crema Protectora Happy Soft 250gr | Cuidado y Protección para Bebé</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -5799,22 +5799,18 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Accesorios, Baby shower, Más vendidos</t>
+          <t>Aseo y cuidado, Baby shower</t>
         </is>
       </c>
       <c r="E100" s="3" t="n">
-        <v>25500</v>
+        <v>27000</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>27000</v>
-      </c>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Rosa', 'Azul']</t>
-        </is>
-      </c>
+        <v>38571</v>
+      </c>
+      <c r="G100" s="2" t="inlineStr"/>
       <c r="H100" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
@@ -5823,16 +5819,16 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/lima-electrica-only-baby-cuidado-seguro-de-unas-para-bebe</t>
+          <t>https://www.solobabys.com/products/crema-protectora-happy-soft-250gr-cuidado-y-proteccion-para-bebe</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/limaelectrica_1000x_b8a0febc-3486-42a7-a3cf-8a61cc5b6601.webp?v=1774036791</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-01T022000.472.webp?v=1780298415</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
@@ -5842,11 +5838,11 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>10643572031798</v>
+        <v>10642900058422</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Set Manicure Baby Care</t>
+          <t>Lima Eléctrica Only Baby | Cuidado Seguro de Uñas para Bebé</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -5860,14 +5856,18 @@
         </is>
       </c>
       <c r="E101" s="3" t="n">
-        <v>25000</v>
+        <v>25500</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>34900</v>
-      </c>
-      <c r="G101" s="2" t="inlineStr"/>
+        <v>27000</v>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Rosa', 'Azul']</t>
+        </is>
+      </c>
       <c r="H101" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
@@ -5876,12 +5876,12 @@
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/set-manicure-baby-care</t>
+          <t>https://www.solobabys.com/products/lima-electrica-only-baby-cuidado-seguro-de-unas-para-bebe</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla-2026-03-27T143126.593_2c7a959d-f5cc-459d-81e2-3ea14b4df0ba.webp?v=1774640025</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/limaelectrica_1000x_b8a0febc-3486-42a7-a3cf-8a61cc5b6601.webp?v=1774036791</t>
         </is>
       </c>
       <c r="L101" s="2" t="n">
@@ -5895,11 +5895,11 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>10651062665526</v>
+        <v>10643572031798</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Cobija TG 08 burbuja Diseños surtidos</t>
+          <t>Set Manicure Baby Care</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -5909,14 +5909,14 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Cobijas y toallas, Baby shower, Más vendidos</t>
+          <t>Aseo y cuidado, Accesorios, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E102" s="3" t="n">
-        <v>24000</v>
+        <v>25000</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>34286</v>
+        <v>34900</v>
       </c>
       <c r="G102" s="2" t="inlineStr"/>
       <c r="H102" s="2" t="n">
@@ -5929,16 +5929,16 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/cobija-tg-08-burbuja-disenos-surtidos</t>
+          <t>https://www.solobabys.com/products/set-manicure-baby-care</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_-_2026-06-03T163734.732.webp?v=1780522748</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla-2026-03-27T143126.593_2c7a959d-f5cc-459d-81e2-3ea14b4df0ba.webp?v=1774640025</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
@@ -5948,11 +5948,11 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>10762511089974</v>
+        <v>10651062665526</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>MORDEDOR CON CADENA ONLY| HLW-040</t>
+          <t>Cobija TG 08 burbuja Diseños surtidos</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -5962,14 +5962,14 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Baby shower</t>
+          <t>Cobijas y toallas, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E103" s="3" t="n">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>31429</v>
+        <v>34286</v>
       </c>
       <c r="G103" s="2" t="inlineStr"/>
       <c r="H103" s="2" t="n">
@@ -5982,30 +5982,30 @@
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/mordedor-con-sujetador-para-bebe</t>
+          <t>https://www.solobabys.com/products/cobija-tg-08-burbuja-disenos-surtidos</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage2jul2026_07_37_12a.m.webp?v=1782995871</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_-_2026-06-03T163734.732.webp?v=1780522748</t>
         </is>
       </c>
       <c r="L103" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container{font-family:'Quicksand',sans-serif;max-width:480px;margin:0 auto;color:#4a5568;padding:26px;background:#fff;} .b-rating{display:flex;align-items:center;gap:8px;margin-bottom:12px;font-size:14px;font-weight:700;color:#c8d431;flex-wrap:wrap;} .b-rating-text</t>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>10651054637366</v>
+        <v>10762511089974</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Cobija vilu cinta estampada Diseños surtidos</t>
+          <t>MORDEDOR CON CADENA ONLY| HLW-040</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Cobijas y toallas, Baby shower, Más vendidos</t>
+          <t>Juguetes, Baby shower</t>
         </is>
       </c>
       <c r="E104" s="3" t="n">
@@ -6035,30 +6035,30 @@
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/cobija-vilu-cinta-estampada-disenos-surtidos</t>
+          <t>https://www.solobabys.com/products/mordedor-con-sujetador-para-bebe</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_-_2026-06-02T212801.807.webp?v=1780453770</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage2jul2026_07_37_12a.m.webp?v=1782995871</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container{font-family:'Quicksand',sans-serif;max-width:480px;margin:0 auto;color:#4a5568;padding:26px;background:#fff;} .b-rating{display:flex;align-items:center;gap:8px;margin-bottom:12px;font-size:14px;font-weight:700;color:#c8d431;flex-wrap:wrap;} .b-rating-text</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>10721360019766</v>
+        <v>10651054637366</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Termo Plegable Infantil Balón | JS-8</t>
+          <t>Cobija vilu cinta estampada Diseños surtidos</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -6068,22 +6068,18 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Alimentación</t>
+          <t>Cobijas y toallas, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E105" s="3" t="n">
         <v>22000</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>31000</v>
-      </c>
-      <c r="G105" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Blanco', 'Verde', 'azul']</t>
-        </is>
-      </c>
+        <v>31429</v>
+      </c>
+      <c r="G105" s="2" t="inlineStr"/>
       <c r="H105" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
@@ -6092,12 +6088,12 @@
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/termo-plegable-infantil-balon-js-8</t>
+          <t>https://www.solobabys.com/products/cobija-vilu-cinta-estampada-disenos-surtidos</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_14.webp?v=1779414355</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_-_2026-06-02T212801.807.webp?v=1780453770</t>
         </is>
       </c>
       <c r="L105" s="2" t="n">
@@ -6111,11 +6107,11 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>10721353236790</v>
+        <v>10721360019766</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Termo Plegable Infantil | JS-9</t>
+          <t>Termo Plegable Infantil Balón | JS-8</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -6125,7 +6121,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Alimentación, Baby shower</t>
+          <t>Alimentación</t>
         </is>
       </c>
       <c r="E106" s="3" t="n">
@@ -6136,11 +6132,11 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Color: ['Púrpura', 'Rosa']</t>
+          <t>Color: ['Blanco', 'Verde', 'azul']</t>
         </is>
       </c>
       <c r="H106" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
@@ -6149,16 +6145,16 @@
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/termo-plegable-infantil-js-9</t>
+          <t>https://www.solobabys.com/products/termo-plegable-infantil-balon-js-8</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_8.webp?v=1779411444</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_14.webp?v=1779414355</t>
         </is>
       </c>
       <c r="L106" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
@@ -6168,11 +6164,11 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>10643064684854</v>
+        <v>10721353236790</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Vaso Amazing Baby | MON1035</t>
+          <t>Termo Plegable Infantil | JS-9</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -6186,14 +6182,14 @@
         </is>
       </c>
       <c r="E107" s="3" t="n">
-        <v>21000</v>
+        <v>22000</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>27600</v>
+        <v>31000</v>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Color: ['Azul', 'Rosa']</t>
+          <t>Color: ['Púrpura', 'Rosa']</t>
         </is>
       </c>
       <c r="H107" s="2" t="n">
@@ -6206,16 +6202,16 @@
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/vaso-amazing-baby-vaso-entrenador-con-asas</t>
+          <t>https://www.solobabys.com/products/termo-plegable-infantil-js-9</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/sbproductos_3_1.webp?v=1774046605</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_8.webp?v=1779411444</t>
         </is>
       </c>
       <c r="L107" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
@@ -6225,11 +6221,11 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>10642009358646</v>
+        <v>10643064684854</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Tapete Foamy Rompecabezas Infantil | Piso Didáctico para Bebé y Niños</t>
+          <t>Vaso Amazing Baby | MON1035</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -6239,22 +6235,22 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Baby shower</t>
+          <t>Alimentación, Baby shower</t>
         </is>
       </c>
       <c r="E108" s="3" t="n">
-        <v>20500</v>
+        <v>21000</v>
       </c>
       <c r="F108" s="3" t="n">
         <v>27600</v>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Color: ['Frutas', 'Números', 'Letras']</t>
+          <t>Color: ['Azul', 'Rosa']</t>
         </is>
       </c>
       <c r="H108" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
@@ -6263,16 +6259,16 @@
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/tapete-foamy-rompecabezas-infantil-piso-didactico-para-bebe-y-ninos</t>
+          <t>https://www.solobabys.com/products/vaso-amazing-baby-vaso-entrenador-con-asas</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/D_NQ_NP_2X_812378-CBT91060493341_082025-F.webp?v=1773965161</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/sbproductos_3_1.webp?v=1774046605</t>
         </is>
       </c>
       <c r="L108" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
@@ -6282,11 +6278,11 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>10729673720118</v>
+        <v>10642009358646</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Tetero Only 8 Onzas | A2DJ</t>
+          <t>Tapete Foamy Rompecabezas Infantil | Piso Didáctico para Bebé y Niños</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -6296,18 +6292,22 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Teteros</t>
+          <t>Juguetes, Baby shower</t>
         </is>
       </c>
       <c r="E109" s="3" t="n">
-        <v>19000</v>
+        <v>20500</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>27143</v>
-      </c>
-      <c r="G109" s="2" t="inlineStr"/>
+        <v>27600</v>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Frutas', 'Números', 'Letras']</t>
+        </is>
+      </c>
       <c r="H109" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
@@ -6316,16 +6316,16 @@
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/tetero-only-8-onzas-a2dj</t>
+          <t>https://www.solobabys.com/products/tapete-foamy-rompecabezas-infantil-piso-didactico-para-bebe-y-ninos</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_88.webp?v=1780097838</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/D_NQ_NP_2X_812378-CBT91060493341_082025-F.webp?v=1773965161</t>
         </is>
       </c>
       <c r="L109" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
@@ -6335,11 +6335,11 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>10651909718326</v>
+        <v>10729673720118</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Orinal infantil Praktiplas Pingüino</t>
+          <t>Tetero Only 8 Onzas | A2DJ</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Bacinillas, Más vendidos</t>
+          <t>Teteros</t>
         </is>
       </c>
       <c r="E110" s="3" t="n">
@@ -6358,13 +6358,9 @@
       <c r="F110" s="3" t="n">
         <v>27143</v>
       </c>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Aguamarina', 'Negro']</t>
-        </is>
-      </c>
+      <c r="G110" s="2" t="inlineStr"/>
       <c r="H110" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
@@ -6373,12 +6369,12 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/orinal-infantil-praktiplas-pinguino</t>
+          <t>https://www.solobabys.com/products/tetero-only-8-onzas-a2dj</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_51.webp?v=1779814860</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_88.webp?v=1780097838</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
@@ -6392,11 +6388,11 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>10649149767990</v>
+        <v>10651909718326</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Bolsas de almacenamiento de leche materna | ONBY-1</t>
+          <t>Orinal infantil Praktiplas Pingüino</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -6406,18 +6402,22 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Recién nacido, Lactancia, Baby shower</t>
+          <t>Bacinillas, Más vendidos</t>
         </is>
       </c>
       <c r="E111" s="3" t="n">
-        <v>18000</v>
+        <v>19000</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>25714</v>
-      </c>
-      <c r="G111" s="2" t="inlineStr"/>
+        <v>27143</v>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Aguamarina', 'Negro']</t>
+        </is>
+      </c>
       <c r="H111" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
@@ -6426,16 +6426,16 @@
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/bolsas-de-almacenamiento-de-leche-materna-250-ml-x-30-unidades</t>
+          <t>https://www.solobabys.com/products/orinal-infantil-praktiplas-pinguino</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_-_2026-06-02T205506.029.webp?v=1780451739</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_51.webp?v=1779814860</t>
         </is>
       </c>
       <c r="L111" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
@@ -6445,11 +6445,11 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>10642865127734</v>
+        <v>10649149767990</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Tetero Only Baby Natural 9oz / 260ml | Alimentación para Bebé</t>
+          <t>Bolsas de almacenamiento de leche materna | ONBY-1</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -6459,22 +6459,18 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Teteros, Baby shower, Más vendidos</t>
+          <t>Recién nacido, Lactancia, Baby shower</t>
         </is>
       </c>
       <c r="E112" s="3" t="n">
-        <v>17500</v>
+        <v>18000</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>22600</v>
-      </c>
-      <c r="G112" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Rosa', 'Azul', 'Transparente']</t>
-        </is>
-      </c>
+        <v>25714</v>
+      </c>
+      <c r="G112" s="2" t="inlineStr"/>
       <c r="H112" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
@@ -6483,12 +6479,12 @@
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/tetero-only-baby-natural-8oz-260ml-alimentacion-para-bebe</t>
+          <t>https://www.solobabys.com/products/bolsas-de-almacenamiento-de-leche-materna-250-ml-x-30-unidades</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_74.webp?v=1779927570</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_-_2026-06-02T205506.029.webp?v=1780451739</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
@@ -6502,11 +6498,11 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>10727775371574</v>
+        <v>10642865127734</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Cepillo Lava Tetero Only Baby A-71</t>
+          <t>Tetero Only Baby Natural 9oz / 260ml | Alimentación para Bebé</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -6516,20 +6512,22 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Teteros</t>
+          <t>Teteros, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E113" s="3" t="n">
         <v>17500</v>
       </c>
-      <c r="F113" s="3" t="n"/>
+      <c r="F113" s="3" t="n">
+        <v>22600</v>
+      </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Color: ['Azul', 'Rosa']</t>
+          <t>Color: ['Rosa', 'Azul', 'Transparente']</t>
         </is>
       </c>
       <c r="H113" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
@@ -6538,12 +6536,12 @@
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/cepillo-lava-tetero-only-baby-a-71</t>
+          <t>https://www.solobabys.com/products/tetero-only-baby-natural-8oz-260ml-alimentacion-para-bebe</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_71.webp?v=1779925711</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_74.webp?v=1779927570</t>
         </is>
       </c>
       <c r="L113" s="2" t="n">
@@ -6557,11 +6555,11 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>10642845761846</v>
+        <v>10727775371574</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Tetero Only Baby Natural 4oz / 125ml | Anticólicos con Asas</t>
+          <t>Cepillo Lava Tetero Only Baby A-71</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -6571,22 +6569,20 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Teteros, Baby shower, Más vendidos</t>
+          <t>Teteros</t>
         </is>
       </c>
       <c r="E114" s="3" t="n">
-        <v>17000</v>
-      </c>
-      <c r="F114" s="3" t="n">
-        <v>22000</v>
-      </c>
+        <v>17500</v>
+      </c>
+      <c r="F114" s="3" t="n"/>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Color: ['Rosa', 'Azul', 'Transparente']</t>
+          <t>Color: ['Azul', 'Rosa']</t>
         </is>
       </c>
       <c r="H114" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
@@ -6595,12 +6591,12 @@
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/tetero-only-baby-natural-4oz-125ml-anticolicos-con-asas</t>
+          <t>https://www.solobabys.com/products/cepillo-lava-tetero-only-baby-a-71</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/sbproductos_1_2.webp?v=1774025676</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_71.webp?v=1779925711</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
@@ -6614,11 +6610,11 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>10643479331126</v>
+        <v>10642845761846</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Copa recolectora de leche materna</t>
+          <t>Tetero Only Baby Natural 4oz / 125ml | Anticólicos con Asas</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -6628,18 +6624,22 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Recién nacido, Lactancia, Más vendidos</t>
+          <t>Teteros, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E115" s="3" t="n">
-        <v>16500</v>
+        <v>17000</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>23571</v>
-      </c>
-      <c r="G115" s="2" t="inlineStr"/>
+        <v>22000</v>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Rosa', 'Azul', 'Transparente']</t>
+        </is>
+      </c>
       <c r="H115" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/fular-cole-portabebe-ergonomico</t>
+          <t>https://www.solobabys.com/products/tetero-only-baby-natural-4oz-125ml-anticolicos-con-asas</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla_55.webp?v=1774162492</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/sbproductos_1_2.webp?v=1774025676</t>
         </is>
       </c>
       <c r="L115" s="2" t="n">
@@ -6667,11 +6667,11 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>10741795520822</v>
+        <v>10643479331126</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Lima eléctrica para Bebé | V168</t>
+          <t>Copa recolectora de leche materna</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -6681,14 +6681,14 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower, Más vendidos</t>
+          <t>Recién nacido, Lactancia, Más vendidos</t>
         </is>
       </c>
       <c r="E116" s="3" t="n">
-        <v>16000</v>
+        <v>16500</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>22857</v>
+        <v>23571</v>
       </c>
       <c r="G116" s="2" t="inlineStr"/>
       <c r="H116" s="2" t="n">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/cortaunas-electrico-para-bebe-v168</t>
+          <t>https://www.solobabys.com/products/fular-cole-portabebe-ergonomico</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-09T172638.946.webp?v=1781044015</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla_55.webp?v=1774162492</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
@@ -6720,11 +6720,11 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>10643571147062</v>
+        <v>10741795520822</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Medias estilo española para bebé</t>
+          <t>Lima eléctrica para Bebé | V168</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -6734,14 +6734,14 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Ropa, Baby shower</t>
+          <t>Aseo y cuidado, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E117" s="3" t="n">
-        <v>14500</v>
+        <v>16000</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>19900</v>
+        <v>22857</v>
       </c>
       <c r="G117" s="2" t="inlineStr"/>
       <c r="H117" s="2" t="n">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/medias-estilo-espanola-para-bebe</t>
+          <t>https://www.solobabys.com/products/cortaunas-electrico-para-bebe-v168</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_-_2026-08-14T185137.710.webp?v=1786751525</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-09T172638.946.webp?v=1781044015</t>
         </is>
       </c>
       <c r="L117" s="2" t="n">
@@ -6773,11 +6773,11 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>10730172449078</v>
+        <v>10643571147062</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Aspirador Nasal Boogy | 20931</t>
+          <t>Medias estilo española para bebé</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -6787,14 +6787,14 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower</t>
+          <t>Ropa, Baby shower</t>
         </is>
       </c>
       <c r="E118" s="3" t="n">
-        <v>14000</v>
+        <v>14500</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>20000</v>
+        <v>19900</v>
       </c>
       <c r="G118" s="2" t="inlineStr"/>
       <c r="H118" s="2" t="n">
@@ -6807,12 +6807,12 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/aspirador-nasal-boogy-20931</t>
+          <t>https://www.solobabys.com/products/medias-estilo-espanola-para-bebe</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_99.webp?v=1780185614</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_-_2026-08-14T185137.710.webp?v=1786751525</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
@@ -6826,11 +6826,11 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>10650919108918</v>
+        <v>10730172449078</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Crema Protectora Happy Soft 60gr | Cuidado y Protección para Bebé</t>
+          <t>Aspirador Nasal Boogy | 20931</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -6844,10 +6844,10 @@
         </is>
       </c>
       <c r="E119" s="3" t="n">
-        <v>12500</v>
+        <v>14000</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>17857</v>
+        <v>20000</v>
       </c>
       <c r="G119" s="2" t="inlineStr"/>
       <c r="H119" s="2" t="n">
@@ -6860,16 +6860,16 @@
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/crema-protectora-happy-soft-60gr-cuidado-y-proteccion-para-bebe</t>
+          <t>https://www.solobabys.com/products/aspirador-nasal-boogy-20931</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-01T022221.997.webp?v=1780299053</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_99.webp?v=1780185614</t>
         </is>
       </c>
       <c r="L119" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
@@ -6879,11 +6879,11 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>10651924660534</v>
+        <v>10650919108918</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Bacín infantil Praktiplas Rana</t>
+          <t>Crema Protectora Happy Soft 60gr | Cuidado y Protección para Bebé</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -6893,22 +6893,18 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Bacinillas</t>
+          <t>Aseo y cuidado, Baby shower</t>
         </is>
       </c>
       <c r="E120" s="3" t="n">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>17143</v>
-      </c>
-      <c r="G120" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Aguamarina', 'Azul', 'fucsia']</t>
-        </is>
-      </c>
+        <v>17857</v>
+      </c>
+      <c r="G120" s="2" t="inlineStr"/>
       <c r="H120" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
@@ -6917,16 +6913,16 @@
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/bacin-infantil-praktiplas-rana</t>
+          <t>https://www.solobabys.com/products/crema-protectora-happy-soft-60gr-cuidado-y-proteccion-para-bebe</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_44.webp?v=1779577786</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-01T022221.997.webp?v=1780299053</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
@@ -6936,11 +6932,11 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>10762017669430</v>
+        <v>10651924660534</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Mordedor Control Silicona para Bebé</t>
+          <t>Bacín infantil Praktiplas Rana</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -6950,18 +6946,22 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Baby shower, Más vendidos</t>
+          <t>Bacinillas</t>
         </is>
       </c>
       <c r="E121" s="3" t="n">
-        <v>11000</v>
+        <v>12000</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>15714</v>
-      </c>
-      <c r="G121" s="2" t="inlineStr"/>
+        <v>17143</v>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Aguamarina', 'Azul', 'fucsia']</t>
+        </is>
+      </c>
       <c r="H121" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
@@ -6970,30 +6970,30 @@
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/mordedor-control-silicona-para-bebe</t>
+          <t>https://www.solobabys.com/products/bacin-infantil-praktiplas-rana</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage1jul2026_12_40_34p.m.webp?v=1782927688</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_44.webp?v=1779577786</t>
         </is>
       </c>
       <c r="L121" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>```html @import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color</t>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>10736632987958</v>
+        <v>10762017669430</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Mordedor Only Baby Dino</t>
+          <t>Mordedor Control Silicona para Bebé</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Baby shower</t>
+          <t>Juguetes, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E122" s="3" t="n">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/mordedor-only-baby-dino</t>
+          <t>https://www.solobabys.com/products/mordedor-control-silicona-para-bebe</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-05T183301.061.webp?v=1780702402</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage1jul2026_12_40_34p.m.webp?v=1782927688</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
@@ -7036,17 +7036,17 @@
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
+          <t>```html @import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>10652006547766</v>
+        <v>10736632987958</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Rascaencias Figuras AB-27 | Alivio para la Dentición del Bebé</t>
+          <t>Mordedor Only Baby Dino</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -7076,16 +7076,16 @@
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/rascaencias-figuras-ab-27-alivio-para-la-denticion-del-bebe</t>
+          <t>https://www.solobabys.com/products/mordedor-only-baby-dino</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/D_NQ_NP_900595-MLA91560968768_092025-O_EmbellecedordeProducto.webp?v=1775076453</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-05T183301.061.webp?v=1780702402</t>
         </is>
       </c>
       <c r="L123" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
@@ -7095,11 +7095,11 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>10642154062134</v>
+        <v>10652006547766</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Tetero Only Baby Natural 2oz / 60ml | Alimentación para Bebé</t>
+          <t>Rascaencias Figuras AB-27 | Alivio para la Dentición del Bebé</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -7109,22 +7109,18 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Teteros, Baby shower</t>
+          <t>Juguetes, Baby shower</t>
         </is>
       </c>
       <c r="E124" s="3" t="n">
-        <v>10500</v>
+        <v>11000</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>13600</v>
-      </c>
-      <c r="G124" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Azul', 'Rosa', 'Transparente']</t>
-        </is>
-      </c>
+        <v>15714</v>
+      </c>
+      <c r="G124" s="2" t="inlineStr"/>
       <c r="H124" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
@@ -7133,30 +7129,30 @@
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/tetero-only-baby-natural-2oz-60ml-alimentacion-para-bebe</t>
+          <t>https://www.solobabys.com/products/rascaencias-figuras-ab-27-alivio-para-la-denticion-del-bebe</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_Image_5_may_2026_10_26_07_a.m..webp?v=1777995497</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/D_NQ_NP_900595-MLA91560968768_092025-O_EmbellecedordeProducto.webp?v=1775076453</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #ffb80</t>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>10642902548790</v>
+        <v>10642154062134</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Guante Mordedor para Bebé | Alivio para Encías</t>
+          <t>Tetero Only Baby Natural 2oz / 60ml | Alimentación para Bebé</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -7166,18 +7162,18 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Accesorios, Baby shower, Más vendidos</t>
+          <t>Teteros, Baby shower</t>
         </is>
       </c>
       <c r="E125" s="3" t="n">
         <v>10500</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>15000</v>
+        <v>13600</v>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Color: ['Rosa', 'Azul', 'Verde']</t>
+          <t>Color: ['Azul', 'Rosa', 'Transparente']</t>
         </is>
       </c>
       <c r="H125" s="2" t="n">
@@ -7190,30 +7186,30 @@
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/guante-mordedor-para-bebe-alivio-para-encias</t>
+          <t>https://www.solobabys.com/products/tetero-only-baby-natural-2oz-60ml-alimentacion-para-bebe</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_64.webp?v=1779828393</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_Image_5_may_2026_10_26_07_a.m..webp?v=1777995497</t>
         </is>
       </c>
       <c r="L125" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #ffb80</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>10643478675766</v>
+        <v>10642902548790</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Pañitos Happy y Soft x100 | Limpieza Suave para Bebé</t>
+          <t>Guante Mordedor para Bebé | Alivio para Encías</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -7223,18 +7219,22 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower</t>
+          <t>Juguetes, Accesorios, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E126" s="3" t="n">
-        <v>10400</v>
+        <v>10500</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>14857</v>
-      </c>
-      <c r="G126" s="2" t="inlineStr"/>
+        <v>15000</v>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Rosa', 'Azul', 'Verde']</t>
+        </is>
+      </c>
       <c r="H126" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
@@ -7243,16 +7243,16 @@
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/panitos-happy-y-soft-x100-limpieza-suave-para-bebe</t>
+          <t>https://www.solobabys.com/products/guante-mordedor-para-bebe-alivio-para-encias</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/55.webp?v=1774123726</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_64.webp?v=1779828393</t>
         </is>
       </c>
       <c r="L126" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
@@ -7262,11 +7262,11 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>10651904344374</v>
+        <v>10643478675766</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Rascaencias Jirafa LW3 | Alivio para la Dentición del Bebé</t>
+          <t>Pañitos Happy y Soft x100 | Limpieza Suave para Bebé</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -7276,22 +7276,18 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Accesorios, Baby shower</t>
+          <t>Aseo y cuidado, Baby shower</t>
         </is>
       </c>
       <c r="E127" s="3" t="n">
-        <v>10000</v>
+        <v>10400</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>14000</v>
-      </c>
-      <c r="G127" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Amarillo', 'Rosa', 'Verde']</t>
-        </is>
-      </c>
+        <v>14857</v>
+      </c>
+      <c r="G127" s="2" t="inlineStr"/>
       <c r="H127" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
@@ -7300,16 +7296,16 @@
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/rascaencias-jirafa-lw3-alivio-para-la-denticion-del-bebe</t>
+          <t>https://www.solobabys.com/products/panitos-happy-y-soft-x100-limpieza-suave-para-bebe</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/1740126304665_1.webp?v=1775065667</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/55.webp?v=1774123726</t>
         </is>
       </c>
       <c r="L127" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
@@ -7319,11 +7315,11 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>10762342793526</v>
+        <v>10651904344374</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Babero Siliconado Ajustable</t>
+          <t>Rascaencias Jirafa LW3 | Alivio para la Dentición del Bebé</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -7333,18 +7329,22 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Alimentación, Baby shower</t>
+          <t>Juguetes, Accesorios, Baby shower</t>
         </is>
       </c>
       <c r="E128" s="3" t="n">
         <v>10000</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>14286</v>
-      </c>
-      <c r="G128" s="2" t="inlineStr"/>
+        <v>14000</v>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Amarillo', 'Rosa', 'Verde']</t>
+        </is>
+      </c>
       <c r="H128" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
@@ -7353,16 +7353,16 @@
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/babero-siliconado-ajustable</t>
+          <t>https://www.solobabys.com/products/rascaencias-jirafa-lw3-alivio-para-la-denticion-del-bebe</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage1jul2026_10_45_36p.m.webp?v=1782964027</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/1740126304665_1.webp?v=1775065667</t>
         </is>
       </c>
       <c r="L128" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
@@ -7372,11 +7372,11 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>10762507878710</v>
+        <v>10762342793526</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Mordedor Control Only Baby</t>
+          <t>Babero Siliconado Ajustable</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -7386,14 +7386,14 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Baby shower, Más vendidos</t>
+          <t>Alimentación, Baby shower</t>
         </is>
       </c>
       <c r="E129" s="3" t="n">
-        <v>9900</v>
+        <v>10000</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>14143</v>
+        <v>14286</v>
       </c>
       <c r="G129" s="2" t="inlineStr"/>
       <c r="H129" s="2" t="n">
@@ -7406,16 +7406,16 @@
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/mordedor-control-only-baby</t>
+          <t>https://www.solobabys.com/products/babero-siliconado-ajustable</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage2jul2026_07_10_28a.m.webp?v=1782994278</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage1jul2026_10_45_36p.m.webp?v=1782964027</t>
         </is>
       </c>
       <c r="L129" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
@@ -7425,11 +7425,11 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>10742260891958</v>
+        <v>10762507878710</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>CHUPA FRUTA ONLY BABY | C-40</t>
+          <t>Mordedor Control Only Baby</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -7439,14 +7439,14 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Alimentación, Más vendidos</t>
+          <t>Juguetes, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E130" s="3" t="n">
-        <v>9000</v>
+        <v>9900</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>12857</v>
+        <v>14143</v>
       </c>
       <c r="G130" s="2" t="inlineStr"/>
       <c r="H130" s="2" t="n">
@@ -7459,16 +7459,16 @@
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/chupa-fruta-only-baby-c-40</t>
+          <t>https://www.solobabys.com/products/mordedor-control-only-baby</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-09T215325.108.webp?v=1781060037</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage2jul2026_07_10_28a.m.webp?v=1782994278</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
@@ -7478,11 +7478,11 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>10762510303542</v>
+        <v>10742260891958</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Termómetro Digital Infantil</t>
+          <t>CHUPA FRUTA ONLY BABY | C-40</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -7492,14 +7492,14 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower, Más vendidos</t>
+          <t>Alimentación, Más vendidos</t>
         </is>
       </c>
       <c r="E131" s="3" t="n">
-        <v>8500</v>
+        <v>9000</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>12143</v>
+        <v>12857</v>
       </c>
       <c r="G131" s="2" t="inlineStr"/>
       <c r="H131" s="2" t="n">
@@ -7512,16 +7512,16 @@
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/termometro-digital-infantil</t>
+          <t>https://www.solobabys.com/products/chupa-fruta-only-baby-c-40</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage2jul2026_07_22_20a.m.webp?v=1782994980</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-09T215325.108.webp?v=1781060037</t>
         </is>
       </c>
       <c r="L131" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
@@ -7531,11 +7531,11 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>10642922602806</v>
+        <v>10762510303542</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Vajilla Love With para Bebé | 939BB</t>
+          <t>Termómetro Digital Infantil</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -7545,22 +7545,18 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Alimentación, Baby shower</t>
+          <t>Aseo y cuidado, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E132" s="3" t="n">
-        <v>7500</v>
+        <v>8500</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>9000</v>
-      </c>
-      <c r="G132" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Verde', 'Naranja', 'Azul', 'Aguamarina']</t>
-        </is>
-      </c>
+        <v>12143</v>
+      </c>
+      <c r="G132" s="2" t="inlineStr"/>
       <c r="H132" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
@@ -7569,12 +7565,12 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/vajilla-love-with-para-bebe-plato-infantil-con-diseno-divertido</t>
+          <t>https://www.solobabys.com/products/termometro-digital-infantil</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/39.webp?v=1774040907</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage2jul2026_07_22_20a.m.webp?v=1782994980</t>
         </is>
       </c>
       <c r="L132" s="2" t="n">
@@ -7588,11 +7584,11 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>10726877331766</v>
+        <v>10642922602806</v>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Cepillo Dental Siliconado 360° para Bebés</t>
+          <t>Vajilla Love With para Bebé | 939BB</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -7602,16 +7598,22 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Más vendidos</t>
+          <t>Alimentación, Baby shower</t>
         </is>
       </c>
       <c r="E133" s="3" t="n">
         <v>7500</v>
       </c>
-      <c r="F133" s="3" t="n"/>
-      <c r="G133" s="2" t="inlineStr"/>
+      <c r="F133" s="3" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Verde', 'Naranja', 'Azul', 'Aguamarina']</t>
+        </is>
+      </c>
       <c r="H133" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
@@ -7620,16 +7622,16 @@
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/cepillo-dental-siliconado-360-para-bebes</t>
+          <t>https://www.solobabys.com/products/vajilla-love-with-para-bebe-plato-infantil-con-diseno-divertido</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_62.webp?v=1779825817</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/39.webp?v=1774040907</t>
         </is>
       </c>
       <c r="L133" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
@@ -7639,11 +7641,11 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>10643440664886</v>
+        <v>10726877331766</v>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Aspirador Nasal Only Baby | HENFZ11</t>
+          <t>Cepillo Dental Siliconado 360° para Bebés</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -7653,22 +7655,16 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower</t>
+          <t>Aseo y cuidado, Más vendidos</t>
         </is>
       </c>
       <c r="E134" s="3" t="n">
-        <v>6500</v>
-      </c>
-      <c r="F134" s="3" t="n">
-        <v>7000</v>
-      </c>
-      <c r="G134" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Azul', 'Rosa']</t>
-        </is>
-      </c>
+        <v>7500</v>
+      </c>
+      <c r="F134" s="3" t="n"/>
+      <c r="G134" s="2" t="inlineStr"/>
       <c r="H134" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
@@ -7677,16 +7673,16 @@
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/aspirador-nasal-only-baby-limpieza-suave-para-bebe</t>
+          <t>https://www.solobabys.com/products/cepillo-dental-siliconado-360-para-bebes</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/aspirador-nasal-azul-para-bebe.webp?v=1774108168</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_62.webp?v=1779825817</t>
         </is>
       </c>
       <c r="L134" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
@@ -7696,11 +7692,11 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>10728210792758</v>
+        <v>10643440664886</v>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Set Manicure Bebé | JJ250347</t>
+          <t>Aspirador Nasal Only Baby | HENFZ11</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -7710,18 +7706,22 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado</t>
+          <t>Aseo y cuidado, Baby shower</t>
         </is>
       </c>
       <c r="E135" s="3" t="n">
         <v>6500</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>9286</v>
-      </c>
-      <c r="G135" s="2" t="inlineStr"/>
+        <v>7000</v>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Azul', 'Rosa']</t>
+        </is>
+      </c>
       <c r="H135" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
@@ -7730,16 +7730,16 @@
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/set-manicure-bebe-jj250347</t>
+          <t>https://www.solobabys.com/products/aspirador-nasal-only-baby-limpieza-suave-para-bebe</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_81.webp?v=1780001979</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/aspirador-nasal-azul-para-bebe.webp?v=1774108168</t>
         </is>
       </c>
       <c r="L135" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
@@ -7749,11 +7749,11 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>10743245766966</v>
+        <v>10728210792758</v>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Cepillo Lengua Only Baby | FZ-121</t>
+          <t>Set Manicure Bebé | JJ250347</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -7763,14 +7763,14 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower, Más vendidos</t>
+          <t>Aseo y cuidado</t>
         </is>
       </c>
       <c r="E136" s="3" t="n">
-        <v>6000</v>
+        <v>6500</v>
       </c>
       <c r="F136" s="3" t="n">
-        <v>8571</v>
+        <v>9286</v>
       </c>
       <c r="G136" s="2" t="inlineStr"/>
       <c r="H136" s="2" t="n">
@@ -7783,16 +7783,16 @@
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/cepillo-lengua-only-baby-fz-121</t>
+          <t>https://www.solobabys.com/products/set-manicure-bebe-jj250347</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-10T193401.800.webp?v=1781138064</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_81.webp?v=1780001979</t>
         </is>
       </c>
       <c r="L136" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
@@ -7802,11 +7802,11 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>10643473727798</v>
+        <v>10743245766966</v>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Pañitos Happy y Soft x40 | Limpieza Suave para Bebé</t>
+          <t>Cepillo Lengua Only Baby | FZ-121</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -7816,14 +7816,14 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower</t>
+          <t>Aseo y cuidado, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E137" s="3" t="n">
-        <v>4700</v>
+        <v>6000</v>
       </c>
       <c r="F137" s="3" t="n">
-        <v>6714</v>
+        <v>8571</v>
       </c>
       <c r="G137" s="2" t="inlineStr"/>
       <c r="H137" s="2" t="n">
@@ -7836,25 +7836,78 @@
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
+          <t>https://www.solobabys.com/products/cepillo-lengua-only-baby-fz-121</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-10T193401.800.webp?v=1781138064</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>10643473727798</v>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Pañitos Happy y Soft x40 | Limpieza Suave para Bebé</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Sin categoría</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Aseo y cuidado, Baby shower</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="n">
+        <v>4700</v>
+      </c>
+      <c r="F138" s="3" t="n">
+        <v>6714</v>
+      </c>
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
           <t>https://www.solobabys.com/products/panitos-happy-y-soft-x40-limpieza-suave-para-bebe</t>
         </is>
       </c>
-      <c r="K137" s="2" t="inlineStr">
+      <c r="K138" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/53.webp?v=1774121918</t>
         </is>
       </c>
-      <c r="L137" s="2" t="n">
+      <c r="L138" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M137" s="2" t="inlineStr">
+      <c r="M138" s="2" t="inlineStr">
         <is>
           <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M137"/>
+  <autoFilter ref="A1:M138"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7900,7 +7953,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C3" s="5" t="n"/>
       <c r="D3" s="5" t="n"/>
@@ -7912,7 +7965,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5">
@@ -7923,7 +7976,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-24 12:28</t>
+          <t>2026-10-24 18:25</t>
         </is>
       </c>
     </row>
@@ -8004,7 +8057,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7976,7 +7976,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-24 18:25</t>
+          <t>2026-10-25 00:30</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7976,7 +7976,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-25 00:30</t>
+          <t>2026-10-25 06:31</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7976,7 +7976,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-25 06:31</t>
+          <t>2026-10-25 12:28</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7976,7 +7976,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-25 12:28</t>
+          <t>2026-10-25 18:26</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7976,7 +7976,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-25 18:26</t>
+          <t>2026-10-26 00:43</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7976,7 +7976,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-26 00:43</t>
+          <t>2026-10-26 06:40</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7976,7 +7976,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-26 06:40</t>
+          <t>2026-10-26 14:42</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7976,7 +7976,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-26 14:42</t>
+          <t>2026-10-26 18:40</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$M$138</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$M$139</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M138"/>
+  <dimension ref="A1:M139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1193,11 +1193,11 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>10817883832630</v>
+        <v>15442618876214</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Gimnasio Colchoneta para Bebé | ABBA Ref. 1222</t>
+          <t>Perro Robot con Control Remoto | Acrobacias, Luces y Música</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1207,14 +1207,14 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Baby shower</t>
+          <t>Juguetes</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>155000</v>
+        <v>175000</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>221429</v>
+        <v>250000</v>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="n">
@@ -1227,30 +1227,30 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/gimnasio-colchoneta-para-bebe-abba-ref-1222</t>
+          <t>https://www.solobabys.com/products/perro-robot-con-control-remoto-acrobacias-luces-y-musica</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-08-19T192609.971.webp?v=1787185623</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/perro-robot-1.jpg?v=1793052017</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-title { font-family: 'Fraunces', serif; font-size: 38px; line-height: 1.1; color: #00afba; margin: 0 0 15px 0; letter-spacin</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>10650840990006</v>
+        <v>10817883832630</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Tetero Avent Natural 9oz x 2 | Alimentación Natural para Bebé</t>
+          <t>Gimnasio Colchoneta para Bebé | ABBA Ref. 1222</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Teteros, Baby shower</t>
+          <t>Juguetes, Baby shower</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
@@ -1280,16 +1280,16 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/tetero-avent-natural-9oz-x-2-alimentacion-natural-para-bebe</t>
+          <t>https://www.solobabys.com/products/gimnasio-colchoneta-para-bebe-abba-ref-1222</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/172369-800-auto.webp?v=1774883176</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-08-19T192609.971.webp?v=1787185623</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
@@ -1299,11 +1299,11 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>10849684193590</v>
+        <v>10650840990006</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Pañalera Morral Maternal Multifuncional</t>
+          <t>Tetero Avent Natural 9oz x 2 | Alimentación Natural para Bebé</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1313,22 +1313,18 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Pañaleras, Baby shower</t>
+          <t>Teteros, Baby shower</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>152000</v>
+        <v>155000</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>249900</v>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Beige', 'Azul', 'Rosa']</t>
-        </is>
-      </c>
+        <v>221429</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
@@ -1337,16 +1333,16 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/panalera-morral-maternal-multifuncional</t>
+          <t>https://www.solobabys.com/products/tetero-avent-natural-9oz-x-2-alimentacion-natural-para-bebe</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-11at4.58.19PM_1.webp?v=1789498706</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/172369-800-auto.webp?v=1774883176</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
@@ -1356,11 +1352,11 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>15397854937398</v>
+        <v>10849684193590</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Combo Cuidado Esencial para Bebé + Pañalera</t>
+          <t>Pañalera Morral Maternal Multifuncional</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1370,16 +1366,22 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Pañaleras, Combos</t>
+          <t>Pañaleras, Baby shower</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>145900</v>
-      </c>
-      <c r="F17" s="3" t="n"/>
-      <c r="G17" s="2" t="inlineStr"/>
+        <v>152000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>249900</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Beige', 'Azul', 'Rosa']</t>
+        </is>
+      </c>
       <c r="H17" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
@@ -1388,16 +1390,16 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/combo-cuidado-esencial-para-bebe-panalera</t>
+          <t>https://www.solobabys.com/products/panalera-morral-maternal-multifuncional</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ImagendeCodex28sept2026_07_21_50.webp?v=1790598153</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-11at4.58.19PM_1.webp?v=1789498706</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
@@ -1407,11 +1409,11 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>10849651917110</v>
+        <v>15397854937398</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Pañalera Multifuncional Tipo Morral</t>
+          <t>Combo Cuidado Esencial para Bebé + Pañalera</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1421,22 +1423,16 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Pañaleras, Baby shower</t>
+          <t>Aseo y cuidado, Pañaleras, Combos</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>145000</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>207143</v>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Rosa', 'Negro', 'Marrón']</t>
-        </is>
-      </c>
+        <v>145900</v>
+      </c>
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
@@ -1445,16 +1441,16 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/panalera-multifuncional-tipo-morral</t>
+          <t>https://www.solobabys.com/products/combo-cuidado-esencial-para-bebe-panalera</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-11at1.08.31PM_1.webp?v=1789498706</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ImagendeCodex28sept2026_07_21_50.webp?v=1790598153</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
@@ -1464,11 +1460,11 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>10830427783478</v>
+        <v>10849651917110</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Set de Bloques Didácticos DIY | 45 Piezas</t>
+          <t>Pañalera Multifuncional Tipo Morral</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1478,7 +1474,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Baby shower</t>
+          <t>Pañaleras, Baby shower</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
@@ -1487,9 +1483,13 @@
       <c r="F19" s="3" t="n">
         <v>207143</v>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Rosa', 'Negro', 'Marrón']</t>
+        </is>
+      </c>
       <c r="H19" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
@@ -1498,16 +1498,16 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/set-de-bloques-didacticos-diy-45-piezas</t>
+          <t>https://www.solobabys.com/products/panalera-multifuncional-tipo-morral</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-09-02T114133.522.webp?v=1788367308</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-11at1.08.31PM_1.webp?v=1789498706</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
@@ -1517,11 +1517,11 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>10854039060790</v>
+        <v>10830427783478</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Set de Nacimiento Bordado Jirafas</t>
+          <t>Set de Bloques Didácticos DIY | 45 Piezas</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1531,22 +1531,18 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Recién nacido, Ropa, Baby shower</t>
+          <t>Juguetes, Baby shower</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>138000</v>
+        <v>145000</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>197143</v>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>Talla: ['Recién nacido', '0-3 meses', '3-6 meses']</t>
-        </is>
-      </c>
+        <v>207143</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
@@ -1555,16 +1551,16 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/set-de-nacimiento-bordado-jirafas</t>
+          <t>https://www.solobabys.com/products/set-de-bloques-didacticos-diy-45-piezas</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-17at11.22.46AM.webp?v=1789685914</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-09-02T114133.522.webp?v=1788367308</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
@@ -1574,11 +1570,11 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>10621948526902</v>
+        <v>10854039060790</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Porta bebé Ergonómico con Asiento</t>
+          <t>Set de Nacimiento Bordado Jirafas</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1588,18 +1584,22 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Paseo y descanso</t>
+          <t>Recién nacido, Ropa, Baby shower</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>132500</v>
+        <v>138000</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>189286</v>
-      </c>
-      <c r="G21" s="2" t="inlineStr"/>
+        <v>197143</v>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Talla: ['Recién nacido', '0-3 meses', '3-6 meses']</t>
+        </is>
+      </c>
       <c r="H21" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
@@ -1608,16 +1608,16 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/cargador-nbsp-portabebe-ergonomico-con-asiento</t>
+          <t>https://www.solobabys.com/products/set-de-nacimiento-bordado-jirafas</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/5421F9F9-A984-48AA-98AA-AB826B5CF25F.webp?v=1773265452</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-17at11.22.46AM.webp?v=1789685914</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
@@ -1627,11 +1627,11 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>10854015598902</v>
+        <v>10621948526902</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Montable Retro Tipo Cargador con Luces y Sonido</t>
+          <t>Porta bebé Ergonómico con Asiento</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1641,14 +1641,14 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Juguetes</t>
+          <t>Paseo y descanso</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>113000</v>
+        <v>132500</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>161429</v>
+        <v>189286</v>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="n">
@@ -1661,16 +1661,16 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/montable-retro-tipo-cargador-con-luces-y-sonido</t>
+          <t>https://www.solobabys.com/products/cargador-nbsp-portabebe-ergonomico-con-asiento</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-17at1.14.04PM_1.webp?v=1789685014</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/5421F9F9-A984-48AA-98AA-AB826B5CF25F.webp?v=1773265452</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
@@ -1680,11 +1680,11 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>10696909914422</v>
+        <v>10854015598902</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Escalera para baño entrenamiento niños</t>
+          <t>Montable Retro Tipo Cargador con Luces y Sonido</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1694,40 +1694,36 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Bacinillas, Más vendidos</t>
+          <t>Juguetes</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>103000</v>
+        <v>113000</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>161429</v>
       </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Rosa', 'azul', 'Blanco']</t>
-        </is>
-      </c>
+      <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.solobabys.com/products/montable-retro-tipo-cargador-con-luces-y-sonido</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-17at1.14.04PM_1.webp?v=1789685014</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>https://www.solobabys.com/products/escalera-para-bano-entrenamiento-ninos</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/reductorinodoroinfantil_30993cd3-7d9a-4b62-becf-bade5606efe9.webp?v=1777927810</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="n">
-        <v>4</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
@@ -1737,11 +1733,11 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>10851679928630</v>
+        <v>10696909914422</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Tapete Maleta Plegable 2 m x 1.80 m</t>
+          <t>Escalera para baño entrenamiento niños</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1751,18 +1747,22 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Paseo y descanso, Baby shower</t>
+          <t>Bacinillas, Más vendidos</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>112000</v>
+        <v>103000</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G24" s="2" t="inlineStr"/>
+        <v>161429</v>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Rosa', 'azul', 'Blanco']</t>
+        </is>
+      </c>
       <c r="H24" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/tapete-maleta-plegable-2-m-x-1-80-m</t>
+          <t>https://www.solobabys.com/products/escalera-para-bano-entrenamiento-ninos</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-16at4.01.44PM.webp?v=1789597965</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/reductorinodoroinfantil_30993cd3-7d9a-4b62-becf-bade5606efe9.webp?v=1777927810</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
@@ -1790,11 +1790,11 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>10817110081846</v>
+        <v>10851679928630</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Bacín Infantil Tipo Inodoro con Sonido</t>
+          <t>Tapete Maleta Plegable 2 m x 1.80 m</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1804,14 +1804,14 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Bacinillas, Baby shower, Más vendidos</t>
+          <t>Paseo y descanso, Baby shower</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>110000</v>
+        <v>112000</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>150000</v>
+        <v>160000</v>
       </c>
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="n">
@@ -1824,16 +1824,16 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/bacin-infantil-tipo-inodoro-con-sonido</t>
+          <t>https://www.solobabys.com/products/tapete-maleta-plegable-2-m-x-1-80-m</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Imagen_de_Codex_24_sept_2026_05_21_38.webp?v=1790245357</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-16at4.01.44PM.webp?v=1789597965</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
@@ -1843,11 +1843,11 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>10585832292662</v>
+        <v>10817110081846</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Gimnasio Piano Musical | Multisensorial para Bebé</t>
+          <t>Bacín Infantil Tipo Inodoro con Sonido</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1857,14 +1857,14 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Más vendidos</t>
+          <t>Bacinillas, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>104000</v>
+        <v>110000</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>148571</v>
+        <v>150000</v>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="n">
@@ -1877,16 +1877,16 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/gimnasio-piano-musical-multisensorial-para-bebe</t>
+          <t>https://www.solobabys.com/products/bacin-infantil-tipo-inodoro-con-sonido</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-16at3.23.14PM_2.webp?v=1789592173</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Imagen_de_Codex_24_sept_2026_05_21_38.webp?v=1790245357</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
@@ -1896,11 +1896,11 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>10854058983734</v>
+        <v>10585832292662</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Set de Nacimiento Rosado con Moños y Corazones</t>
+          <t>Gimnasio Piano Musical | Multisensorial para Bebé</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1910,14 +1910,14 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Recién nacido, Ropa</t>
+          <t>Juguetes, Más vendidos</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>100000</v>
+        <v>104000</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>142857</v>
+        <v>148571</v>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="n">
@@ -1930,16 +1930,16 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/set-de-nacimiento-rosado-con-monos-y-corazones</t>
+          <t>https://www.solobabys.com/products/gimnasio-piano-musical-multisensorial-para-bebe</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-17at11.21.16AM.webp?v=1789687068</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-16at3.23.14PM_2.webp?v=1789592173</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
@@ -1949,11 +1949,11 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>10854045253942</v>
+        <v>10854058983734</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Set de Nacimiento Azul con Jirafas</t>
+          <t>Set de Nacimiento Rosado con Moños y Corazones</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>96000</v>
+        <v>100000</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>137143</v>
+        <v>142857</v>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="n">
@@ -1983,12 +1983,12 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/set-de-nacimiento-azul-con-jirafas</t>
+          <t>https://www.solobabys.com/products/set-de-nacimiento-rosado-con-monos-y-corazones</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-17at11.21.55AM_1.webp?v=1789686432</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-17at11.21.16AM.webp?v=1789687068</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
@@ -2002,11 +2002,11 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>10871386308918</v>
+        <v>10854045253942</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Casa de Muñecas Dream Villa 137 Piezas</t>
+          <t>Set de Nacimiento Azul con Jirafas</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2016,14 +2016,14 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Juguetes</t>
+          <t>Recién nacido, Ropa</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>95000</v>
+        <v>96000</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>135000</v>
+        <v>137143</v>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="n">
@@ -2036,12 +2036,12 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/casa-de-munecas-dream-villa-137-piezas</t>
+          <t>https://www.solobabys.com/products/set-de-nacimiento-azul-con-jirafas</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-24at5.37.31PM.webp?v=1790363242</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-17at11.21.55AM_1.webp?v=1789686432</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
@@ -2055,11 +2055,11 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>10643033653558</v>
+        <v>10871386308918</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Extractor de Leche Eléctrico Only Baby | HENA245</t>
+          <t>Casa de Muñecas Dream Villa 137 Piezas</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2069,40 +2069,36 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Lactancia, Baby shower</t>
+          <t>Juguetes</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
         <v>95000</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>124000</v>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Azul', 'Blanco', 'Rosa']</t>
-        </is>
-      </c>
+        <v>135000</v>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.solobabys.com/products/casa-de-munecas-dream-villa-137-piezas</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-24at5.37.31PM.webp?v=1790363242</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>https://www.solobabys.com/products/extractor-de-leche-electrico-only-baby-portatil-y-practico</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_76.webp?v=1780002422</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="n">
-        <v>4</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
@@ -2112,11 +2108,11 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>10730112876854</v>
+        <v>10643033653558</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Combo Todo para Bebé</t>
+          <t>Extractor de Leche Eléctrico Only Baby | HENA245</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2126,20 +2122,22 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Accesorios, Combos, Baby shower, Más vendidos</t>
+          <t>Lactancia, Baby shower</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>93400</v>
-      </c>
-      <c r="F31" s="3" t="n"/>
+        <v>95000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>124000</v>
+      </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Color: ['Rosa', 'azul']</t>
+          <t>Color: ['Azul', 'Blanco', 'Rosa']</t>
         </is>
       </c>
       <c r="H31" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
@@ -2148,16 +2146,16 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/combo-todo-para-bebe</t>
+          <t>https://www.solobabys.com/products/extractor-de-leche-electrico-only-baby-portatil-y-practico</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_-_2026-06-02T202102.310.webp?v=1780449734</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_76.webp?v=1780002422</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
@@ -2167,11 +2165,11 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>10829212647734</v>
+        <v>10730112876854</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Set de Alimentación para Muñeca | My Doll Feeding Set</t>
+          <t>Combo Todo para Bebé</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2181,18 +2179,20 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Juguetes</t>
+          <t>Accesorios, Combos, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>92000</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>131429</v>
-      </c>
-      <c r="G32" s="2" t="inlineStr"/>
+        <v>93400</v>
+      </c>
+      <c r="F32" s="3" t="n"/>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Rosa', 'azul']</t>
+        </is>
+      </c>
       <c r="H32" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
@@ -2201,16 +2201,16 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/set-de-alimentacion-para-muneca-my-doll-feeding-set</t>
+          <t>https://www.solobabys.com/products/combo-todo-para-bebe</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-08-31T172850.056.webp?v=1788215512</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_-_2026-06-02T202102.310.webp?v=1780449734</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
@@ -2220,11 +2220,11 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>10761980608822</v>
+        <v>10829212647734</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Set de Ropa para Bebé</t>
+          <t>Set de Alimentación para Muñeca | My Doll Feeding Set</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Ropa, Baby shower</t>
+          <t>Juguetes</t>
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>91000</v>
+        <v>92000</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>130000</v>
+        <v>131429</v>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="n">
@@ -2254,12 +2254,12 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/set-de-ropa-para-bebe-1</t>
+          <t>https://www.solobabys.com/products/set-de-alimentacion-para-muneca-my-doll-feeding-set</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage1jul2026_11_22_57a.m.webp?v=1782923165</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-08-31T172850.056.webp?v=1788215512</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
@@ -2273,11 +2273,11 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>10621946069302</v>
+        <v>10761980608822</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Pañalera con Cambiador Morral Maternal Multifuncional</t>
+          <t>Set de Ropa para Bebé</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2287,14 +2287,14 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Pañaleras, Baby shower</t>
+          <t>Ropa, Baby shower</t>
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>89900</v>
+        <v>91000</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>11000</v>
+        <v>130000</v>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="n">
@@ -2307,12 +2307,12 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/panalera-con-cambiador</t>
+          <t>https://www.solobabys.com/products/set-de-ropa-para-bebe-1</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/D_NQ_NP_683831-MCO82656835888_032025-O.webp?v=1773264515</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage1jul2026_11_22_57a.m.webp?v=1782923165</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
@@ -2326,11 +2326,11 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>15407815328054</v>
+        <v>10621946069302</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Set de Teteros Only Baby</t>
+          <t>Pañalera con Cambiador Morral Maternal Multifuncional</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2340,14 +2340,14 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Teteros</t>
+          <t>Pañaleras, Baby shower</t>
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>89000</v>
+        <v>89900</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>127000</v>
+        <v>11000</v>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="n">
@@ -2360,16 +2360,16 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/set-de-teteros-only-baby</t>
+          <t>https://www.solobabys.com/products/panalera-con-cambiador</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-10-03at3.50.29PM.webp?v=1791306639</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/D_NQ_NP_683831-MCO82656835888_032025-O.webp?v=1773264515</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
@@ -2379,11 +2379,11 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>10829207830838</v>
+        <v>15407815328054</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Carro Todo Terreno a Control Remoto | Power Cross Country</t>
+          <t>Set de Teteros Only Baby</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2393,14 +2393,14 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Juguetes</t>
+          <t>Teteros</t>
         </is>
       </c>
       <c r="E36" s="3" t="n">
         <v>89000</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>127143</v>
+        <v>127000</v>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="n">
@@ -2413,16 +2413,16 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/carro-todo-terreno-a-control-remoto-power-cross-country</t>
+          <t>https://www.solobabys.com/products/set-de-teteros-only-baby</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-08-31T164808.628.webp?v=1788213027</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-10-03at3.50.29PM.webp?v=1791306639</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
@@ -2432,11 +2432,11 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>10743176560950</v>
+        <v>10829207830838</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Combo Todo lo que tu Bebé Necesita</t>
+          <t>Carro Todo Terreno a Control Remoto | Power Cross Country</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2446,13 +2446,15 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Accesorios, Combos, Baby shower</t>
+          <t>Juguetes</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>88000</v>
-      </c>
-      <c r="F37" s="3" t="n"/>
+        <v>89000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>127143</v>
+      </c>
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="n">
         <v>1</v>
@@ -2464,16 +2466,16 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/combo-todo-lo-que-tu-bebe-necesita</t>
+          <t>https://www.solobabys.com/products/carro-todo-terreno-a-control-remoto-power-cross-country</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-10T181553.409.webp?v=1781133660</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-08-31T164808.628.webp?v=1788213027</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
@@ -2483,11 +2485,11 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>10761992995126</v>
+        <v>10743176560950</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Combo Cobija + Almohada + Cuellero</t>
+          <t>Combo Todo lo que tu Bebé Necesita</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2497,11 +2499,11 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Cobijas y toallas, Combos, Baby shower</t>
+          <t>Accesorios, Combos, Baby shower</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>86000</v>
+        <v>88000</v>
       </c>
       <c r="F38" s="3" t="n"/>
       <c r="G38" s="2" t="inlineStr"/>
@@ -2515,16 +2517,16 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/combo-cobija-almohada-cuellero</t>
+          <t>https://www.solobabys.com/products/combo-todo-lo-que-tu-bebe-necesita</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage1jul2026_11_54_36a.m.webp?v=1782924955</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-10T181553.409.webp?v=1781133660</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
@@ -2534,11 +2536,11 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>10651912470838</v>
+        <v>10761992995126</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Extractor Only DD-10 Eléctrico-Digital | Práctico y Cómodo para Mamá</t>
+          <t>Combo Cobija + Almohada + Cuellero</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2548,22 +2550,16 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Lactancia, Baby shower</t>
+          <t>Cobijas y toallas, Combos, Baby shower</t>
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>85000</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>121429</v>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Rosado', 'Blanco', 'Verde']</t>
-        </is>
-      </c>
+        <v>86000</v>
+      </c>
+      <c r="F39" s="3" t="n"/>
+      <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
@@ -2572,16 +2568,16 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/extractor-only-dd-10-electrico-digital-practico-y-comodo-para-mama</t>
+          <t>https://www.solobabys.com/products/combo-cobija-almohada-cuellero</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/EmbellecedordeProducto-bc293d22-69fd-47cb-9649-0ec341376f71.webp?v=1775062941</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage1jul2026_11_54_36a.m.webp?v=1782924955</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
@@ -2591,11 +2587,11 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>10862123548982</v>
+        <v>10651912470838</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Set de Camisetas Esqueleto para Bebé Vaquirín Baby</t>
+          <t>Extractor Only DD-10 Eléctrico-Digital | Práctico y Cómodo para Mamá</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2605,18 +2601,22 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Ropa, Baby shower</t>
+          <t>Lactancia, Baby shower</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>82000</v>
+        <v>85000</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>117143</v>
-      </c>
-      <c r="G40" s="2" t="inlineStr"/>
+        <v>121429</v>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Rosado', 'Blanco', 'Verde']</t>
+        </is>
+      </c>
       <c r="H40" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
@@ -2625,16 +2625,16 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/set-de-camisetas-esqueleto-para-bebe-vaquirin-baby</t>
+          <t>https://www.solobabys.com/products/extractor-only-dd-10-electrico-digital-practico-y-comodo-para-mama</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsApp_Image_2026-09-22_at_11.40.44_AM.webp?v=1790267534</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/EmbellecedordeProducto-bc293d22-69fd-47cb-9649-0ec341376f71.webp?v=1775062941</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
@@ -2644,11 +2644,11 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>10762514399542</v>
+        <v>10862123548982</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Nido para Bebé BBTOOS</t>
+          <t>Set de Camisetas Esqueleto para Bebé Vaquirín Baby</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2658,14 +2658,14 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Recién nacido, Paseo y descanso, Baby shower</t>
+          <t>Ropa, Baby shower</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>80500</v>
+        <v>82000</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>115000</v>
+        <v>117143</v>
       </c>
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="n">
@@ -2678,16 +2678,16 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/nido-para-bebe-bbtoos</t>
+          <t>https://www.solobabys.com/products/set-de-camisetas-esqueleto-para-bebe-vaquirin-baby</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage2jul2026_07_54_15a.m.webp?v=1782996905</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsApp_Image_2026-09-22_at_11.40.44_AM.webp?v=1790267534</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
@@ -2697,11 +2697,11 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>10869213462838</v>
+        <v>10762514399542</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Tren Dominó Automático con Luces y Música</t>
+          <t>Nido para Bebé BBTOOS</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2711,14 +2711,14 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Juguetes</t>
+          <t>Recién nacido, Paseo y descanso, Baby shower</t>
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>79900</v>
+        <v>80500</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>114143</v>
+        <v>115000</v>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="n">
@@ -2731,12 +2731,12 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/tren-domino-automatico-con-luces-y-musica</t>
+          <t>https://www.solobabys.com/products/nido-para-bebe-bbtoos</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-23at5.31.48PM.webp?v=1790210485</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage2jul2026_07_54_15a.m.webp?v=1782996905</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
@@ -2750,11 +2750,11 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>10869204517174</v>
+        <v>10869213462838</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Piano Didáctico Tigre con Luces y Sonidos</t>
+          <t>Tren Dominó Automático con Luces y Música</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2764,14 +2764,14 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Baby shower</t>
+          <t>Juguetes</t>
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>78000</v>
+        <v>79900</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>111429</v>
+        <v>114143</v>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="n">
@@ -2784,12 +2784,12 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/piano-didactico-tigre-con-luces-y-sonidos</t>
+          <t>https://www.solobabys.com/products/tren-domino-automatico-con-luces-y-musica</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-23at5.18.28PM_1.webp?v=1790209742</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-23at5.31.48PM.webp?v=1790210485</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
@@ -2803,11 +2803,11 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>10869220213046</v>
+        <v>10869204517174</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Piano Didáctico Vaquita con Luces y Sonidos</t>
+          <t>Piano Didáctico Tigre con Luces y Sonidos</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2817,14 +2817,14 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Más vendidos</t>
+          <t>Juguetes, Baby shower</t>
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>77900</v>
+        <v>78000</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>111000</v>
+        <v>111429</v>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="n">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/piano-didactico-vaquita-con-luces-y-sonidos</t>
+          <t>https://www.solobabys.com/products/piano-didactico-tigre-con-luces-y-sonidos</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-23at5.37.49PM.webp?v=1790210785</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-23at5.18.28PM_1.webp?v=1790209742</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
@@ -2856,11 +2856,11 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>10621944824118</v>
+        <v>10869220213046</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Pañalera Morral Maternal Multifuncional</t>
+          <t>Piano Didáctico Vaquita con Luces y Sonidos</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2870,14 +2870,14 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Pañaleras</t>
+          <t>Juguetes, Más vendidos</t>
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>72000</v>
+        <v>77900</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>102857</v>
+        <v>111000</v>
       </c>
       <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="n">
@@ -2890,16 +2890,16 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/panalera</t>
+          <t>https://www.solobabys.com/products/piano-didactico-vaquita-con-luces-y-sonidos</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/05066dca-4efe-4f3b-82f0-5f1396ef405d.webp?v=1773264220</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-23at5.37.49PM.webp?v=1790210785</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
@@ -2909,11 +2909,11 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>15407790293302</v>
+        <v>10621944824118</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Extractor de Leche Eléctrico Recargable</t>
+          <t>Pañalera Morral Maternal Multifuncional</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2923,20 +2923,18 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Recién nacido, Teteros, Lactancia</t>
+          <t>Pañaleras</t>
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>71000</v>
-      </c>
-      <c r="F46" s="3" t="n"/>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Verde', 'Rosa', 'Beige']</t>
-        </is>
-      </c>
+        <v>72000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>102857</v>
+      </c>
+      <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
@@ -2945,16 +2943,16 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/extractor-de-leche-electrico-recargable</t>
+          <t>https://www.solobabys.com/products/panalera</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-10-03at4.36.35PM_1.webp?v=1791305619</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/05066dca-4efe-4f3b-82f0-5f1396ef405d.webp?v=1773264220</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
@@ -2964,11 +2962,11 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>10621943972150</v>
+        <v>15407790293302</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Pañalera Morral Bolso Maternal Multifuncional</t>
+          <t>Extractor de Leche Eléctrico Recargable</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2978,18 +2976,20 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Pañaleras, Baby shower, Más vendidos</t>
+          <t>Recién nacido, Teteros, Lactancia</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>70000</v>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G47" s="2" t="inlineStr"/>
+        <v>71000</v>
+      </c>
+      <c r="F47" s="3" t="n"/>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Verde', 'Rosa', 'Beige']</t>
+        </is>
+      </c>
       <c r="H47" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
@@ -2998,16 +2998,16 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/panalera-morral</t>
+          <t>https://www.solobabys.com/products/extractor-de-leche-electrico-recargable</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/panaleramorral.webp?v=1773264032</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-10-03at4.36.35PM_1.webp?v=1791305619</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
@@ -3017,11 +3017,11 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>10651920302390</v>
+        <v>10621943972150</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>BACIN PRAKTIPLAS MONKEY</t>
+          <t>Pañalera Morral Bolso Maternal Multifuncional</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3031,14 +3031,14 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Bacinillas</t>
+          <t>Pañaleras, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>67000</v>
+        <v>70000</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>95714</v>
+        <v>100000</v>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="n">
@@ -3051,16 +3051,16 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/bacin-infantil-praktiplas-monkey</t>
+          <t>https://www.solobabys.com/products/panalera-morral</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla-2026-04-01T125046.533.webp?v=1775066022</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/panaleramorral.webp?v=1773264032</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
@@ -3070,11 +3070,11 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>15408113484086</v>
+        <v>10651920302390</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Tapete Piano Musical Infantil</t>
+          <t>BACIN PRAKTIPLAS MONKEY</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -3084,14 +3084,14 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Accesorios</t>
+          <t>Bacinillas</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>65000</v>
+        <v>67000</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>92900</v>
+        <v>95714</v>
       </c>
       <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="n">
@@ -3104,16 +3104,16 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/tapete-piano-musical-infantil</t>
+          <t>https://www.solobabys.com/products/bacin-infantil-praktiplas-monkey</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-10-02at4.36.40PM.webp?v=1791323260</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla-2026-04-01T125046.533.webp?v=1775066022</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
@@ -3123,11 +3123,11 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>10585812664630</v>
+        <v>15408113484086</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Pañalera Bebe Morral | Impermeable</t>
+          <t>Tapete Piano Musical Infantil</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3137,22 +3137,18 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Pañaleras, Baby shower</t>
+          <t>Accesorios</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
         <v>65000</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>92857</v>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Azul', 'Rosa', 'Verde']</t>
-        </is>
-      </c>
+        <v>92900</v>
+      </c>
+      <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
@@ -3161,16 +3157,16 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/panalera-bebe-morral-impermeable</t>
+          <t>https://www.solobabys.com/products/tapete-piano-musical-infantil</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/31269009-1200-auto.webp?v=1770595199</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-10-02at4.36.40PM.webp?v=1791323260</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
@@ -3180,11 +3176,11 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>10643479167286</v>
+        <v>10585812664630</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Set de Aseo Baby Care Kit Completo 20 Piezas</t>
+          <t>Pañalera Bebe Morral | Impermeable</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -3194,40 +3190,40 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado</t>
+          <t>Pañaleras, Baby shower</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
         <v>65000</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>79900</v>
+        <v>92857</v>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Color: ['Azul', 'Rosa']</t>
+          <t>Color: ['Azul', 'Rosa', 'Verde']</t>
         </is>
       </c>
       <c r="H51" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.solobabys.com/products/panalera-bebe-morral-impermeable</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/31269009-1200-auto.webp?v=1770595199</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="n">
         <v>2</v>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>https://www.solobabys.com/products/set-de-aseo-baby-care-kit-completo-20-piezas</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla_72.webp?v=1774561267</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="n">
-        <v>6</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
@@ -3237,11 +3233,11 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>10812588589366</v>
+        <v>10643479167286</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Abejita Bailarina Dancing Bee</t>
+          <t>Set de Aseo Baby Care Kit Completo 20 Piezas</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3251,18 +3247,22 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Baby shower, Más vendidos</t>
+          <t>Aseo y cuidado</t>
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>63000</v>
+        <v>65000</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>90000</v>
-      </c>
-      <c r="G52" s="2" t="inlineStr"/>
+        <v>79900</v>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Azul', 'Rosa']</t>
+        </is>
+      </c>
       <c r="H52" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
@@ -3271,16 +3271,16 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/abejita-bailarina-dancing-bee</t>
+          <t>https://www.solobabys.com/products/set-de-aseo-baby-care-kit-completo-20-piezas</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsApp_32.webp?v=1786662172</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla_72.webp?v=1774561267</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
@@ -3290,11 +3290,11 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>10817874559286</v>
+        <v>10812588589366</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Bañera para Bebé con Soporte Anatómico</t>
+          <t>Abejita Bailarina Dancing Bee</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3304,14 +3304,14 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower</t>
+          <t>Juguetes, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>62000</v>
+        <v>63000</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>88571</v>
+        <v>90000</v>
       </c>
       <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="2" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/banera-para-bebe-con-soporte-anatomico</t>
+          <t>https://www.solobabys.com/products/abejita-bailarina-dancing-bee</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-08-19T190108.179.webp?v=1787184104</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsApp_32.webp?v=1786662172</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
@@ -3343,11 +3343,11 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>10643571212598</v>
+        <v>10817874559286</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Pack x12 de medias con sonajero para bebé</t>
+          <t>Bañera para Bebé con Soporte Anatómico</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3357,14 +3357,14 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Ropa, Baby shower</t>
+          <t>Aseo y cuidado, Baby shower</t>
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>60000</v>
+        <v>62000</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>85714</v>
+        <v>88571</v>
       </c>
       <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="n">
@@ -3377,16 +3377,16 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/pack-de-medias-con-sonajero-para-bebe</t>
+          <t>https://www.solobabys.com/products/banera-para-bebe-con-soporte-anatomico</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla_91.webp?v=1774567784</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-08-19T190108.179.webp?v=1787184104</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
@@ -3396,11 +3396,11 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>10643570426166</v>
+        <v>10643571212598</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Media Tejido BB MX3-627</t>
+          <t>Pack x12 de medias con sonajero para bebé</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3410,14 +3410,14 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Ropa, Baby shower</t>
         </is>
       </c>
       <c r="E55" s="3" t="n">
         <v>60000</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>29900</v>
+        <v>85714</v>
       </c>
       <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="n">
@@ -3430,30 +3430,30 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/media-tejido-bb-mx3-627</t>
+          <t>https://www.solobabys.com/products/pack-de-medias-con-sonajero-para-bebe</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsApp_Image_2026-03-21_at_6.55.04_PM_1.jpg?v=1774564952</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla_91.webp?v=1774567784</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container{ font-family:'Quicksand',sans-serif; max-width:480px; margin:0 auto; color:#4a5568; padding:26px; background:#ffffff; } .b-rating{ display:flex; align-items:center; gap:8px; margin-bottom:12px; font-size:14px; font-weight:700; color:#c8d431; flex-wrap:wra</t>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>15407949349174</v>
+        <v>10643570426166</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Combo Lactancia Materna Only Baby</t>
+          <t>Media Tejido BB MX3-627</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3463,13 +3463,15 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Teteros, Alimentación, Combos</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v>59900</v>
-      </c>
-      <c r="F56" s="3" t="n"/>
+        <v>60000</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>29900</v>
+      </c>
       <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="2" t="n">
         <v>1</v>
@@ -3481,30 +3483,30 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/combo-lactancia-materna-only-baby</t>
+          <t>https://www.solobabys.com/products/media-tejido-bb-mx3-627</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-10-01at11.33.07AM.webp?v=1791314681</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsApp_Image_2026-03-21_at_6.55.04_PM_1.jpg?v=1774564952</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container{ font-family:'Quicksand',sans-serif; max-width:480px; margin:0 auto; color:#4a5568; padding:26px; background:#ffffff; } .b-rating{ display:flex; align-items:center; gap:8px; margin-bottom:12px; font-size:14px; font-weight:700; color:#c8d431; flex-wrap:wra</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>10813212197174</v>
+        <v>15407949349174</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>COBIJA BURBUJA ESTAMPADA Y ALMOHADAS</t>
+          <t>Combo Lactancia Materna Only Baby</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3514,11 +3516,11 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Cobijas y toallas, Baby shower, Más vendidos</t>
+          <t>Teteros, Alimentación, Combos</t>
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>59000</v>
+        <v>59900</v>
       </c>
       <c r="F57" s="3" t="n"/>
       <c r="G57" s="2" t="inlineStr"/>
@@ -3532,16 +3534,16 @@
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/cobija-burbuja-stpada-y-almohadas</t>
+          <t>https://www.solobabys.com/products/combo-lactancia-materna-only-baby</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-08-14T175108.874.webp?v=1786747890</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-10-01at11.33.07AM.webp?v=1791314681</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
@@ -3551,11 +3553,11 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>15397792940342</v>
+        <v>10813212197174</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Elefante Musical con Luces y Pelotas Flotantes</t>
+          <t>COBIJA BURBUJA ESTAMPADA Y ALMOHADAS</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3565,15 +3567,13 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Juguetes</t>
+          <t>Cobijas y toallas, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E58" s="3" t="n">
-        <v>58900</v>
-      </c>
-      <c r="F58" s="3" t="n">
-        <v>84000</v>
-      </c>
+        <v>59000</v>
+      </c>
+      <c r="F58" s="3" t="n"/>
       <c r="G58" s="2" t="inlineStr"/>
       <c r="H58" s="2" t="n">
         <v>1</v>
@@ -3585,16 +3585,16 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/elefante-musical-con-luces-y-pelotas-flotantes</t>
+          <t>https://www.solobabys.com/products/cobija-burbuja-stpada-y-almohadas</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-26at5.27.17PM.webp?v=1790596404</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-08-14T175108.874.webp?v=1786747890</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
@@ -3604,11 +3604,11 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>10871389880630</v>
+        <v>15397792940342</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Piano Didáctico Mariposa con Luces y Sonidos</t>
+          <t>Elefante Musical con Luces y Pelotas Flotantes</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3622,10 +3622,10 @@
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>56000</v>
+        <v>58900</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>80000</v>
+        <v>84000</v>
       </c>
       <c r="G59" s="2" t="inlineStr"/>
       <c r="H59" s="2" t="n">
@@ -3638,16 +3638,16 @@
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/piano-didactico-mariposa-con-luces-y-sonidos</t>
+          <t>https://www.solobabys.com/products/elefante-musical-con-luces-y-pelotas-flotantes</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-24at5.47.49PM.webp?v=1790363588</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-26at5.27.17PM.webp?v=1790596404</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
@@ -3657,11 +3657,11 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>10746777862454</v>
+        <v>10871389880630</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Combo Protección y Seguridad para Bebé</t>
+          <t>Piano Didáctico Mariposa con Luces y Sonidos</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3671,34 +3671,36 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Accesorios, Combos, Baby shower, Más vendidos</t>
+          <t>Juguetes</t>
         </is>
       </c>
       <c r="E60" s="3" t="n">
         <v>56000</v>
       </c>
-      <c r="F60" s="3" t="n"/>
+      <c r="F60" s="3" t="n">
+        <v>80000</v>
+      </c>
       <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/combo-proteccion-y-seguridad-para-bebe</t>
+          <t>https://www.solobabys.com/products/piano-didactico-mariposa-con-luces-y-sonidos</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/9943c8dc-e899-4b4f-9743-01890aeaf845.webp?v=1781635738</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-24at5.47.49PM.webp?v=1790363588</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
@@ -3708,11 +3710,11 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>10730141974838</v>
+        <v>10746777862454</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Tetero Only 11 Onzas | A1DJ</t>
+          <t>Combo Protección y Seguridad para Bebé</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3722,36 +3724,34 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Teteros</t>
+          <t>Accesorios, Combos, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E61" s="3" t="n">
-        <v>55000</v>
-      </c>
-      <c r="F61" s="3" t="n">
-        <v>40000</v>
-      </c>
+        <v>56000</v>
+      </c>
+      <c r="F61" s="3" t="n"/>
       <c r="G61" s="2" t="inlineStr"/>
       <c r="H61" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/tetero-only-11-onzas-a1dj</t>
+          <t>https://www.solobabys.com/products/combo-proteccion-y-seguridad-para-bebe</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_93.webp?v=1780178551</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/9943c8dc-e899-4b4f-9743-01890aeaf845.webp?v=1781635738</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
@@ -3761,11 +3761,11 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>10762038378806</v>
+        <v>10730141974838</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Vajilla en Silicona para Bebé</t>
+          <t>Tetero Only 11 Onzas | A1DJ</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3775,14 +3775,14 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Alimentación, Baby shower, Más vendidos</t>
+          <t>Teteros</t>
         </is>
       </c>
       <c r="E62" s="3" t="n">
         <v>55000</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>78571</v>
+        <v>40000</v>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="n">
@@ -3795,30 +3795,30 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/vajilla-en-silicona-para-bebe</t>
+          <t>https://www.solobabys.com/products/tetero-only-11-onzas-a1dj</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage1jul2026_01_13_14p.m.webp?v=1782929663</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_93.webp?v=1780178551</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>```html @import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color</t>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>15397818728758</v>
+        <v>10762038378806</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Delfín Musical con Pelota Flotante</t>
+          <t>Vajilla en Silicona para Bebé</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3828,14 +3828,14 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Juguetes</t>
+          <t>Alimentación, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E63" s="3" t="n">
-        <v>54000</v>
+        <v>55000</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>77000</v>
+        <v>78571</v>
       </c>
       <c r="G63" s="2" t="inlineStr"/>
       <c r="H63" s="2" t="n">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/delfin-musical-con-pelota-flotante</t>
+          <t>https://www.solobabys.com/products/vajilla-en-silicona-para-bebe</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-26at5.11.21PM_1.webp?v=1790597093</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage1jul2026_01_13_14p.m.webp?v=1782929663</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
@@ -3861,17 +3861,17 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
+          <t>```html @import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>10800174727478</v>
+        <v>15397818728758</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>BACIN PRAKTIPLAS TRONO</t>
+          <t>Delfín Musical con Pelota Flotante</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3881,14 +3881,14 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Bacinillas, Más vendidos</t>
+          <t>Juguetes</t>
         </is>
       </c>
       <c r="E64" s="3" t="n">
-        <v>50500</v>
+        <v>54000</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>72143</v>
+        <v>77000</v>
       </c>
       <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="n">
@@ -3901,16 +3901,16 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/bacin-praktiplas-trono</t>
+          <t>https://www.solobabys.com/products/delfin-musical-con-pelota-flotante</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-08-05T163918.997.webp?v=1785966083</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-26at5.11.21PM_1.webp?v=1790597093</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
@@ -3920,11 +3920,11 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>15397872009526</v>
+        <v>10800174727478</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Combo Lonchera Infantil + Termo</t>
+          <t>BACIN PRAKTIPLAS TRONO</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3934,13 +3934,15 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Alimentación, Combos</t>
+          <t>Bacinillas, Más vendidos</t>
         </is>
       </c>
       <c r="E65" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="F65" s="3" t="n"/>
+        <v>50500</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>72143</v>
+      </c>
       <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="2" t="n">
         <v>1</v>
@@ -3952,16 +3954,16 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/combo-lonchera-infantil-termo</t>
+          <t>https://www.solobabys.com/products/bacin-praktiplas-trono</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ImagendeCodex28sept2026_07_26_32.webp?v=1790598866</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-08-05T163918.997.webp?v=1785966083</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
@@ -3971,11 +3973,11 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>10642848547126</v>
+        <v>15397872009526</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>BACIN PRAKTIPLAS LOCO</t>
+          <t>Combo Lonchera Infantil + Termo</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3985,22 +3987,16 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Bacinillas, Accesorios, Baby shower, Más vendidos</t>
+          <t>Alimentación, Combos</t>
         </is>
       </c>
       <c r="E66" s="3" t="n">
         <v>50000</v>
       </c>
-      <c r="F66" s="3" t="n">
-        <v>67000</v>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Azul', 'Verde', 'Rosa']</t>
-        </is>
-      </c>
+      <c r="F66" s="3" t="n"/>
+      <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
@@ -4009,16 +4005,16 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/bacin-loco-2-en-1-prakti-plas-linea-infantil</t>
+          <t>https://www.solobabys.com/products/combo-lonchera-infantil-termo</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/D_Q_NP_2X_753134-MCO90831803976_082025-P.webp?v=1774026320</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ImagendeCodex28sept2026_07_26_32.webp?v=1790598866</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
@@ -4028,11 +4024,11 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>15404831867190</v>
+        <v>10642848547126</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Set Lavateros + Tetero Only Baby 10 oz</t>
+          <t>BACIN PRAKTIPLAS LOCO</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -4042,22 +4038,22 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Teteros, Combos</t>
+          <t>Bacinillas, Accesorios, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E67" s="3" t="n">
-        <v>49900</v>
+        <v>50000</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>71000</v>
+        <v>67000</v>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Color: ['Púrpura', 'Rosa']</t>
+          <t>Color: ['Azul', 'Verde', 'Rosa']</t>
         </is>
       </c>
       <c r="H67" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
@@ -4066,12 +4062,12 @@
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/set-lavateros-tetero-only-baby-10-oz</t>
+          <t>https://www.solobabys.com/products/bacin-loco-2-en-1-prakti-plas-linea-infantil</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-10-01at11.08.04AM.webp?v=1790975971</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/D_Q_NP_2X_753134-MCO90831803976_082025-P.webp?v=1774026320</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
@@ -4085,11 +4081,11 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>15401647800630</v>
+        <v>15404831867190</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Combo Lonchera Completa + Pañitos Húmedos</t>
+          <t>Set Lavateros + Tetero Only Baby 10 oz</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -4099,16 +4095,22 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Alimentación, Combos</t>
+          <t>Teteros, Combos</t>
         </is>
       </c>
       <c r="E68" s="3" t="n">
         <v>49900</v>
       </c>
-      <c r="F68" s="3" t="n"/>
-      <c r="G68" s="2" t="inlineStr"/>
+      <c r="F68" s="3" t="n">
+        <v>71000</v>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Púrpura', 'Rosa']</t>
+        </is>
+      </c>
       <c r="H68" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
@@ -4117,16 +4119,16 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/combo-lonchera-completa-panitos-humedos</t>
+          <t>https://www.solobabys.com/products/set-lavateros-tetero-only-baby-10-oz</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-29at3.06.15PM.webp?v=1790716209</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-10-01at11.08.04AM.webp?v=1790975971</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
@@ -4136,11 +4138,11 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>10851622256950</v>
+        <v>15401647800630</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Medusa Bailarina con Luces y Música</t>
+          <t>Combo Lonchera Completa + Pañitos Húmedos</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -4150,15 +4152,13 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Más vendidos</t>
+          <t>Aseo y cuidado, Alimentación, Combos</t>
         </is>
       </c>
       <c r="E69" s="3" t="n">
-        <v>49000</v>
-      </c>
-      <c r="F69" s="3" t="n">
-        <v>70000</v>
-      </c>
+        <v>49900</v>
+      </c>
+      <c r="F69" s="3" t="n"/>
       <c r="G69" s="2" t="inlineStr"/>
       <c r="H69" s="2" t="n">
         <v>1</v>
@@ -4170,16 +4170,16 @@
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/medusa-bailarina-con-luces-y-musica</t>
+          <t>https://www.solobabys.com/products/combo-lonchera-completa-panitos-humedos</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-15at6.13.47PM_1_1.webp?v=1789584498</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-29at3.06.15PM.webp?v=1790716209</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
@@ -4189,11 +4189,11 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>10819649962294</v>
+        <v>10851622256950</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Carro Transformable en Robot Classic</t>
+          <t>Medusa Bailarina con Luces y Música</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Baby shower</t>
+          <t>Juguetes, Más vendidos</t>
         </is>
       </c>
       <c r="E70" s="3" t="n">
@@ -4223,16 +4223,16 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/carro-transformable-en-robot-classic</t>
+          <t>https://www.solobabys.com/products/medusa-bailarina-con-luces-y-musica</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-08-21T170448.131.webp?v=1787349923</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-15at6.13.47PM_1_1.webp?v=1789584498</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
@@ -4242,11 +4242,11 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>10762351051062</v>
+        <v>10819649962294</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>SONAJERO HAPPY MONKEY | 168278-6 ANIMALES</t>
+          <t>Carro Transformable en Robot Classic</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4260,10 +4260,10 @@
         </is>
       </c>
       <c r="E71" s="3" t="n">
-        <v>48000</v>
+        <v>49000</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>68571</v>
+        <v>70000</v>
       </c>
       <c r="G71" s="2" t="inlineStr"/>
       <c r="H71" s="2" t="n">
@@ -4276,16 +4276,16 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/sonajero-de-peluche-para-bebe</t>
+          <t>https://www.solobabys.com/products/carro-transformable-en-robot-classic</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage1jul2026_11_15_15p.m.webp?v=1782965757</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-08-21T170448.131.webp?v=1787349923</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
@@ -4295,11 +4295,11 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>10849657192758</v>
+        <v>10762351051062</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Lima Eléctrica para Uñas de Bebé</t>
+          <t>SONAJERO HAPPY MONKEY | 168278-6 ANIMALES</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4309,14 +4309,14 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado</t>
+          <t>Juguetes, Baby shower</t>
         </is>
       </c>
       <c r="E72" s="3" t="n">
-        <v>47000</v>
+        <v>48000</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>67143</v>
+        <v>68571</v>
       </c>
       <c r="G72" s="2" t="inlineStr"/>
       <c r="H72" s="2" t="n">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/lima-electrica-para-unas-de-bebe</t>
+          <t>https://www.solobabys.com/products/sonajero-de-peluche-para-bebe</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage15sept2026_14_09_36.webp?v=1789499433</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage1jul2026_11_15_15p.m.webp?v=1782965757</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
@@ -4348,11 +4348,11 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>10819647668534</v>
+        <v>10849657192758</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Mascota de Peluche Interactiva con Maletín | Lovely Pet</t>
+          <t>Lima Eléctrica para Uñas de Bebé</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Baby shower</t>
+          <t>Aseo y cuidado</t>
         </is>
       </c>
       <c r="E73" s="3" t="n">
@@ -4382,16 +4382,16 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/mascota-de-peluche-interactiva-con-maletin-lovely-pet</t>
+          <t>https://www.solobabys.com/products/lima-electrica-para-unas-de-bebe</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-08-21T164918.946.webp?v=1787349005</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage15sept2026_14_09_36.webp?v=1789499433</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
@@ -4401,11 +4401,11 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>10726814023990</v>
+        <v>10819647668534</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Plato + Cuchara Siliconada Cangrejo</t>
+          <t>Mascota de Peluche Interactiva con Maletín | Lovely Pet</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4415,14 +4415,14 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Alimentación, Baby shower</t>
+          <t>Juguetes, Baby shower</t>
         </is>
       </c>
       <c r="E74" s="3" t="n">
-        <v>46200</v>
+        <v>47000</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>66000</v>
+        <v>67143</v>
       </c>
       <c r="G74" s="2" t="inlineStr"/>
       <c r="H74" s="2" t="n">
@@ -4435,16 +4435,16 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/plato-cuchara-siliconada-cangrejo</t>
+          <t>https://www.solobabys.com/products/mascota-de-peluche-interactiva-con-maletin-lovely-pet</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_57.webp?v=1779816409</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-08-21T164918.946.webp?v=1787349005</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
@@ -4454,11 +4454,11 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>15439275786550</v>
+        <v>10726814023990</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Perrito con Movimiento, Luz y Sonido | Camina Solito</t>
+          <t>Plato + Cuchara Siliconada Cangrejo</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -4468,11 +4468,11 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Juguetes</t>
+          <t>Alimentación, Baby shower</t>
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>46000</v>
+        <v>46200</v>
       </c>
       <c r="F75" s="3" t="n">
         <v>66000</v>
@@ -4488,30 +4488,30 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/perrito-con-movimiento-luz-y-sonido-camina-solito</t>
+          <t>https://www.solobabys.com/products/plato-cuchara-siliconada-cangrejo</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/perrito-luz-sonido-1.jpg?v=1792866073</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_57.webp?v=1779816409</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-title { font-family: 'Fraunces', serif; font-size: 38px; line-height: 1.1; color: #00afba; margin: 0 0 15px 0; letter-spacin</t>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>10819653271862</v>
+        <v>15439275786550</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Camión Transformable en Robot 2 en 1 | Super Change Truck</t>
+          <t>Perrito con Movimiento, Luz y Sonido | Camina Solito</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4521,14 +4521,14 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Baby shower</t>
+          <t>Juguetes</t>
         </is>
       </c>
       <c r="E76" s="3" t="n">
         <v>46000</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>65714</v>
+        <v>66000</v>
       </c>
       <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="2" t="n">
@@ -4541,30 +4541,30 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/camion-transformable-en-robot-2-en-1-super-change-truck</t>
+          <t>https://www.solobabys.com/products/perrito-con-movimiento-luz-y-sonido-camina-solito</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-08-21T172546.714.webp?v=1787351184</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/perrito-luz-sonido-1.jpg?v=1792866073</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-title { font-family: 'Fraunces', serif; font-size: 38px; line-height: 1.1; color: #00afba; margin: 0 0 15px 0; letter-spacin</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>15407841476918</v>
+        <v>10819653271862</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Combo Plato 360° Antiderrames + Babero de Silicona</t>
+          <t>Camión Transformable en Robot 2 en 1 | Super Change Truck</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -4574,13 +4574,15 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Alimentación, Combos</t>
+          <t>Juguetes, Baby shower</t>
         </is>
       </c>
       <c r="E77" s="3" t="n">
-        <v>45000</v>
-      </c>
-      <c r="F77" s="3" t="n"/>
+        <v>46000</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>65714</v>
+      </c>
       <c r="G77" s="2" t="inlineStr"/>
       <c r="H77" s="2" t="n">
         <v>1</v>
@@ -4592,16 +4594,16 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/combo-plato-360-antiderrames-babero-de-silicona</t>
+          <t>https://www.solobabys.com/products/camion-transformable-en-robot-2-en-1-super-change-truck</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-29at3.32.35PM.webp?v=1791307237</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-08-21T172546.714.webp?v=1787351184</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
@@ -4611,11 +4613,11 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>10735539552566</v>
+        <v>15407841476918</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Semanario Mi Ropita 322-002 Sacos</t>
+          <t>Combo Plato 360° Antiderrames + Babero de Silicona</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -4625,11 +4627,11 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Recién nacido, Ropa, Baby shower, Más vendidos</t>
+          <t>Aseo y cuidado, Alimentación, Combos</t>
         </is>
       </c>
       <c r="E78" s="3" t="n">
-        <v>43000</v>
+        <v>45000</v>
       </c>
       <c r="F78" s="3" t="n"/>
       <c r="G78" s="2" t="inlineStr"/>
@@ -4643,16 +4645,16 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/semanario-mi-ropita-322-002-sacos-1</t>
+          <t>https://www.solobabys.com/products/combo-plato-360-antiderrames-babero-de-silicona</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-03T183144.604.webp?v=1780529685</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-29at3.32.35PM.webp?v=1791307237</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
@@ -4662,11 +4664,11 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>10810924826934</v>
+        <v>10735539552566</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Set Toalla con Capucha + 6 Babitas</t>
+          <t>Semanario Mi Ropita 322-002 Sacos</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -4676,15 +4678,13 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Recién nacido, Cobijas y toallas, Baby shower, Más vendidos</t>
+          <t>Recién nacido, Ropa, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>42000</v>
-      </c>
-      <c r="F79" s="3" t="n">
-        <v>60000</v>
-      </c>
+        <v>43000</v>
+      </c>
+      <c r="F79" s="3" t="n"/>
       <c r="G79" s="2" t="inlineStr"/>
       <c r="H79" s="2" t="n">
         <v>1</v>
@@ -4696,16 +4696,16 @@
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/set-toalla-con-capucha-6-babitas</t>
+          <t>https://www.solobabys.com/products/semanario-mi-ropita-322-002-sacos-1</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-08-11T175525.349.webp?v=1786488969</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-03T183144.604.webp?v=1780529685</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
@@ -4715,11 +4715,11 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>10650947977526</v>
+        <v>10810924826934</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Crema Protectora Happy Soft 500gr | Cuidado y Protección para Bebé</t>
+          <t>Set Toalla con Capucha + 6 Babitas</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4729,14 +4729,14 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower</t>
+          <t>Recién nacido, Cobijas y toallas, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>40900</v>
+        <v>42000</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>58429</v>
+        <v>60000</v>
       </c>
       <c r="G80" s="2" t="inlineStr"/>
       <c r="H80" s="2" t="n">
@@ -4749,16 +4749,16 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/crema-protectora-happy-soft-500gr-cuidado-y-proteccion-para-bebe</t>
+          <t>https://www.solobabys.com/products/set-toalla-con-capucha-6-babitas</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_100.webp?v=1780298213</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-08-11T175525.349.webp?v=1786488969</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
@@ -4768,11 +4768,11 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>10829223625014</v>
+        <v>10650947977526</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Set de Bloques Didácticos de Construcción 37 Piezas</t>
+          <t>Crema Protectora Happy Soft 500gr | Cuidado y Protección para Bebé</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -4782,14 +4782,14 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Juguetes</t>
+          <t>Aseo y cuidado, Baby shower</t>
         </is>
       </c>
       <c r="E81" s="3" t="n">
-        <v>40000</v>
+        <v>40900</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>57143</v>
+        <v>58429</v>
       </c>
       <c r="G81" s="2" t="inlineStr"/>
       <c r="H81" s="2" t="n">
@@ -4802,16 +4802,16 @@
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/set-de-bloques-didacticos-de-construccion-37-piezas</t>
+          <t>https://www.solobabys.com/products/crema-protectora-happy-soft-500gr-cuidado-y-proteccion-para-bebe</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-08-31T182839.165.webp?v=1788218975</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_100.webp?v=1780298213</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
@@ -4821,11 +4821,11 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>10762350395702</v>
+        <v>10829223625014</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Licuadora Portátil Juice Cup</t>
+          <t>Set de Bloques Didácticos de Construcción 37 Piezas</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -4835,7 +4835,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Alimentación</t>
+          <t>Juguetes</t>
         </is>
       </c>
       <c r="E82" s="3" t="n">
@@ -4855,16 +4855,16 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/licuadora-portatil-juice-cup</t>
+          <t>https://www.solobabys.com/products/set-de-bloques-didacticos-de-construccion-37-piezas</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage1jul2026_11_02_29p.m.webp?v=1782965026</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-08-31T182839.165.webp?v=1788218975</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
@@ -4874,11 +4874,11 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>10651068825910</v>
+        <v>10762350395702</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Extractor manual de leche materna Only Baby</t>
+          <t>Licuadora Portátil Juice Cup</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -4888,22 +4888,18 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Recién nacido, Teteros, Lactancia, Baby shower, Más vendidos</t>
+          <t>Alimentación</t>
         </is>
       </c>
       <c r="E83" s="3" t="n">
-        <v>38500</v>
+        <v>40000</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>55000</v>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Transparente', 'Rosa', 'Verde', 'Azul']</t>
-        </is>
-      </c>
+        <v>57143</v>
+      </c>
+      <c r="G83" s="2" t="inlineStr"/>
       <c r="H83" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
@@ -4912,16 +4908,16 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/extractor-manual-de-leche-materna-only-baby</t>
+          <t>https://www.solobabys.com/products/licuadora-portatil-juice-cup</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla-2026-03-30T174249.061.webp?v=1774910588</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage1jul2026_11_02_29p.m.webp?v=1782965026</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
@@ -4931,11 +4927,11 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>10812587344182</v>
+        <v>10651068825910</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Set de Bloques Didácticos Infantil con Molino y Figuras</t>
+          <t>Extractor manual de leche materna Only Baby</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -4945,18 +4941,22 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Baby shower</t>
+          <t>Recién nacido, Teteros, Lactancia, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E84" s="3" t="n">
-        <v>38000</v>
+        <v>38500</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>54286</v>
-      </c>
-      <c r="G84" s="2" t="inlineStr"/>
+        <v>55000</v>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Transparente', 'Rosa', 'Verde', 'Azul']</t>
+        </is>
+      </c>
       <c r="H84" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
@@ -4965,16 +4965,16 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/set-de-bloques-didacticos-infantil-con-molino-y-figuras</t>
+          <t>https://www.solobabys.com/products/extractor-manual-de-leche-materna-only-baby</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsApp_27.webp?v=1786661794</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla-2026-03-30T174249.061.webp?v=1774910588</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
@@ -4984,11 +4984,11 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>10649160843574</v>
+        <v>10812587344182</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Bacin Prakiplas 7337 Tortuga | 7709412827917</t>
+          <t>Set de Bloques Didácticos Infantil con Molino y Figuras</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -4998,14 +4998,14 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Bacinillas</t>
+          <t>Juguetes, Baby shower</t>
         </is>
       </c>
       <c r="E85" s="3" t="n">
-        <v>37500</v>
+        <v>38000</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>53571</v>
+        <v>54286</v>
       </c>
       <c r="G85" s="2" t="inlineStr"/>
       <c r="H85" s="2" t="n">
@@ -5018,16 +5018,16 @@
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/adaptador-reductor-de-bano-infantil-diseno-tipo-carro</t>
+          <t>https://www.solobabys.com/products/set-de-bloques-didacticos-infantil-con-molino-y-figuras</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla-2026-03-28T160638.235.webp?v=1774732117</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsApp_27.webp?v=1786661794</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
@@ -5037,11 +5037,11 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>10762339385654</v>
+        <v>10649160843574</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Set Toalla con Capota + Babitas WaKid's</t>
+          <t>Bacin Prakiplas 7337 Tortuga | 7709412827917</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -5051,14 +5051,14 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Recién nacido, Cobijas y toallas, Baby shower, Más vendidos</t>
+          <t>Bacinillas</t>
         </is>
       </c>
       <c r="E86" s="3" t="n">
-        <v>36000</v>
+        <v>37500</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>51429</v>
+        <v>53571</v>
       </c>
       <c r="G86" s="2" t="inlineStr"/>
       <c r="H86" s="2" t="n">
@@ -5071,16 +5071,16 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/set-toalla-con-capota-babitas-wakids</t>
+          <t>https://www.solobabys.com/products/adaptador-reductor-de-bano-infantil-diseno-tipo-carro</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage1jul2026_10_34_42p.m.webp?v=1782963320</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla-2026-03-28T160638.235.webp?v=1774732117</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
@@ -5090,11 +5090,11 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>10861984448822</v>
+        <v>10762339385654</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Tapete Didáctico Plegable con Bolso de Transporte</t>
+          <t>Set Toalla con Capota + Babitas WaKid's</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -5104,14 +5104,14 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Baby shower</t>
+          <t>Recién nacido, Cobijas y toallas, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E87" s="3" t="n">
-        <v>35000</v>
+        <v>36000</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>50000</v>
+        <v>51429</v>
       </c>
       <c r="G87" s="2" t="inlineStr"/>
       <c r="H87" s="2" t="n">
@@ -5124,16 +5124,16 @@
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/tapete-didactico-plegable-con-bolso-de-transporte</t>
+          <t>https://www.solobabys.com/products/set-toalla-con-capota-babitas-wakids</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-21at3.35.30PM_2.webp?v=1790029328</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage1jul2026_10_34_42p.m.webp?v=1782963320</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
@@ -5143,11 +5143,11 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>10645594538294</v>
+        <v>10861984448822</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Tapete inflable con agua para bebé</t>
+          <t>Tapete Didáctico Plegable con Bolso de Transporte</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Más vendidos</t>
+          <t>Juguetes, Baby shower</t>
         </is>
       </c>
       <c r="E88" s="3" t="n">
@@ -5177,16 +5177,16 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/tapete-inflable-con-agua-para-bebe</t>
+          <t>https://www.solobabys.com/products/tapete-didactico-plegable-con-bolso-de-transporte</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla-2026-03-27T144417.793.webp?v=1774640713</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-21at3.35.30PM_2.webp?v=1790029328</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
@@ -5196,11 +5196,11 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>10643504759094</v>
+        <v>10645594538294</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Extractor Eléctrico Portátil de Leche</t>
+          <t>Tapete inflable con agua para bebé</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Lactancia</t>
+          <t>Juguetes, Más vendidos</t>
         </is>
       </c>
       <c r="E89" s="3" t="n">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/extractor-manual-de-leche-materna</t>
+          <t>https://www.solobabys.com/products/tapete-inflable-con-agua-para-bebe</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla_87.webp?v=1774564344</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla-2026-03-27T144417.793.webp?v=1774640713</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
@@ -5249,11 +5249,11 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>10762503979318</v>
+        <v>10643504759094</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Chaleco para Moto Bebé</t>
+          <t>Extractor Eléctrico Portátil de Leche</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Accesorios, Baby shower</t>
+          <t>Lactancia</t>
         </is>
       </c>
       <c r="E90" s="3" t="n">
@@ -5283,16 +5283,16 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/chaleco-para-moto-bebe</t>
+          <t>https://www.solobabys.com/products/extractor-manual-de-leche-materna</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage2jul2026_06_52_50a.m.webp?v=1782993218</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla_87.webp?v=1774564344</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
@@ -5302,11 +5302,11 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>10650894762294</v>
+        <v>10762503979318</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Aspirador Nasal Eléctrico HENHR1228 | Limpieza Suave y Práctica para Bebé</t>
+          <t>Chaleco para Moto Bebé</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -5316,22 +5316,18 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower</t>
+          <t>Accesorios, Baby shower</t>
         </is>
       </c>
       <c r="E91" s="3" t="n">
-        <v>34000</v>
+        <v>35000</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>47600</v>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Rosa', 'Amarillo', 'Verde', 'Azul']</t>
-        </is>
-      </c>
+        <v>50000</v>
+      </c>
+      <c r="G91" s="2" t="inlineStr"/>
       <c r="H91" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
@@ -5340,16 +5336,16 @@
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/aspirador-nasal-electrico-henhr1228-limpieza-suave-y-practica-para-bebe</t>
+          <t>https://www.solobabys.com/products/chaleco-para-moto-bebe</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_41.webp?v=1779576241</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage2jul2026_06_52_50a.m.webp?v=1782993218</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
@@ -5359,11 +5355,11 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>10651903099190</v>
+        <v>10650894762294</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Bacín infantil Praktiplas Oso</t>
+          <t>Aspirador Nasal Eléctrico HENHR1228 | Limpieza Suave y Práctica para Bebé</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -5373,18 +5369,22 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Bacinillas</t>
+          <t>Aseo y cuidado, Baby shower</t>
         </is>
       </c>
       <c r="E92" s="3" t="n">
-        <v>33500</v>
+        <v>34000</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>47857</v>
-      </c>
-      <c r="G92" s="2" t="inlineStr"/>
+        <v>47600</v>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Rosa', 'Amarillo', 'Verde', 'Azul']</t>
+        </is>
+      </c>
       <c r="H92" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
@@ -5393,16 +5393,16 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/bacin-infantil-praktiplas-oso</t>
+          <t>https://www.solobabys.com/products/aspirador-nasal-electrico-henhr1228-limpieza-suave-y-practica-para-bebe</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla-2026-04-01T122700.534.webp?v=1775064763</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_41.webp?v=1779576241</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
@@ -5412,11 +5412,11 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>15420728574262</v>
+        <v>10651903099190</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Perrito Superhéroe Musical con Luces | Super Electric Dog</t>
+          <t>Bacín infantil Praktiplas Oso</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -5426,14 +5426,14 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Juguetes</t>
+          <t>Bacinillas</t>
         </is>
       </c>
       <c r="E93" s="3" t="n">
-        <v>33000</v>
+        <v>33500</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>47000</v>
+        <v>47857</v>
       </c>
       <c r="G93" s="2" t="inlineStr"/>
       <c r="H93" s="2" t="n">
@@ -5446,30 +5446,30 @@
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/perrito-superheroe-musical-con-luces-super-electric-dog</t>
+          <t>https://www.solobabys.com/products/bacin-infantil-praktiplas-oso</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/super-electric-dog-2.webp?v=1792063802</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla-2026-04-01T122700.534.webp?v=1775064763</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-title { font-family: 'Fraunces', serif; font-size: 38px; line-height: 1.1; color: #00afba; margin: 0 0 15px 0; letter-spacin</t>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>10649163104566</v>
+        <v>15420728574262</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Cobija capota animales Modelo CL1006</t>
+          <t>Perrito Superhéroe Musical con Luces | Super Electric Dog</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -5479,14 +5479,14 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Recién nacido, Cobijas y toallas, Baby shower, Más vendidos</t>
+          <t>Juguetes</t>
         </is>
       </c>
       <c r="E94" s="3" t="n">
         <v>33000</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>47143</v>
+        <v>47000</v>
       </c>
       <c r="G94" s="2" t="inlineStr"/>
       <c r="H94" s="2" t="n">
@@ -5499,30 +5499,30 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/cobija-capota-animales-modelo-cl1006</t>
+          <t>https://www.solobabys.com/products/perrito-superheroe-musical-con-luces-super-electric-dog</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-03-21at4.46.17PM_1.jpg?v=1774733372</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/super-electric-dog-2.webp?v=1792063802</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-title { font-family: 'Fraunces', serif; font-size: 38px; line-height: 1.1; color: #00afba; margin: 0 0 15px 0; letter-spacin</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>10721369522486</v>
+        <v>10649163104566</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Cepillo Lava Teteros | MST6608</t>
+          <t>Cobija capota animales Modelo CL1006</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -5532,22 +5532,18 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Teteros, Más vendidos</t>
+          <t>Recién nacido, Cobijas y toallas, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E95" s="3" t="n">
-        <v>30700</v>
+        <v>33000</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>43857</v>
-      </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Rojo', 'azul']</t>
-        </is>
-      </c>
+        <v>47143</v>
+      </c>
+      <c r="G95" s="2" t="inlineStr"/>
       <c r="H95" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
@@ -5556,12 +5552,12 @@
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/cepillo-lava-teteros-mst6608</t>
+          <t>https://www.solobabys.com/products/cobija-capota-animales-modelo-cl1006</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_17.webp?v=1779418188</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-03-21at4.46.17PM_1.jpg?v=1774733372</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
@@ -5575,11 +5571,11 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>10643571310902</v>
+        <v>10721369522486</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Toalla suave y absorbente para bebé</t>
+          <t>Cepillo Lava Teteros | MST6608</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -5589,18 +5585,22 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Cobijas y toallas, Baby shower</t>
+          <t>Teteros, Más vendidos</t>
         </is>
       </c>
       <c r="E96" s="3" t="n">
-        <v>28500</v>
+        <v>30700</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>40714</v>
-      </c>
-      <c r="G96" s="2" t="inlineStr"/>
+        <v>43857</v>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Rojo', 'azul']</t>
+        </is>
+      </c>
       <c r="H96" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
@@ -5609,12 +5609,12 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/toalla-suave-y-absorbente-para-bebe</t>
+          <t>https://www.solobabys.com/products/cepillo-lava-teteros-mst6608</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-03-21at5.41.21PM_3.jpg?v=1774569011</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_17.webp?v=1779418188</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
@@ -5628,11 +5628,11 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>10643571573046</v>
+        <v>10643571310902</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Set de Aseo Kokibebe</t>
+          <t>Toalla suave y absorbente para bebé</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -5642,14 +5642,14 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower</t>
+          <t>Cobijas y toallas, Baby shower</t>
         </is>
       </c>
       <c r="E97" s="3" t="n">
         <v>28500</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>36900</v>
+        <v>40714</v>
       </c>
       <c r="G97" s="2" t="inlineStr"/>
       <c r="H97" s="2" t="n">
@@ -5662,16 +5662,16 @@
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/set-de-aseo-kokibebe</t>
+          <t>https://www.solobabys.com/products/toalla-suave-y-absorbente-para-bebe</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla-2026-03-27T110341.589_a2241f01-ac70-4d1e-a938-52f6eaddf13d.webp?v=1774627574</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-03-21at5.41.21PM_3.jpg?v=1774569011</t>
         </is>
       </c>
       <c r="L97" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
@@ -5681,11 +5681,11 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>10837689532726</v>
+        <v>10643571573046</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Ajuar prematuro para Bebé 5 Piezas – My Best Friends</t>
+          <t>Set de Aseo Kokibebe</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -5695,30 +5695,32 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Recién nacido, Ropa, Baby shower</t>
+          <t>Aseo y cuidado, Baby shower</t>
         </is>
       </c>
       <c r="E98" s="3" t="n">
-        <v>28000</v>
-      </c>
-      <c r="F98" s="3" t="n"/>
+        <v>28500</v>
+      </c>
+      <c r="F98" s="3" t="n">
+        <v>36900</v>
+      </c>
       <c r="G98" s="2" t="inlineStr"/>
       <c r="H98" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/ajuar-para-bebe-5-piezas-my-best-friends</t>
+          <t>https://www.solobabys.com/products/set-de-aseo-kokibebe</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-03at11.35.47AM_2.webp?v=1788819715</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla-2026-03-27T110341.589_a2241f01-ac70-4d1e-a938-52f6eaddf13d.webp?v=1774627574</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
@@ -5732,11 +5734,11 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>10837681799478</v>
+        <v>10837689532726</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Lima Eléctrica para Uñas de Bebé</t>
+          <t>Ajuar prematuro para Bebé 5 Piezas – My Best Friends</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -5746,36 +5748,34 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Juguetes</t>
+          <t>Recién nacido, Ropa, Baby shower</t>
         </is>
       </c>
       <c r="E99" s="3" t="n">
-        <v>27000</v>
-      </c>
-      <c r="F99" s="3" t="n">
-        <v>38571</v>
-      </c>
+        <v>28000</v>
+      </c>
+      <c r="F99" s="3" t="n"/>
       <c r="G99" s="2" t="inlineStr"/>
       <c r="H99" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/set-de-manicure-para-bebe</t>
+          <t>https://www.solobabys.com/products/ajuar-para-bebe-5-piezas-my-best-friends</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage7sept2026_17_09_49.webp?v=1788819099</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-03at11.35.47AM_2.webp?v=1788819715</t>
         </is>
       </c>
       <c r="L99" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
@@ -5785,11 +5785,11 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>10650935755062</v>
+        <v>10837681799478</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Crema Protectora Happy Soft 250gr | Cuidado y Protección para Bebé</t>
+          <t>Lima Eléctrica para Uñas de Bebé</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -5799,7 +5799,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower</t>
+          <t>Aseo y cuidado, Juguetes</t>
         </is>
       </c>
       <c r="E100" s="3" t="n">
@@ -5819,16 +5819,16 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/crema-protectora-happy-soft-250gr-cuidado-y-proteccion-para-bebe</t>
+          <t>https://www.solobabys.com/products/set-de-manicure-para-bebe</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-01T022000.472.webp?v=1780298415</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage7sept2026_17_09_49.webp?v=1788819099</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
@@ -5838,11 +5838,11 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>10642900058422</v>
+        <v>10650935755062</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Lima Eléctrica Only Baby | Cuidado Seguro de Uñas para Bebé</t>
+          <t>Crema Protectora Happy Soft 250gr | Cuidado y Protección para Bebé</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -5852,22 +5852,18 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Accesorios, Baby shower, Más vendidos</t>
+          <t>Aseo y cuidado, Baby shower</t>
         </is>
       </c>
       <c r="E101" s="3" t="n">
-        <v>25500</v>
+        <v>27000</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>27000</v>
-      </c>
-      <c r="G101" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Rosa', 'Azul']</t>
-        </is>
-      </c>
+        <v>38571</v>
+      </c>
+      <c r="G101" s="2" t="inlineStr"/>
       <c r="H101" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
@@ -5876,16 +5872,16 @@
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/lima-electrica-only-baby-cuidado-seguro-de-unas-para-bebe</t>
+          <t>https://www.solobabys.com/products/crema-protectora-happy-soft-250gr-cuidado-y-proteccion-para-bebe</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/limaelectrica_1000x_b8a0febc-3486-42a7-a3cf-8a61cc5b6601.webp?v=1774036791</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-01T022000.472.webp?v=1780298415</t>
         </is>
       </c>
       <c r="L101" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
@@ -5895,11 +5891,11 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>10643572031798</v>
+        <v>10642900058422</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Set Manicure Baby Care</t>
+          <t>Lima Eléctrica Only Baby | Cuidado Seguro de Uñas para Bebé</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -5913,14 +5909,18 @@
         </is>
       </c>
       <c r="E102" s="3" t="n">
-        <v>25000</v>
+        <v>25500</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>34900</v>
-      </c>
-      <c r="G102" s="2" t="inlineStr"/>
+        <v>27000</v>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Rosa', 'Azul']</t>
+        </is>
+      </c>
       <c r="H102" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
@@ -5929,12 +5929,12 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/set-manicure-baby-care</t>
+          <t>https://www.solobabys.com/products/lima-electrica-only-baby-cuidado-seguro-de-unas-para-bebe</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla-2026-03-27T143126.593_2c7a959d-f5cc-459d-81e2-3ea14b4df0ba.webp?v=1774640025</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/limaelectrica_1000x_b8a0febc-3486-42a7-a3cf-8a61cc5b6601.webp?v=1774036791</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
@@ -5948,11 +5948,11 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>10651062665526</v>
+        <v>10643572031798</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Cobija TG 08 burbuja Diseños surtidos</t>
+          <t>Set Manicure Baby Care</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -5962,14 +5962,14 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Cobijas y toallas, Baby shower, Más vendidos</t>
+          <t>Aseo y cuidado, Accesorios, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E103" s="3" t="n">
-        <v>24000</v>
+        <v>25000</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>34286</v>
+        <v>34900</v>
       </c>
       <c r="G103" s="2" t="inlineStr"/>
       <c r="H103" s="2" t="n">
@@ -5982,16 +5982,16 @@
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/cobija-tg-08-burbuja-disenos-surtidos</t>
+          <t>https://www.solobabys.com/products/set-manicure-baby-care</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_-_2026-06-03T163734.732.webp?v=1780522748</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla-2026-03-27T143126.593_2c7a959d-f5cc-459d-81e2-3ea14b4df0ba.webp?v=1774640025</t>
         </is>
       </c>
       <c r="L103" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
@@ -6001,11 +6001,11 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>10762511089974</v>
+        <v>10651062665526</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>MORDEDOR CON CADENA ONLY| HLW-040</t>
+          <t>Cobija TG 08 burbuja Diseños surtidos</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -6015,14 +6015,14 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Baby shower</t>
+          <t>Cobijas y toallas, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E104" s="3" t="n">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>31429</v>
+        <v>34286</v>
       </c>
       <c r="G104" s="2" t="inlineStr"/>
       <c r="H104" s="2" t="n">
@@ -6035,30 +6035,30 @@
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/mordedor-con-sujetador-para-bebe</t>
+          <t>https://www.solobabys.com/products/cobija-tg-08-burbuja-disenos-surtidos</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage2jul2026_07_37_12a.m.webp?v=1782995871</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_-_2026-06-03T163734.732.webp?v=1780522748</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container{font-family:'Quicksand',sans-serif;max-width:480px;margin:0 auto;color:#4a5568;padding:26px;background:#fff;} .b-rating{display:flex;align-items:center;gap:8px;margin-bottom:12px;font-size:14px;font-weight:700;color:#c8d431;flex-wrap:wrap;} .b-rating-text</t>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>10651054637366</v>
+        <v>10762511089974</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Cobija vilu cinta estampada Diseños surtidos</t>
+          <t>MORDEDOR CON CADENA ONLY| HLW-040</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Cobijas y toallas, Baby shower, Más vendidos</t>
+          <t>Juguetes, Baby shower</t>
         </is>
       </c>
       <c r="E105" s="3" t="n">
@@ -6088,30 +6088,30 @@
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/cobija-vilu-cinta-estampada-disenos-surtidos</t>
+          <t>https://www.solobabys.com/products/mordedor-con-sujetador-para-bebe</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_-_2026-06-02T212801.807.webp?v=1780453770</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage2jul2026_07_37_12a.m.webp?v=1782995871</t>
         </is>
       </c>
       <c r="L105" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container{font-family:'Quicksand',sans-serif;max-width:480px;margin:0 auto;color:#4a5568;padding:26px;background:#fff;} .b-rating{display:flex;align-items:center;gap:8px;margin-bottom:12px;font-size:14px;font-weight:700;color:#c8d431;flex-wrap:wrap;} .b-rating-text</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>10721360019766</v>
+        <v>10651054637366</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Termo Plegable Infantil Balón | JS-8</t>
+          <t>Cobija vilu cinta estampada Diseños surtidos</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -6121,22 +6121,18 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Alimentación</t>
+          <t>Cobijas y toallas, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E106" s="3" t="n">
         <v>22000</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>31000</v>
-      </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Blanco', 'Verde', 'azul']</t>
-        </is>
-      </c>
+        <v>31429</v>
+      </c>
+      <c r="G106" s="2" t="inlineStr"/>
       <c r="H106" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
@@ -6145,12 +6141,12 @@
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/termo-plegable-infantil-balon-js-8</t>
+          <t>https://www.solobabys.com/products/cobija-vilu-cinta-estampada-disenos-surtidos</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_14.webp?v=1779414355</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_-_2026-06-02T212801.807.webp?v=1780453770</t>
         </is>
       </c>
       <c r="L106" s="2" t="n">
@@ -6164,11 +6160,11 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>10721353236790</v>
+        <v>10721360019766</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Termo Plegable Infantil | JS-9</t>
+          <t>Termo Plegable Infantil Balón | JS-8</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -6178,7 +6174,7 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Alimentación, Baby shower</t>
+          <t>Alimentación</t>
         </is>
       </c>
       <c r="E107" s="3" t="n">
@@ -6189,11 +6185,11 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Color: ['Púrpura', 'Rosa']</t>
+          <t>Color: ['Blanco', 'Verde', 'azul']</t>
         </is>
       </c>
       <c r="H107" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
@@ -6202,16 +6198,16 @@
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/termo-plegable-infantil-js-9</t>
+          <t>https://www.solobabys.com/products/termo-plegable-infantil-balon-js-8</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_8.webp?v=1779411444</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_14.webp?v=1779414355</t>
         </is>
       </c>
       <c r="L107" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
@@ -6221,11 +6217,11 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>10643064684854</v>
+        <v>10721353236790</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Vaso Amazing Baby | MON1035</t>
+          <t>Termo Plegable Infantil | JS-9</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -6239,14 +6235,14 @@
         </is>
       </c>
       <c r="E108" s="3" t="n">
-        <v>21000</v>
+        <v>22000</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>27600</v>
+        <v>31000</v>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Color: ['Azul', 'Rosa']</t>
+          <t>Color: ['Púrpura', 'Rosa']</t>
         </is>
       </c>
       <c r="H108" s="2" t="n">
@@ -6259,16 +6255,16 @@
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/vaso-amazing-baby-vaso-entrenador-con-asas</t>
+          <t>https://www.solobabys.com/products/termo-plegable-infantil-js-9</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/sbproductos_3_1.webp?v=1774046605</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_8.webp?v=1779411444</t>
         </is>
       </c>
       <c r="L108" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
@@ -6278,11 +6274,11 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>10642009358646</v>
+        <v>10643064684854</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Tapete Foamy Rompecabezas Infantil | Piso Didáctico para Bebé y Niños</t>
+          <t>Vaso Amazing Baby | MON1035</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -6292,22 +6288,22 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Baby shower</t>
+          <t>Alimentación, Baby shower</t>
         </is>
       </c>
       <c r="E109" s="3" t="n">
-        <v>20500</v>
+        <v>21000</v>
       </c>
       <c r="F109" s="3" t="n">
         <v>27600</v>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Color: ['Frutas', 'Números', 'Letras']</t>
+          <t>Color: ['Azul', 'Rosa']</t>
         </is>
       </c>
       <c r="H109" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
@@ -6316,16 +6312,16 @@
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/tapete-foamy-rompecabezas-infantil-piso-didactico-para-bebe-y-ninos</t>
+          <t>https://www.solobabys.com/products/vaso-amazing-baby-vaso-entrenador-con-asas</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/D_NQ_NP_2X_812378-CBT91060493341_082025-F.webp?v=1773965161</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/sbproductos_3_1.webp?v=1774046605</t>
         </is>
       </c>
       <c r="L109" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
@@ -6335,11 +6331,11 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>10729673720118</v>
+        <v>10642009358646</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Tetero Only 8 Onzas | A2DJ</t>
+          <t>Tapete Foamy Rompecabezas Infantil | Piso Didáctico para Bebé y Niños</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -6349,18 +6345,22 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Teteros</t>
+          <t>Juguetes, Baby shower</t>
         </is>
       </c>
       <c r="E110" s="3" t="n">
-        <v>19000</v>
+        <v>20500</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>27143</v>
-      </c>
-      <c r="G110" s="2" t="inlineStr"/>
+        <v>27600</v>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Frutas', 'Números', 'Letras']</t>
+        </is>
+      </c>
       <c r="H110" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
@@ -6369,16 +6369,16 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/tetero-only-8-onzas-a2dj</t>
+          <t>https://www.solobabys.com/products/tapete-foamy-rompecabezas-infantil-piso-didactico-para-bebe-y-ninos</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_88.webp?v=1780097838</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/D_NQ_NP_2X_812378-CBT91060493341_082025-F.webp?v=1773965161</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
@@ -6388,11 +6388,11 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>10651909718326</v>
+        <v>10729673720118</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Orinal infantil Praktiplas Pingüino</t>
+          <t>Tetero Only 8 Onzas | A2DJ</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Bacinillas, Más vendidos</t>
+          <t>Teteros</t>
         </is>
       </c>
       <c r="E111" s="3" t="n">
@@ -6411,13 +6411,9 @@
       <c r="F111" s="3" t="n">
         <v>27143</v>
       </c>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Aguamarina', 'Negro']</t>
-        </is>
-      </c>
+      <c r="G111" s="2" t="inlineStr"/>
       <c r="H111" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
@@ -6426,12 +6422,12 @@
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/orinal-infantil-praktiplas-pinguino</t>
+          <t>https://www.solobabys.com/products/tetero-only-8-onzas-a2dj</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_51.webp?v=1779814860</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_88.webp?v=1780097838</t>
         </is>
       </c>
       <c r="L111" s="2" t="n">
@@ -6445,11 +6441,11 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>10649149767990</v>
+        <v>10651909718326</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Bolsas de almacenamiento de leche materna | ONBY-1</t>
+          <t>Orinal infantil Praktiplas Pingüino</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -6459,18 +6455,22 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Recién nacido, Lactancia, Baby shower</t>
+          <t>Bacinillas, Más vendidos</t>
         </is>
       </c>
       <c r="E112" s="3" t="n">
-        <v>18000</v>
+        <v>19000</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>25714</v>
-      </c>
-      <c r="G112" s="2" t="inlineStr"/>
+        <v>27143</v>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Aguamarina', 'Negro']</t>
+        </is>
+      </c>
       <c r="H112" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
@@ -6479,16 +6479,16 @@
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/bolsas-de-almacenamiento-de-leche-materna-250-ml-x-30-unidades</t>
+          <t>https://www.solobabys.com/products/orinal-infantil-praktiplas-pinguino</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_-_2026-06-02T205506.029.webp?v=1780451739</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_51.webp?v=1779814860</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
@@ -6498,11 +6498,11 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>10642865127734</v>
+        <v>10649149767990</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Tetero Only Baby Natural 9oz / 260ml | Alimentación para Bebé</t>
+          <t>Bolsas de almacenamiento de leche materna | ONBY-1</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -6512,22 +6512,18 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Teteros, Baby shower, Más vendidos</t>
+          <t>Recién nacido, Lactancia, Baby shower</t>
         </is>
       </c>
       <c r="E113" s="3" t="n">
-        <v>17500</v>
+        <v>18000</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>22600</v>
-      </c>
-      <c r="G113" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Rosa', 'Azul', 'Transparente']</t>
-        </is>
-      </c>
+        <v>25714</v>
+      </c>
+      <c r="G113" s="2" t="inlineStr"/>
       <c r="H113" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
@@ -6536,12 +6532,12 @@
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/tetero-only-baby-natural-8oz-260ml-alimentacion-para-bebe</t>
+          <t>https://www.solobabys.com/products/bolsas-de-almacenamiento-de-leche-materna-250-ml-x-30-unidades</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_74.webp?v=1779927570</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_-_2026-06-02T205506.029.webp?v=1780451739</t>
         </is>
       </c>
       <c r="L113" s="2" t="n">
@@ -6555,11 +6551,11 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>10727775371574</v>
+        <v>10642865127734</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Cepillo Lava Tetero Only Baby A-71</t>
+          <t>Tetero Only Baby Natural 9oz / 260ml | Alimentación para Bebé</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -6569,20 +6565,22 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Teteros</t>
+          <t>Teteros, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E114" s="3" t="n">
         <v>17500</v>
       </c>
-      <c r="F114" s="3" t="n"/>
+      <c r="F114" s="3" t="n">
+        <v>22600</v>
+      </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Color: ['Azul', 'Rosa']</t>
+          <t>Color: ['Rosa', 'Azul', 'Transparente']</t>
         </is>
       </c>
       <c r="H114" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
@@ -6591,12 +6589,12 @@
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/cepillo-lava-tetero-only-baby-a-71</t>
+          <t>https://www.solobabys.com/products/tetero-only-baby-natural-8oz-260ml-alimentacion-para-bebe</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_71.webp?v=1779925711</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_74.webp?v=1779927570</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
@@ -6610,11 +6608,11 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>10642845761846</v>
+        <v>10727775371574</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Tetero Only Baby Natural 4oz / 125ml | Anticólicos con Asas</t>
+          <t>Cepillo Lava Tetero Only Baby A-71</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -6624,22 +6622,20 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Teteros, Baby shower, Más vendidos</t>
+          <t>Teteros</t>
         </is>
       </c>
       <c r="E115" s="3" t="n">
-        <v>17000</v>
-      </c>
-      <c r="F115" s="3" t="n">
-        <v>22000</v>
-      </c>
+        <v>17500</v>
+      </c>
+      <c r="F115" s="3" t="n"/>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Color: ['Rosa', 'Azul', 'Transparente']</t>
+          <t>Color: ['Azul', 'Rosa']</t>
         </is>
       </c>
       <c r="H115" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
@@ -6648,12 +6644,12 @@
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/tetero-only-baby-natural-4oz-125ml-anticolicos-con-asas</t>
+          <t>https://www.solobabys.com/products/cepillo-lava-tetero-only-baby-a-71</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/sbproductos_1_2.webp?v=1774025676</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_71.webp?v=1779925711</t>
         </is>
       </c>
       <c r="L115" s="2" t="n">
@@ -6667,11 +6663,11 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>10643479331126</v>
+        <v>10642845761846</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Copa recolectora de leche materna</t>
+          <t>Tetero Only Baby Natural 4oz / 125ml | Anticólicos con Asas</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -6681,18 +6677,22 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Recién nacido, Lactancia, Más vendidos</t>
+          <t>Teteros, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E116" s="3" t="n">
-        <v>16500</v>
+        <v>17000</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>23571</v>
-      </c>
-      <c r="G116" s="2" t="inlineStr"/>
+        <v>22000</v>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Rosa', 'Azul', 'Transparente']</t>
+        </is>
+      </c>
       <c r="H116" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
@@ -6701,12 +6701,12 @@
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/fular-cole-portabebe-ergonomico</t>
+          <t>https://www.solobabys.com/products/tetero-only-baby-natural-4oz-125ml-anticolicos-con-asas</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla_55.webp?v=1774162492</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/sbproductos_1_2.webp?v=1774025676</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
@@ -6720,11 +6720,11 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>10741795520822</v>
+        <v>10643479331126</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Lima eléctrica para Bebé | V168</t>
+          <t>Copa recolectora de leche materna</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -6734,14 +6734,14 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower, Más vendidos</t>
+          <t>Recién nacido, Lactancia, Más vendidos</t>
         </is>
       </c>
       <c r="E117" s="3" t="n">
-        <v>16000</v>
+        <v>16500</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>22857</v>
+        <v>23571</v>
       </c>
       <c r="G117" s="2" t="inlineStr"/>
       <c r="H117" s="2" t="n">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/cortaunas-electrico-para-bebe-v168</t>
+          <t>https://www.solobabys.com/products/fular-cole-portabebe-ergonomico</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-09T172638.946.webp?v=1781044015</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla_55.webp?v=1774162492</t>
         </is>
       </c>
       <c r="L117" s="2" t="n">
@@ -6773,11 +6773,11 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>10643571147062</v>
+        <v>10741795520822</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Medias estilo española para bebé</t>
+          <t>Lima eléctrica para Bebé | V168</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -6787,14 +6787,14 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Ropa, Baby shower</t>
+          <t>Aseo y cuidado, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E118" s="3" t="n">
-        <v>14500</v>
+        <v>16000</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>19900</v>
+        <v>22857</v>
       </c>
       <c r="G118" s="2" t="inlineStr"/>
       <c r="H118" s="2" t="n">
@@ -6807,12 +6807,12 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/medias-estilo-espanola-para-bebe</t>
+          <t>https://www.solobabys.com/products/cortaunas-electrico-para-bebe-v168</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_-_2026-08-14T185137.710.webp?v=1786751525</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-09T172638.946.webp?v=1781044015</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
@@ -6826,11 +6826,11 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>10730172449078</v>
+        <v>10643571147062</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Aspirador Nasal Boogy | 20931</t>
+          <t>Medias estilo española para bebé</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -6840,14 +6840,14 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower</t>
+          <t>Ropa, Baby shower</t>
         </is>
       </c>
       <c r="E119" s="3" t="n">
-        <v>14000</v>
+        <v>14500</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>20000</v>
+        <v>19900</v>
       </c>
       <c r="G119" s="2" t="inlineStr"/>
       <c r="H119" s="2" t="n">
@@ -6860,12 +6860,12 @@
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/aspirador-nasal-boogy-20931</t>
+          <t>https://www.solobabys.com/products/medias-estilo-espanola-para-bebe</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_99.webp?v=1780185614</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_-_2026-08-14T185137.710.webp?v=1786751525</t>
         </is>
       </c>
       <c r="L119" s="2" t="n">
@@ -6879,11 +6879,11 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>10650919108918</v>
+        <v>10730172449078</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Crema Protectora Happy Soft 60gr | Cuidado y Protección para Bebé</t>
+          <t>Aspirador Nasal Boogy | 20931</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -6897,10 +6897,10 @@
         </is>
       </c>
       <c r="E120" s="3" t="n">
-        <v>12500</v>
+        <v>14000</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>17857</v>
+        <v>20000</v>
       </c>
       <c r="G120" s="2" t="inlineStr"/>
       <c r="H120" s="2" t="n">
@@ -6913,16 +6913,16 @@
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/crema-protectora-happy-soft-60gr-cuidado-y-proteccion-para-bebe</t>
+          <t>https://www.solobabys.com/products/aspirador-nasal-boogy-20931</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-01T022221.997.webp?v=1780299053</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_99.webp?v=1780185614</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
@@ -6932,11 +6932,11 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>10651924660534</v>
+        <v>10650919108918</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Bacín infantil Praktiplas Rana</t>
+          <t>Crema Protectora Happy Soft 60gr | Cuidado y Protección para Bebé</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -6946,22 +6946,18 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Bacinillas</t>
+          <t>Aseo y cuidado, Baby shower</t>
         </is>
       </c>
       <c r="E121" s="3" t="n">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>17143</v>
-      </c>
-      <c r="G121" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Aguamarina', 'Azul', 'fucsia']</t>
-        </is>
-      </c>
+        <v>17857</v>
+      </c>
+      <c r="G121" s="2" t="inlineStr"/>
       <c r="H121" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
@@ -6970,16 +6966,16 @@
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/bacin-infantil-praktiplas-rana</t>
+          <t>https://www.solobabys.com/products/crema-protectora-happy-soft-60gr-cuidado-y-proteccion-para-bebe</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_44.webp?v=1779577786</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-01T022221.997.webp?v=1780299053</t>
         </is>
       </c>
       <c r="L121" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
@@ -6989,11 +6985,11 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>10762017669430</v>
+        <v>10651924660534</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Mordedor Control Silicona para Bebé</t>
+          <t>Bacín infantil Praktiplas Rana</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -7003,18 +6999,22 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Baby shower, Más vendidos</t>
+          <t>Bacinillas</t>
         </is>
       </c>
       <c r="E122" s="3" t="n">
-        <v>11000</v>
+        <v>12000</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>15714</v>
-      </c>
-      <c r="G122" s="2" t="inlineStr"/>
+        <v>17143</v>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Aguamarina', 'Azul', 'fucsia']</t>
+        </is>
+      </c>
       <c r="H122" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
@@ -7023,30 +7023,30 @@
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/mordedor-control-silicona-para-bebe</t>
+          <t>https://www.solobabys.com/products/bacin-infantil-praktiplas-rana</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage1jul2026_12_40_34p.m.webp?v=1782927688</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_44.webp?v=1779577786</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>```html @import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color</t>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>10736632987958</v>
+        <v>10762017669430</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Mordedor Only Baby Dino</t>
+          <t>Mordedor Control Silicona para Bebé</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Baby shower</t>
+          <t>Juguetes, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E123" s="3" t="n">
@@ -7076,12 +7076,12 @@
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/mordedor-only-baby-dino</t>
+          <t>https://www.solobabys.com/products/mordedor-control-silicona-para-bebe</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-05T183301.061.webp?v=1780702402</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage1jul2026_12_40_34p.m.webp?v=1782927688</t>
         </is>
       </c>
       <c r="L123" s="2" t="n">
@@ -7089,17 +7089,17 @@
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
+          <t>```html @import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>10652006547766</v>
+        <v>10736632987958</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Rascaencias Figuras AB-27 | Alivio para la Dentición del Bebé</t>
+          <t>Mordedor Only Baby Dino</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -7129,16 +7129,16 @@
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/rascaencias-figuras-ab-27-alivio-para-la-denticion-del-bebe</t>
+          <t>https://www.solobabys.com/products/mordedor-only-baby-dino</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/D_NQ_NP_900595-MLA91560968768_092025-O_EmbellecedordeProducto.webp?v=1775076453</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-05T183301.061.webp?v=1780702402</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
@@ -7148,11 +7148,11 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>10642154062134</v>
+        <v>10652006547766</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Tetero Only Baby Natural 2oz / 60ml | Alimentación para Bebé</t>
+          <t>Rascaencias Figuras AB-27 | Alivio para la Dentición del Bebé</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -7162,22 +7162,18 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Teteros, Baby shower</t>
+          <t>Juguetes, Baby shower</t>
         </is>
       </c>
       <c r="E125" s="3" t="n">
-        <v>10500</v>
+        <v>11000</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>13600</v>
-      </c>
-      <c r="G125" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Azul', 'Rosa', 'Transparente']</t>
-        </is>
-      </c>
+        <v>15714</v>
+      </c>
+      <c r="G125" s="2" t="inlineStr"/>
       <c r="H125" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
@@ -7186,30 +7182,30 @@
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/tetero-only-baby-natural-2oz-60ml-alimentacion-para-bebe</t>
+          <t>https://www.solobabys.com/products/rascaencias-figuras-ab-27-alivio-para-la-denticion-del-bebe</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_Image_5_may_2026_10_26_07_a.m..webp?v=1777995497</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/D_NQ_NP_900595-MLA91560968768_092025-O_EmbellecedordeProducto.webp?v=1775076453</t>
         </is>
       </c>
       <c r="L125" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #ffb80</t>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>10642902548790</v>
+        <v>10642154062134</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Guante Mordedor para Bebé | Alivio para Encías</t>
+          <t>Tetero Only Baby Natural 2oz / 60ml | Alimentación para Bebé</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -7219,18 +7215,18 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Accesorios, Baby shower, Más vendidos</t>
+          <t>Teteros, Baby shower</t>
         </is>
       </c>
       <c r="E126" s="3" t="n">
         <v>10500</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>15000</v>
+        <v>13600</v>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Color: ['Rosa', 'Azul', 'Verde']</t>
+          <t>Color: ['Azul', 'Rosa', 'Transparente']</t>
         </is>
       </c>
       <c r="H126" s="2" t="n">
@@ -7243,30 +7239,30 @@
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/guante-mordedor-para-bebe-alivio-para-encias</t>
+          <t>https://www.solobabys.com/products/tetero-only-baby-natural-2oz-60ml-alimentacion-para-bebe</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_64.webp?v=1779828393</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_Image_5_may_2026_10_26_07_a.m..webp?v=1777995497</t>
         </is>
       </c>
       <c r="L126" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #ffb80</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>10643478675766</v>
+        <v>10642902548790</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Pañitos Happy y Soft x100 | Limpieza Suave para Bebé</t>
+          <t>Guante Mordedor para Bebé | Alivio para Encías</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -7276,18 +7272,22 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower</t>
+          <t>Juguetes, Accesorios, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E127" s="3" t="n">
-        <v>10400</v>
+        <v>10500</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>14857</v>
-      </c>
-      <c r="G127" s="2" t="inlineStr"/>
+        <v>15000</v>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Rosa', 'Azul', 'Verde']</t>
+        </is>
+      </c>
       <c r="H127" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
@@ -7296,16 +7296,16 @@
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/panitos-happy-y-soft-x100-limpieza-suave-para-bebe</t>
+          <t>https://www.solobabys.com/products/guante-mordedor-para-bebe-alivio-para-encias</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/55.webp?v=1774123726</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_64.webp?v=1779828393</t>
         </is>
       </c>
       <c r="L127" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
@@ -7315,11 +7315,11 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>10651904344374</v>
+        <v>10643478675766</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Rascaencias Jirafa LW3 | Alivio para la Dentición del Bebé</t>
+          <t>Pañitos Happy y Soft x100 | Limpieza Suave para Bebé</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -7329,22 +7329,18 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Accesorios, Baby shower</t>
+          <t>Aseo y cuidado, Baby shower</t>
         </is>
       </c>
       <c r="E128" s="3" t="n">
-        <v>10000</v>
+        <v>10400</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>14000</v>
-      </c>
-      <c r="G128" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Amarillo', 'Rosa', 'Verde']</t>
-        </is>
-      </c>
+        <v>14857</v>
+      </c>
+      <c r="G128" s="2" t="inlineStr"/>
       <c r="H128" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
@@ -7353,16 +7349,16 @@
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/rascaencias-jirafa-lw3-alivio-para-la-denticion-del-bebe</t>
+          <t>https://www.solobabys.com/products/panitos-happy-y-soft-x100-limpieza-suave-para-bebe</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/1740126304665_1.webp?v=1775065667</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/55.webp?v=1774123726</t>
         </is>
       </c>
       <c r="L128" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
@@ -7372,11 +7368,11 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>10762342793526</v>
+        <v>10651904344374</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Babero Siliconado Ajustable</t>
+          <t>Rascaencias Jirafa LW3 | Alivio para la Dentición del Bebé</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -7386,18 +7382,22 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Alimentación, Baby shower</t>
+          <t>Juguetes, Accesorios, Baby shower</t>
         </is>
       </c>
       <c r="E129" s="3" t="n">
         <v>10000</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>14286</v>
-      </c>
-      <c r="G129" s="2" t="inlineStr"/>
+        <v>14000</v>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Amarillo', 'Rosa', 'Verde']</t>
+        </is>
+      </c>
       <c r="H129" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
@@ -7406,16 +7406,16 @@
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/babero-siliconado-ajustable</t>
+          <t>https://www.solobabys.com/products/rascaencias-jirafa-lw3-alivio-para-la-denticion-del-bebe</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage1jul2026_10_45_36p.m.webp?v=1782964027</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/1740126304665_1.webp?v=1775065667</t>
         </is>
       </c>
       <c r="L129" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
@@ -7425,11 +7425,11 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>10762507878710</v>
+        <v>10762342793526</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Mordedor Control Only Baby</t>
+          <t>Babero Siliconado Ajustable</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -7439,14 +7439,14 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Baby shower, Más vendidos</t>
+          <t>Alimentación, Baby shower</t>
         </is>
       </c>
       <c r="E130" s="3" t="n">
-        <v>9900</v>
+        <v>10000</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>14143</v>
+        <v>14286</v>
       </c>
       <c r="G130" s="2" t="inlineStr"/>
       <c r="H130" s="2" t="n">
@@ -7459,16 +7459,16 @@
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/mordedor-control-only-baby</t>
+          <t>https://www.solobabys.com/products/babero-siliconado-ajustable</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage2jul2026_07_10_28a.m.webp?v=1782994278</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage1jul2026_10_45_36p.m.webp?v=1782964027</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
@@ -7478,11 +7478,11 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>10742260891958</v>
+        <v>10762507878710</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>CHUPA FRUTA ONLY BABY | C-40</t>
+          <t>Mordedor Control Only Baby</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -7492,14 +7492,14 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Alimentación, Más vendidos</t>
+          <t>Juguetes, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E131" s="3" t="n">
-        <v>9000</v>
+        <v>9900</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>12857</v>
+        <v>14143</v>
       </c>
       <c r="G131" s="2" t="inlineStr"/>
       <c r="H131" s="2" t="n">
@@ -7512,16 +7512,16 @@
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/chupa-fruta-only-baby-c-40</t>
+          <t>https://www.solobabys.com/products/mordedor-control-only-baby</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-09T215325.108.webp?v=1781060037</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage2jul2026_07_10_28a.m.webp?v=1782994278</t>
         </is>
       </c>
       <c r="L131" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
@@ -7531,11 +7531,11 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>10762510303542</v>
+        <v>10742260891958</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Termómetro Digital Infantil</t>
+          <t>CHUPA FRUTA ONLY BABY | C-40</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -7545,14 +7545,14 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower, Más vendidos</t>
+          <t>Alimentación, Más vendidos</t>
         </is>
       </c>
       <c r="E132" s="3" t="n">
-        <v>8500</v>
+        <v>9000</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>12143</v>
+        <v>12857</v>
       </c>
       <c r="G132" s="2" t="inlineStr"/>
       <c r="H132" s="2" t="n">
@@ -7565,16 +7565,16 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/termometro-digital-infantil</t>
+          <t>https://www.solobabys.com/products/chupa-fruta-only-baby-c-40</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage2jul2026_07_22_20a.m.webp?v=1782994980</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-09T215325.108.webp?v=1781060037</t>
         </is>
       </c>
       <c r="L132" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
@@ -7584,11 +7584,11 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>10642922602806</v>
+        <v>10762510303542</v>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Vajilla Love With para Bebé | 939BB</t>
+          <t>Termómetro Digital Infantil</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -7598,22 +7598,18 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Alimentación, Baby shower</t>
+          <t>Aseo y cuidado, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E133" s="3" t="n">
-        <v>7500</v>
+        <v>8500</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>9000</v>
-      </c>
-      <c r="G133" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Verde', 'Naranja', 'Azul', 'Aguamarina']</t>
-        </is>
-      </c>
+        <v>12143</v>
+      </c>
+      <c r="G133" s="2" t="inlineStr"/>
       <c r="H133" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
@@ -7622,12 +7618,12 @@
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/vajilla-love-with-para-bebe-plato-infantil-con-diseno-divertido</t>
+          <t>https://www.solobabys.com/products/termometro-digital-infantil</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/39.webp?v=1774040907</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage2jul2026_07_22_20a.m.webp?v=1782994980</t>
         </is>
       </c>
       <c r="L133" s="2" t="n">
@@ -7641,11 +7637,11 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>10726877331766</v>
+        <v>10642922602806</v>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Cepillo Dental Siliconado 360° para Bebés</t>
+          <t>Vajilla Love With para Bebé | 939BB</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -7655,16 +7651,22 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Más vendidos</t>
+          <t>Alimentación, Baby shower</t>
         </is>
       </c>
       <c r="E134" s="3" t="n">
         <v>7500</v>
       </c>
-      <c r="F134" s="3" t="n"/>
-      <c r="G134" s="2" t="inlineStr"/>
+      <c r="F134" s="3" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Verde', 'Naranja', 'Azul', 'Aguamarina']</t>
+        </is>
+      </c>
       <c r="H134" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
@@ -7673,16 +7675,16 @@
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/cepillo-dental-siliconado-360-para-bebes</t>
+          <t>https://www.solobabys.com/products/vajilla-love-with-para-bebe-plato-infantil-con-diseno-divertido</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_62.webp?v=1779825817</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/39.webp?v=1774040907</t>
         </is>
       </c>
       <c r="L134" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
@@ -7692,11 +7694,11 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>10643440664886</v>
+        <v>10726877331766</v>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Aspirador Nasal Only Baby | HENFZ11</t>
+          <t>Cepillo Dental Siliconado 360° para Bebés</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -7706,22 +7708,16 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower</t>
+          <t>Aseo y cuidado, Más vendidos</t>
         </is>
       </c>
       <c r="E135" s="3" t="n">
-        <v>6500</v>
-      </c>
-      <c r="F135" s="3" t="n">
-        <v>7000</v>
-      </c>
-      <c r="G135" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Azul', 'Rosa']</t>
-        </is>
-      </c>
+        <v>7500</v>
+      </c>
+      <c r="F135" s="3" t="n"/>
+      <c r="G135" s="2" t="inlineStr"/>
       <c r="H135" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
@@ -7730,16 +7726,16 @@
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/aspirador-nasal-only-baby-limpieza-suave-para-bebe</t>
+          <t>https://www.solobabys.com/products/cepillo-dental-siliconado-360-para-bebes</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/aspirador-nasal-azul-para-bebe.webp?v=1774108168</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_62.webp?v=1779825817</t>
         </is>
       </c>
       <c r="L135" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
@@ -7749,11 +7745,11 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>10728210792758</v>
+        <v>10643440664886</v>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Set Manicure Bebé | JJ250347</t>
+          <t>Aspirador Nasal Only Baby | HENFZ11</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -7763,18 +7759,22 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado</t>
+          <t>Aseo y cuidado, Baby shower</t>
         </is>
       </c>
       <c r="E136" s="3" t="n">
         <v>6500</v>
       </c>
       <c r="F136" s="3" t="n">
-        <v>9286</v>
-      </c>
-      <c r="G136" s="2" t="inlineStr"/>
+        <v>7000</v>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Azul', 'Rosa']</t>
+        </is>
+      </c>
       <c r="H136" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
@@ -7783,16 +7783,16 @@
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/set-manicure-bebe-jj250347</t>
+          <t>https://www.solobabys.com/products/aspirador-nasal-only-baby-limpieza-suave-para-bebe</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_81.webp?v=1780001979</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/aspirador-nasal-azul-para-bebe.webp?v=1774108168</t>
         </is>
       </c>
       <c r="L136" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
@@ -7802,11 +7802,11 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>10743245766966</v>
+        <v>10728210792758</v>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Cepillo Lengua Only Baby | FZ-121</t>
+          <t>Set Manicure Bebé | JJ250347</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -7816,14 +7816,14 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower, Más vendidos</t>
+          <t>Aseo y cuidado</t>
         </is>
       </c>
       <c r="E137" s="3" t="n">
-        <v>6000</v>
+        <v>6500</v>
       </c>
       <c r="F137" s="3" t="n">
-        <v>8571</v>
+        <v>9286</v>
       </c>
       <c r="G137" s="2" t="inlineStr"/>
       <c r="H137" s="2" t="n">
@@ -7836,16 +7836,16 @@
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/cepillo-lengua-only-baby-fz-121</t>
+          <t>https://www.solobabys.com/products/set-manicure-bebe-jj250347</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-10T193401.800.webp?v=1781138064</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_81.webp?v=1780001979</t>
         </is>
       </c>
       <c r="L137" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
@@ -7855,11 +7855,11 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>10643473727798</v>
+        <v>10743245766966</v>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Pañitos Happy y Soft x40 | Limpieza Suave para Bebé</t>
+          <t>Cepillo Lengua Only Baby | FZ-121</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -7869,14 +7869,14 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower</t>
+          <t>Aseo y cuidado, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E138" s="3" t="n">
-        <v>4700</v>
+        <v>6000</v>
       </c>
       <c r="F138" s="3" t="n">
-        <v>6714</v>
+        <v>8571</v>
       </c>
       <c r="G138" s="2" t="inlineStr"/>
       <c r="H138" s="2" t="n">
@@ -7889,25 +7889,78 @@
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
+          <t>https://www.solobabys.com/products/cepillo-lengua-only-baby-fz-121</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-10T193401.800.webp?v=1781138064</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>10643473727798</v>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>Pañitos Happy y Soft x40 | Limpieza Suave para Bebé</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Sin categoría</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Aseo y cuidado, Baby shower</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="n">
+        <v>4700</v>
+      </c>
+      <c r="F139" s="3" t="n">
+        <v>6714</v>
+      </c>
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
           <t>https://www.solobabys.com/products/panitos-happy-y-soft-x40-limpieza-suave-para-bebe</t>
         </is>
       </c>
-      <c r="K138" s="2" t="inlineStr">
+      <c r="K139" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/53.webp?v=1774121918</t>
         </is>
       </c>
-      <c r="L138" s="2" t="n">
+      <c r="L139" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M138" s="2" t="inlineStr">
+      <c r="M139" s="2" t="inlineStr">
         <is>
           <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M138"/>
+  <autoFilter ref="A1:M139"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7953,7 +8006,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C3" s="5" t="n"/>
       <c r="D3" s="5" t="n"/>
@@ -7965,7 +8018,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5">
@@ -7976,7 +8029,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-26 18:40</t>
+          <t>2026-10-27 00:34</t>
         </is>
       </c>
     </row>
@@ -8057,7 +8110,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -8029,7 +8029,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:34</t>
+          <t>2026-10-27 06:37</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -8029,7 +8029,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-27 06:37</t>
+          <t>2026-10-27 12:39</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -8029,7 +8029,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-27 12:39</t>
+          <t>2026-10-27 18:40</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -560,7 +560,7 @@
         <v>565000</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>807143</v>
+        <v>808000</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>510000</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>728571</v>
+        <v>729000</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>475000</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>678571</v>
+        <v>679000</v>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="n">
@@ -784,7 +784,7 @@
         <v>445000</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>635714</v>
+        <v>636000</v>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="n">
@@ -890,7 +890,7 @@
         <v>398000</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>568571</v>
+        <v>569000</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>320000</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>457143</v>
+        <v>458000</v>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="n">
@@ -1055,7 +1055,7 @@
         <v>211000</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>301429</v>
+        <v>302000</v>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="n">
@@ -1108,7 +1108,7 @@
         <v>200000</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>285714</v>
+        <v>286000</v>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="n">
@@ -1161,7 +1161,7 @@
         <v>192000</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>274286</v>
+        <v>275000</v>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="n">
@@ -1267,7 +1267,7 @@
         <v>155000</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>221429</v>
+        <v>222000</v>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="n">
@@ -1320,7 +1320,7 @@
         <v>155000</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>221429</v>
+        <v>222000</v>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="n">
@@ -1373,7 +1373,7 @@
         <v>152000</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>249900</v>
+        <v>250000</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>145000</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>207143</v>
+        <v>208000</v>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>145000</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>207143</v>
+        <v>208000</v>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="n">
@@ -1591,7 +1591,7 @@
         <v>138000</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>197143</v>
+        <v>198000</v>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>132500</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>189286</v>
+        <v>190000</v>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="n">
@@ -1701,7 +1701,7 @@
         <v>113000</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>161429</v>
+        <v>162000</v>
       </c>
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="n">
@@ -1754,7 +1754,7 @@
         <v>103000</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>161429</v>
+        <v>162000</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>104000</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>148571</v>
+        <v>149000</v>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="n">
@@ -1970,7 +1970,7 @@
         <v>100000</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>142857</v>
+        <v>143000</v>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="n">
@@ -2023,7 +2023,7 @@
         <v>96000</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>137143</v>
+        <v>138000</v>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="n">
@@ -2241,7 +2241,7 @@
         <v>92000</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>131429</v>
+        <v>132000</v>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="n">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
         <v>89000</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>127143</v>
+        <v>128000</v>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="n">
@@ -2608,7 +2608,7 @@
         <v>85000</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>121429</v>
+        <v>122000</v>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>82000</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>117143</v>
+        <v>118000</v>
       </c>
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="n">
@@ -2771,7 +2771,7 @@
         <v>79900</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>114143</v>
+        <v>115000</v>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="n">
@@ -2824,7 +2824,7 @@
         <v>78000</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>111429</v>
+        <v>112000</v>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="n">
@@ -2930,7 +2930,7 @@
         <v>72000</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>102857</v>
+        <v>103000</v>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="n">
@@ -3091,7 +3091,7 @@
         <v>67000</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>95714</v>
+        <v>96000</v>
       </c>
       <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="n">
@@ -3144,7 +3144,7 @@
         <v>65000</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>92900</v>
+        <v>93000</v>
       </c>
       <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="n">
@@ -3197,7 +3197,7 @@
         <v>65000</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>92857</v>
+        <v>93000</v>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>65000</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>79900</v>
+        <v>80000</v>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>62000</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>88571</v>
+        <v>89000</v>
       </c>
       <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="n">
@@ -3417,7 +3417,7 @@
         <v>60000</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>85714</v>
+        <v>86000</v>
       </c>
       <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="n">
@@ -3835,7 +3835,7 @@
         <v>55000</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>78571</v>
+        <v>79000</v>
       </c>
       <c r="G63" s="2" t="inlineStr"/>
       <c r="H63" s="2" t="n">
@@ -3941,7 +3941,7 @@
         <v>50500</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>72143</v>
+        <v>73000</v>
       </c>
       <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="2" t="n">
@@ -4316,7 +4316,7 @@
         <v>48000</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>68571</v>
+        <v>69000</v>
       </c>
       <c r="G72" s="2" t="inlineStr"/>
       <c r="H72" s="2" t="n">
@@ -4369,7 +4369,7 @@
         <v>47000</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>67143</v>
+        <v>68000</v>
       </c>
       <c r="G73" s="2" t="inlineStr"/>
       <c r="H73" s="2" t="n">
@@ -4422,7 +4422,7 @@
         <v>47000</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>67143</v>
+        <v>68000</v>
       </c>
       <c r="G74" s="2" t="inlineStr"/>
       <c r="H74" s="2" t="n">
@@ -4581,7 +4581,7 @@
         <v>46000</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>65714</v>
+        <v>66000</v>
       </c>
       <c r="G77" s="2" t="inlineStr"/>
       <c r="H77" s="2" t="n">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -4789,7 +4789,7 @@
         <v>40900</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>58429</v>
+        <v>59000</v>
       </c>
       <c r="G81" s="2" t="inlineStr"/>
       <c r="H81" s="2" t="n">
@@ -4842,7 +4842,7 @@
         <v>40000</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>57143</v>
+        <v>58000</v>
       </c>
       <c r="G82" s="2" t="inlineStr"/>
       <c r="H82" s="2" t="n">
@@ -4895,7 +4895,7 @@
         <v>40000</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>57143</v>
+        <v>58000</v>
       </c>
       <c r="G83" s="2" t="inlineStr"/>
       <c r="H83" s="2" t="n">
@@ -5005,7 +5005,7 @@
         <v>38000</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>54286</v>
+        <v>55000</v>
       </c>
       <c r="G85" s="2" t="inlineStr"/>
       <c r="H85" s="2" t="n">
@@ -5058,7 +5058,7 @@
         <v>37500</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>53571</v>
+        <v>54000</v>
       </c>
       <c r="G86" s="2" t="inlineStr"/>
       <c r="H86" s="2" t="n">
@@ -5111,7 +5111,7 @@
         <v>36000</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>51429</v>
+        <v>52000</v>
       </c>
       <c r="G87" s="2" t="inlineStr"/>
       <c r="H87" s="2" t="n">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -5376,7 +5376,7 @@
         <v>34000</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>47600</v>
+        <v>48000</v>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>33500</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>47857</v>
+        <v>48000</v>
       </c>
       <c r="G93" s="2" t="inlineStr"/>
       <c r="H93" s="2" t="n">
@@ -5539,7 +5539,7 @@
         <v>33000</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>47143</v>
+        <v>48000</v>
       </c>
       <c r="G95" s="2" t="inlineStr"/>
       <c r="H95" s="2" t="n">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -5592,7 +5592,7 @@
         <v>30700</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>43857</v>
+        <v>44000</v>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v>28500</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>40714</v>
+        <v>41000</v>
       </c>
       <c r="G97" s="2" t="inlineStr"/>
       <c r="H97" s="2" t="n">
@@ -5702,7 +5702,7 @@
         <v>28500</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>36900</v>
+        <v>37000</v>
       </c>
       <c r="G98" s="2" t="inlineStr"/>
       <c r="H98" s="2" t="n">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -5806,7 +5806,7 @@
         <v>27000</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>38571</v>
+        <v>39000</v>
       </c>
       <c r="G100" s="2" t="inlineStr"/>
       <c r="H100" s="2" t="n">
@@ -5859,7 +5859,7 @@
         <v>27000</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>38571</v>
+        <v>39000</v>
       </c>
       <c r="G101" s="2" t="inlineStr"/>
       <c r="H101" s="2" t="n">
@@ -5969,7 +5969,7 @@
         <v>25000</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>34900</v>
+        <v>35000</v>
       </c>
       <c r="G103" s="2" t="inlineStr"/>
       <c r="H103" s="2" t="n">
@@ -6022,7 +6022,7 @@
         <v>24000</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>34286</v>
+        <v>35000</v>
       </c>
       <c r="G104" s="2" t="inlineStr"/>
       <c r="H104" s="2" t="n">
@@ -6075,7 +6075,7 @@
         <v>22000</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>31429</v>
+        <v>32000</v>
       </c>
       <c r="G105" s="2" t="inlineStr"/>
       <c r="H105" s="2" t="n">
@@ -6128,7 +6128,7 @@
         <v>22000</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>31429</v>
+        <v>32000</v>
       </c>
       <c r="G106" s="2" t="inlineStr"/>
       <c r="H106" s="2" t="n">
@@ -6295,7 +6295,7 @@
         <v>21000</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>27600</v>
+        <v>28000</v>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>20500</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>27600</v>
+        <v>28000</v>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>19000</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>27143</v>
+        <v>28000</v>
       </c>
       <c r="G111" s="2" t="inlineStr"/>
       <c r="H111" s="2" t="n">
@@ -6462,7 +6462,7 @@
         <v>19000</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>27143</v>
+        <v>28000</v>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>18000</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>25714</v>
+        <v>26000</v>
       </c>
       <c r="G113" s="2" t="inlineStr"/>
       <c r="H113" s="2" t="n">
@@ -6572,7 +6572,7 @@
         <v>17500</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>22600</v>
+        <v>23000</v>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>16500</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>23571</v>
+        <v>24000</v>
       </c>
       <c r="G117" s="2" t="inlineStr"/>
       <c r="H117" s="2" t="n">
@@ -6794,7 +6794,7 @@
         <v>16000</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>22857</v>
+        <v>23000</v>
       </c>
       <c r="G118" s="2" t="inlineStr"/>
       <c r="H118" s="2" t="n">
@@ -6847,7 +6847,7 @@
         <v>14500</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>19900</v>
+        <v>20000</v>
       </c>
       <c r="G119" s="2" t="inlineStr"/>
       <c r="H119" s="2" t="n">
@@ -6953,7 +6953,7 @@
         <v>12500</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>17857</v>
+        <v>18000</v>
       </c>
       <c r="G121" s="2" t="inlineStr"/>
       <c r="H121" s="2" t="n">
@@ -7006,7 +7006,7 @@
         <v>12000</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>17143</v>
+        <v>17500</v>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>11000</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>15714</v>
+        <v>16000</v>
       </c>
       <c r="G123" s="2" t="inlineStr"/>
       <c r="H123" s="2" t="n">
@@ -7116,7 +7116,7 @@
         <v>11000</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>15714</v>
+        <v>16000</v>
       </c>
       <c r="G124" s="2" t="inlineStr"/>
       <c r="H124" s="2" t="n">
@@ -7169,7 +7169,7 @@
         <v>11000</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>15714</v>
+        <v>16000</v>
       </c>
       <c r="G125" s="2" t="inlineStr"/>
       <c r="H125" s="2" t="n">
@@ -7222,7 +7222,7 @@
         <v>10500</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>13600</v>
+        <v>14000</v>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>10400</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>14857</v>
+        <v>15000</v>
       </c>
       <c r="G128" s="2" t="inlineStr"/>
       <c r="H128" s="2" t="n">
@@ -7446,7 +7446,7 @@
         <v>10000</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>14286</v>
+        <v>14500</v>
       </c>
       <c r="G130" s="2" t="inlineStr"/>
       <c r="H130" s="2" t="n">
@@ -7499,7 +7499,7 @@
         <v>9900</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>14143</v>
+        <v>14500</v>
       </c>
       <c r="G131" s="2" t="inlineStr"/>
       <c r="H131" s="2" t="n">
@@ -7552,7 +7552,7 @@
         <v>9000</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>12857</v>
+        <v>13000</v>
       </c>
       <c r="G132" s="2" t="inlineStr"/>
       <c r="H132" s="2" t="n">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
@@ -7605,7 +7605,7 @@
         <v>8500</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>12143</v>
+        <v>12500</v>
       </c>
       <c r="G133" s="2" t="inlineStr"/>
       <c r="H133" s="2" t="n">
@@ -7823,7 +7823,7 @@
         <v>6500</v>
       </c>
       <c r="F137" s="3" t="n">
-        <v>9286</v>
+        <v>9300</v>
       </c>
       <c r="G137" s="2" t="inlineStr"/>
       <c r="H137" s="2" t="n">
@@ -7876,7 +7876,7 @@
         <v>6000</v>
       </c>
       <c r="F138" s="3" t="n">
-        <v>8571</v>
+        <v>8600</v>
       </c>
       <c r="G138" s="2" t="inlineStr"/>
       <c r="H138" s="2" t="n">
@@ -7929,7 +7929,7 @@
         <v>4700</v>
       </c>
       <c r="F139" s="3" t="n">
-        <v>6714</v>
+        <v>6800</v>
       </c>
       <c r="G139" s="2" t="inlineStr"/>
       <c r="H139" s="2" t="n">
@@ -8018,7 +8018,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5">
@@ -8029,7 +8029,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-27 18:40</t>
+          <t>2026-10-28 00:44</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -8029,7 +8029,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-28 00:44</t>
+          <t>2026-10-28 06:43</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -8029,7 +8029,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-28 06:43</t>
+          <t>2026-10-28 12:44</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -8029,7 +8029,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-28 12:44</t>
+          <t>2026-10-28 18:41</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -7081,11 +7081,11 @@
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage1jul2026_12_40_34p.m.webp?v=1782927688</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/descarga_10.webp?v=1793227107</t>
         </is>
       </c>
       <c r="L123" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
@@ -8029,7 +8029,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-28 18:41</t>
+          <t>2026-10-29 00:44</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -8029,7 +8029,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29 00:44</t>
+          <t>2026-10-29 06:46</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -8029,7 +8029,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29 06:46</t>
+          <t>2026-10-29 12:46</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -8029,7 +8029,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29 12:46</t>
+          <t>2026-10-29 18:44</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -8029,7 +8029,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29 18:44</t>
+          <t>2026-10-30 00:45</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -8029,7 +8029,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30 00:45</t>
+          <t>2026-10-30 06:47</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -8029,7 +8029,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30 06:47</t>
+          <t>2026-10-30 12:46</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$M$139</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$M$140</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M139"/>
+  <dimension ref="A1:M140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4348,11 +4348,11 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>10849657192758</v>
+        <v>15450059735350</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Lima Eléctrica para Uñas de Bebé</t>
+          <t>Libro de Estudio Interactivo Musical | Abecedario, Sonidos y Juegos</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4362,14 +4362,14 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado</t>
+          <t>Juguetes</t>
         </is>
       </c>
       <c r="E73" s="3" t="n">
-        <v>47000</v>
+        <v>47300</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>68000</v>
+        <v>58000</v>
       </c>
       <c r="G73" s="2" t="inlineStr"/>
       <c r="H73" s="2" t="n">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/lima-electrica-para-unas-de-bebe</t>
+          <t>https://www.solobabys.com/products/libro-de-estudio-interactivo-musical-abecedario-sonidos-y-juegos</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage15sept2026_14_09_36.webp?v=1789499433</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/libro-de-estudio-interactivo-1.png?v=1793378526</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
@@ -4395,17 +4395,17 @@
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-title { font-family: 'Fraunces', serif; font-size: 38px; line-height: 1.1; color: #00afba; margin: 0 0 15px 0; letter-spacin</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>10819647668534</v>
+        <v>10849657192758</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Mascota de Peluche Interactiva con Maletín | Lovely Pet</t>
+          <t>Lima Eléctrica para Uñas de Bebé</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Baby shower</t>
+          <t>Aseo y cuidado</t>
         </is>
       </c>
       <c r="E74" s="3" t="n">
@@ -4435,16 +4435,16 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/mascota-de-peluche-interactiva-con-maletin-lovely-pet</t>
+          <t>https://www.solobabys.com/products/lima-electrica-para-unas-de-bebe</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-08-21T164918.946.webp?v=1787349005</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage15sept2026_14_09_36.webp?v=1789499433</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
@@ -4454,11 +4454,11 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>10726814023990</v>
+        <v>10819647668534</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Plato + Cuchara Siliconada Cangrejo</t>
+          <t>Mascota de Peluche Interactiva con Maletín | Lovely Pet</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -4468,14 +4468,14 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Alimentación, Baby shower</t>
+          <t>Juguetes, Baby shower</t>
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>46200</v>
+        <v>47000</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>66000</v>
+        <v>68000</v>
       </c>
       <c r="G75" s="2" t="inlineStr"/>
       <c r="H75" s="2" t="n">
@@ -4488,16 +4488,16 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/plato-cuchara-siliconada-cangrejo</t>
+          <t>https://www.solobabys.com/products/mascota-de-peluche-interactiva-con-maletin-lovely-pet</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_57.webp?v=1779816409</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-08-21T164918.946.webp?v=1787349005</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
@@ -4507,11 +4507,11 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>15439275786550</v>
+        <v>10726814023990</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Perrito con Movimiento, Luz y Sonido | Camina Solito</t>
+          <t>Plato + Cuchara Siliconada Cangrejo</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4521,11 +4521,11 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Juguetes</t>
+          <t>Alimentación, Baby shower</t>
         </is>
       </c>
       <c r="E76" s="3" t="n">
-        <v>46000</v>
+        <v>46200</v>
       </c>
       <c r="F76" s="3" t="n">
         <v>66000</v>
@@ -4541,30 +4541,30 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/perrito-con-movimiento-luz-y-sonido-camina-solito</t>
+          <t>https://www.solobabys.com/products/plato-cuchara-siliconada-cangrejo</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/perrito-luz-sonido-1.jpg?v=1792866073</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_57.webp?v=1779816409</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-title { font-family: 'Fraunces', serif; font-size: 38px; line-height: 1.1; color: #00afba; margin: 0 0 15px 0; letter-spacin</t>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>10819653271862</v>
+        <v>15439275786550</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Camión Transformable en Robot 2 en 1 | Super Change Truck</t>
+          <t>Perrito con Movimiento, Luz y Sonido | Camina Solito</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Baby shower</t>
+          <t>Juguetes</t>
         </is>
       </c>
       <c r="E77" s="3" t="n">
@@ -4594,30 +4594,30 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/camion-transformable-en-robot-2-en-1-super-change-truck</t>
+          <t>https://www.solobabys.com/products/perrito-con-movimiento-luz-y-sonido-camina-solito</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-08-21T172546.714.webp?v=1787351184</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/perrito-luz-sonido-1.jpg?v=1792866073</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-title { font-family: 'Fraunces', serif; font-size: 38px; line-height: 1.1; color: #00afba; margin: 0 0 15px 0; letter-spacin</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>15407841476918</v>
+        <v>10819653271862</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Combo Plato 360° Antiderrames + Babero de Silicona</t>
+          <t>Camión Transformable en Robot 2 en 1 | Super Change Truck</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -4627,13 +4627,15 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Alimentación, Combos</t>
+          <t>Juguetes, Baby shower</t>
         </is>
       </c>
       <c r="E78" s="3" t="n">
-        <v>45000</v>
-      </c>
-      <c r="F78" s="3" t="n"/>
+        <v>46000</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>66000</v>
+      </c>
       <c r="G78" s="2" t="inlineStr"/>
       <c r="H78" s="2" t="n">
         <v>1</v>
@@ -4645,16 +4647,16 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/combo-plato-360-antiderrames-babero-de-silicona</t>
+          <t>https://www.solobabys.com/products/camion-transformable-en-robot-2-en-1-super-change-truck</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-29at3.32.35PM.webp?v=1791307237</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-08-21T172546.714.webp?v=1787351184</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
@@ -4664,11 +4666,11 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>10735539552566</v>
+        <v>15407841476918</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Semanario Mi Ropita 322-002 Sacos</t>
+          <t>Combo Plato 360° Antiderrames + Babero de Silicona</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -4678,11 +4680,11 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Recién nacido, Ropa, Baby shower, Más vendidos</t>
+          <t>Aseo y cuidado, Alimentación, Combos</t>
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>43000</v>
+        <v>45000</v>
       </c>
       <c r="F79" s="3" t="n"/>
       <c r="G79" s="2" t="inlineStr"/>
@@ -4691,21 +4693,21 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/semanario-mi-ropita-322-002-sacos-1</t>
+          <t>https://www.solobabys.com/products/combo-plato-360-antiderrames-babero-de-silicona</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-03T183144.604.webp?v=1780529685</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-29at3.32.35PM.webp?v=1791307237</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
@@ -4715,11 +4717,11 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>10810924826934</v>
+        <v>10735539552566</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Set Toalla con Capucha + 6 Babitas</t>
+          <t>Semanario Mi Ropita 322-002 Sacos</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4729,36 +4731,34 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Recién nacido, Cobijas y toallas, Baby shower, Más vendidos</t>
+          <t>Recién nacido, Ropa, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>42000</v>
-      </c>
-      <c r="F80" s="3" t="n">
-        <v>60000</v>
-      </c>
+        <v>43000</v>
+      </c>
+      <c r="F80" s="3" t="n"/>
       <c r="G80" s="2" t="inlineStr"/>
       <c r="H80" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/set-toalla-con-capucha-6-babitas</t>
+          <t>https://www.solobabys.com/products/semanario-mi-ropita-322-002-sacos-1</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-08-11T175525.349.webp?v=1786488969</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-03T183144.604.webp?v=1780529685</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
@@ -4768,11 +4768,11 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>10650947977526</v>
+        <v>10810924826934</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Crema Protectora Happy Soft 500gr | Cuidado y Protección para Bebé</t>
+          <t>Set Toalla con Capucha + 6 Babitas</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -4782,14 +4782,14 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower</t>
+          <t>Recién nacido, Cobijas y toallas, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E81" s="3" t="n">
-        <v>40900</v>
+        <v>42000</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>59000</v>
+        <v>60000</v>
       </c>
       <c r="G81" s="2" t="inlineStr"/>
       <c r="H81" s="2" t="n">
@@ -4802,16 +4802,16 @@
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/crema-protectora-happy-soft-500gr-cuidado-y-proteccion-para-bebe</t>
+          <t>https://www.solobabys.com/products/set-toalla-con-capucha-6-babitas</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_100.webp?v=1780298213</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-08-11T175525.349.webp?v=1786488969</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
@@ -4821,11 +4821,11 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>10829223625014</v>
+        <v>10650947977526</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Set de Bloques Didácticos de Construcción 37 Piezas</t>
+          <t>Crema Protectora Happy Soft 500gr | Cuidado y Protección para Bebé</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -4835,14 +4835,14 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Juguetes</t>
+          <t>Aseo y cuidado, Baby shower</t>
         </is>
       </c>
       <c r="E82" s="3" t="n">
-        <v>40000</v>
+        <v>40900</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>58000</v>
+        <v>59000</v>
       </c>
       <c r="G82" s="2" t="inlineStr"/>
       <c r="H82" s="2" t="n">
@@ -4855,16 +4855,16 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/set-de-bloques-didacticos-de-construccion-37-piezas</t>
+          <t>https://www.solobabys.com/products/crema-protectora-happy-soft-500gr-cuidado-y-proteccion-para-bebe</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-08-31T182839.165.webp?v=1788218975</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_100.webp?v=1780298213</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
@@ -4874,11 +4874,11 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>10762350395702</v>
+        <v>10829223625014</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Licuadora Portátil Juice Cup</t>
+          <t>Set de Bloques Didácticos de Construcción 37 Piezas</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Alimentación</t>
+          <t>Juguetes</t>
         </is>
       </c>
       <c r="E83" s="3" t="n">
@@ -4908,16 +4908,16 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/licuadora-portatil-juice-cup</t>
+          <t>https://www.solobabys.com/products/set-de-bloques-didacticos-de-construccion-37-piezas</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage1jul2026_11_02_29p.m.webp?v=1782965026</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-08-31T182839.165.webp?v=1788218975</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
@@ -4927,11 +4927,11 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>10651068825910</v>
+        <v>10762350395702</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Extractor manual de leche materna Only Baby</t>
+          <t>Licuadora Portátil Juice Cup</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -4941,22 +4941,18 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Recién nacido, Teteros, Lactancia, Baby shower, Más vendidos</t>
+          <t>Alimentación</t>
         </is>
       </c>
       <c r="E84" s="3" t="n">
-        <v>38500</v>
+        <v>40000</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>55000</v>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Transparente', 'Rosa', 'Verde', 'Azul']</t>
-        </is>
-      </c>
+        <v>58000</v>
+      </c>
+      <c r="G84" s="2" t="inlineStr"/>
       <c r="H84" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
@@ -4965,16 +4961,16 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/extractor-manual-de-leche-materna-only-baby</t>
+          <t>https://www.solobabys.com/products/licuadora-portatil-juice-cup</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla-2026-03-30T174249.061.webp?v=1774910588</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage1jul2026_11_02_29p.m.webp?v=1782965026</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
@@ -4984,11 +4980,11 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>10812587344182</v>
+        <v>10651068825910</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Set de Bloques Didácticos Infantil con Molino y Figuras</t>
+          <t>Extractor manual de leche materna Only Baby</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -4998,18 +4994,22 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Baby shower</t>
+          <t>Recién nacido, Teteros, Lactancia, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E85" s="3" t="n">
-        <v>38000</v>
+        <v>38500</v>
       </c>
       <c r="F85" s="3" t="n">
         <v>55000</v>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Transparente', 'Rosa', 'Verde', 'Azul']</t>
+        </is>
+      </c>
       <c r="H85" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
@@ -5018,16 +5018,16 @@
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/set-de-bloques-didacticos-infantil-con-molino-y-figuras</t>
+          <t>https://www.solobabys.com/products/extractor-manual-de-leche-materna-only-baby</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsApp_27.webp?v=1786661794</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla-2026-03-30T174249.061.webp?v=1774910588</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
@@ -5037,11 +5037,11 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>10649160843574</v>
+        <v>10812587344182</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Bacin Prakiplas 7337 Tortuga | 7709412827917</t>
+          <t>Set de Bloques Didácticos Infantil con Molino y Figuras</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -5051,14 +5051,14 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Bacinillas</t>
+          <t>Juguetes, Baby shower</t>
         </is>
       </c>
       <c r="E86" s="3" t="n">
-        <v>37500</v>
+        <v>38000</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>54000</v>
+        <v>55000</v>
       </c>
       <c r="G86" s="2" t="inlineStr"/>
       <c r="H86" s="2" t="n">
@@ -5071,16 +5071,16 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/adaptador-reductor-de-bano-infantil-diseno-tipo-carro</t>
+          <t>https://www.solobabys.com/products/set-de-bloques-didacticos-infantil-con-molino-y-figuras</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla-2026-03-28T160638.235.webp?v=1774732117</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsApp_27.webp?v=1786661794</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
@@ -5090,11 +5090,11 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>10762339385654</v>
+        <v>10649160843574</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Set Toalla con Capota + Babitas WaKid's</t>
+          <t>Bacin Prakiplas 7337 Tortuga | 7709412827917</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -5104,14 +5104,14 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Recién nacido, Cobijas y toallas, Baby shower, Más vendidos</t>
+          <t>Bacinillas</t>
         </is>
       </c>
       <c r="E87" s="3" t="n">
-        <v>36000</v>
+        <v>37500</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>52000</v>
+        <v>54000</v>
       </c>
       <c r="G87" s="2" t="inlineStr"/>
       <c r="H87" s="2" t="n">
@@ -5119,21 +5119,21 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/set-toalla-con-capota-babitas-wakids</t>
+          <t>https://www.solobabys.com/products/adaptador-reductor-de-bano-infantil-diseno-tipo-carro</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage1jul2026_10_34_42p.m.webp?v=1782963320</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla-2026-03-28T160638.235.webp?v=1774732117</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
@@ -5143,11 +5143,11 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>10861984448822</v>
+        <v>10762339385654</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Tapete Didáctico Plegable con Bolso de Transporte</t>
+          <t>Set Toalla con Capota + Babitas WaKid's</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -5157,14 +5157,14 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Baby shower</t>
+          <t>Recién nacido, Cobijas y toallas, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E88" s="3" t="n">
-        <v>35000</v>
+        <v>36000</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>50000</v>
+        <v>52000</v>
       </c>
       <c r="G88" s="2" t="inlineStr"/>
       <c r="H88" s="2" t="n">
@@ -5172,21 +5172,21 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/tapete-didactico-plegable-con-bolso-de-transporte</t>
+          <t>https://www.solobabys.com/products/set-toalla-con-capota-babitas-wakids</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-21at3.35.30PM_2.webp?v=1790029328</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage1jul2026_10_34_42p.m.webp?v=1782963320</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
@@ -5196,11 +5196,11 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>10645594538294</v>
+        <v>10861984448822</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Tapete inflable con agua para bebé</t>
+          <t>Tapete Didáctico Plegable con Bolso de Transporte</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Más vendidos</t>
+          <t>Juguetes, Baby shower</t>
         </is>
       </c>
       <c r="E89" s="3" t="n">
@@ -5230,16 +5230,16 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/tapete-inflable-con-agua-para-bebe</t>
+          <t>https://www.solobabys.com/products/tapete-didactico-plegable-con-bolso-de-transporte</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla-2026-03-27T144417.793.webp?v=1774640713</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-21at3.35.30PM_2.webp?v=1790029328</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
@@ -5249,11 +5249,11 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>10643504759094</v>
+        <v>10645594538294</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Extractor Eléctrico Portátil de Leche</t>
+          <t>Tapete inflable con agua para bebé</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Lactancia</t>
+          <t>Juguetes, Más vendidos</t>
         </is>
       </c>
       <c r="E90" s="3" t="n">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/extractor-manual-de-leche-materna</t>
+          <t>https://www.solobabys.com/products/tapete-inflable-con-agua-para-bebe</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla_87.webp?v=1774564344</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla-2026-03-27T144417.793.webp?v=1774640713</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
@@ -5302,11 +5302,11 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>10762503979318</v>
+        <v>10643504759094</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Chaleco para Moto Bebé</t>
+          <t>Extractor Eléctrico Portátil de Leche</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Accesorios, Baby shower</t>
+          <t>Lactancia</t>
         </is>
       </c>
       <c r="E91" s="3" t="n">
@@ -5331,21 +5331,21 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/chaleco-para-moto-bebe</t>
+          <t>https://www.solobabys.com/products/extractor-manual-de-leche-materna</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage2jul2026_06_52_50a.m.webp?v=1782993218</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla_87.webp?v=1774564344</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
@@ -5355,11 +5355,11 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>10650894762294</v>
+        <v>10762503979318</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Aspirador Nasal Eléctrico HENHR1228 | Limpieza Suave y Práctica para Bebé</t>
+          <t>Chaleco para Moto Bebé</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -5369,40 +5369,36 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower</t>
+          <t>Accesorios, Baby shower</t>
         </is>
       </c>
       <c r="E92" s="3" t="n">
-        <v>34000</v>
+        <v>35000</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>48000</v>
-      </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Rosa', 'Amarillo', 'Verde', 'Azul']</t>
-        </is>
-      </c>
+        <v>50000</v>
+      </c>
+      <c r="G92" s="2" t="inlineStr"/>
       <c r="H92" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/aspirador-nasal-electrico-henhr1228-limpieza-suave-y-practica-para-bebe</t>
+          <t>https://www.solobabys.com/products/chaleco-para-moto-bebe</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_41.webp?v=1779576241</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage2jul2026_06_52_50a.m.webp?v=1782993218</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
@@ -5412,11 +5408,11 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>10651903099190</v>
+        <v>10650894762294</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Bacín infantil Praktiplas Oso</t>
+          <t>Aspirador Nasal Eléctrico HENHR1228 | Limpieza Suave y Práctica para Bebé</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -5426,18 +5422,22 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Bacinillas</t>
+          <t>Aseo y cuidado, Baby shower</t>
         </is>
       </c>
       <c r="E93" s="3" t="n">
-        <v>33500</v>
+        <v>34000</v>
       </c>
       <c r="F93" s="3" t="n">
         <v>48000</v>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Rosa', 'Amarillo', 'Verde', 'Azul']</t>
+        </is>
+      </c>
       <c r="H93" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
@@ -5446,16 +5446,16 @@
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/bacin-infantil-praktiplas-oso</t>
+          <t>https://www.solobabys.com/products/aspirador-nasal-electrico-henhr1228-limpieza-suave-y-practica-para-bebe</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla-2026-04-01T122700.534.webp?v=1775064763</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_41.webp?v=1779576241</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
@@ -5465,11 +5465,11 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>15420728574262</v>
+        <v>10651903099190</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Perrito Superhéroe Musical con Luces | Super Electric Dog</t>
+          <t>Bacín infantil Praktiplas Oso</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -5479,14 +5479,14 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Juguetes</t>
+          <t>Bacinillas</t>
         </is>
       </c>
       <c r="E94" s="3" t="n">
-        <v>33000</v>
+        <v>33500</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>47000</v>
+        <v>48000</v>
       </c>
       <c r="G94" s="2" t="inlineStr"/>
       <c r="H94" s="2" t="n">
@@ -5499,30 +5499,30 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/perrito-superheroe-musical-con-luces-super-electric-dog</t>
+          <t>https://www.solobabys.com/products/bacin-infantil-praktiplas-oso</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/super-electric-dog-2.webp?v=1792063802</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla-2026-04-01T122700.534.webp?v=1775064763</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-title { font-family: 'Fraunces', serif; font-size: 38px; line-height: 1.1; color: #00afba; margin: 0 0 15px 0; letter-spacin</t>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>10649163104566</v>
+        <v>15420728574262</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Cobija capota animales Modelo CL1006</t>
+          <t>Perrito Superhéroe Musical con Luces | Super Electric Dog</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -5532,14 +5532,14 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Recién nacido, Cobijas y toallas, Baby shower, Más vendidos</t>
+          <t>Juguetes</t>
         </is>
       </c>
       <c r="E95" s="3" t="n">
         <v>33000</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>48000</v>
+        <v>47000</v>
       </c>
       <c r="G95" s="2" t="inlineStr"/>
       <c r="H95" s="2" t="n">
@@ -5547,35 +5547,35 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/cobija-capota-animales-modelo-cl1006</t>
+          <t>https://www.solobabys.com/products/perrito-superheroe-musical-con-luces-super-electric-dog</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-03-21at4.46.17PM_1.jpg?v=1774733372</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/super-electric-dog-2.webp?v=1792063802</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-title { font-family: 'Fraunces', serif; font-size: 38px; line-height: 1.1; color: #00afba; margin: 0 0 15px 0; letter-spacin</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>10721369522486</v>
+        <v>10649163104566</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Cepillo Lava Teteros | MST6608</t>
+          <t>Cobija capota animales Modelo CL1006</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -5585,36 +5585,32 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Teteros, Más vendidos</t>
+          <t>Recién nacido, Cobijas y toallas, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E96" s="3" t="n">
-        <v>30700</v>
+        <v>33000</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>44000</v>
-      </c>
-      <c r="G96" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Rojo', 'azul']</t>
-        </is>
-      </c>
+        <v>48000</v>
+      </c>
+      <c r="G96" s="2" t="inlineStr"/>
       <c r="H96" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/cepillo-lava-teteros-mst6608</t>
+          <t>https://www.solobabys.com/products/cobija-capota-animales-modelo-cl1006</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_17.webp?v=1779418188</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-03-21at4.46.17PM_1.jpg?v=1774733372</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
@@ -5628,11 +5624,11 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>10643571310902</v>
+        <v>10721369522486</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Toalla suave y absorbente para bebé</t>
+          <t>Cepillo Lava Teteros | MST6608</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -5642,18 +5638,22 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Cobijas y toallas, Baby shower</t>
+          <t>Teteros, Más vendidos</t>
         </is>
       </c>
       <c r="E97" s="3" t="n">
-        <v>28500</v>
+        <v>30700</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>41000</v>
-      </c>
-      <c r="G97" s="2" t="inlineStr"/>
+        <v>44000</v>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Rojo', 'azul']</t>
+        </is>
+      </c>
       <c r="H97" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
@@ -5662,12 +5662,12 @@
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/toalla-suave-y-absorbente-para-bebe</t>
+          <t>https://www.solobabys.com/products/cepillo-lava-teteros-mst6608</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-03-21at5.41.21PM_3.jpg?v=1774569011</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_17.webp?v=1779418188</t>
         </is>
       </c>
       <c r="L97" s="2" t="n">
@@ -5681,11 +5681,11 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>10643571573046</v>
+        <v>10643571310902</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Set de Aseo Kokibebe</t>
+          <t>Toalla suave y absorbente para bebé</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -5695,14 +5695,14 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower</t>
+          <t>Cobijas y toallas, Baby shower</t>
         </is>
       </c>
       <c r="E98" s="3" t="n">
         <v>28500</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>37000</v>
+        <v>41000</v>
       </c>
       <c r="G98" s="2" t="inlineStr"/>
       <c r="H98" s="2" t="n">
@@ -5710,21 +5710,21 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/set-de-aseo-kokibebe</t>
+          <t>https://www.solobabys.com/products/toalla-suave-y-absorbente-para-bebe</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla-2026-03-27T110341.589_a2241f01-ac70-4d1e-a938-52f6eaddf13d.webp?v=1774627574</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-03-21at5.41.21PM_3.jpg?v=1774569011</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
@@ -5734,11 +5734,11 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>10837689532726</v>
+        <v>10643571573046</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Ajuar prematuro para Bebé 5 Piezas – My Best Friends</t>
+          <t>Set de Aseo Kokibebe</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -5748,13 +5748,15 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Recién nacido, Ropa, Baby shower</t>
+          <t>Aseo y cuidado, Baby shower</t>
         </is>
       </c>
       <c r="E99" s="3" t="n">
-        <v>28000</v>
-      </c>
-      <c r="F99" s="3" t="n"/>
+        <v>28500</v>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>37000</v>
+      </c>
       <c r="G99" s="2" t="inlineStr"/>
       <c r="H99" s="2" t="n">
         <v>1</v>
@@ -5766,12 +5768,12 @@
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/ajuar-para-bebe-5-piezas-my-best-friends</t>
+          <t>https://www.solobabys.com/products/set-de-aseo-kokibebe</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-03at11.35.47AM_2.webp?v=1788819715</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla-2026-03-27T110341.589_a2241f01-ac70-4d1e-a938-52f6eaddf13d.webp?v=1774627574</t>
         </is>
       </c>
       <c r="L99" s="2" t="n">
@@ -5785,11 +5787,11 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>10837681799478</v>
+        <v>10837689532726</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Lima Eléctrica para Uñas de Bebé</t>
+          <t>Ajuar prematuro para Bebé 5 Piezas – My Best Friends</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -5799,36 +5801,34 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Juguetes</t>
+          <t>Recién nacido, Ropa, Baby shower</t>
         </is>
       </c>
       <c r="E100" s="3" t="n">
-        <v>27000</v>
-      </c>
-      <c r="F100" s="3" t="n">
-        <v>39000</v>
-      </c>
+        <v>28000</v>
+      </c>
+      <c r="F100" s="3" t="n"/>
       <c r="G100" s="2" t="inlineStr"/>
       <c r="H100" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/set-de-manicure-para-bebe</t>
+          <t>https://www.solobabys.com/products/ajuar-para-bebe-5-piezas-my-best-friends</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage7sept2026_17_09_49.webp?v=1788819099</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/WhatsAppImage2026-09-03at11.35.47AM_2.webp?v=1788819715</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
@@ -5838,11 +5838,11 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>10650935755062</v>
+        <v>10837681799478</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Crema Protectora Happy Soft 250gr | Cuidado y Protección para Bebé</t>
+          <t>Lima Eléctrica para Uñas de Bebé</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -5852,7 +5852,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower</t>
+          <t>Aseo y cuidado, Juguetes</t>
         </is>
       </c>
       <c r="E101" s="3" t="n">
@@ -5872,16 +5872,16 @@
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/crema-protectora-happy-soft-250gr-cuidado-y-proteccion-para-bebe</t>
+          <t>https://www.solobabys.com/products/set-de-manicure-para-bebe</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-01T022000.472.webp?v=1780298415</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage7sept2026_17_09_49.webp?v=1788819099</t>
         </is>
       </c>
       <c r="L101" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
@@ -5891,11 +5891,11 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>10642900058422</v>
+        <v>10650935755062</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Lima Eléctrica Only Baby | Cuidado Seguro de Uñas para Bebé</t>
+          <t>Crema Protectora Happy Soft 250gr | Cuidado y Protección para Bebé</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -5905,22 +5905,18 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Accesorios, Baby shower, Más vendidos</t>
+          <t>Aseo y cuidado, Baby shower</t>
         </is>
       </c>
       <c r="E102" s="3" t="n">
-        <v>25500</v>
+        <v>27000</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>27000</v>
-      </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Rosa', 'Azul']</t>
-        </is>
-      </c>
+        <v>39000</v>
+      </c>
+      <c r="G102" s="2" t="inlineStr"/>
       <c r="H102" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
@@ -5929,16 +5925,16 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/lima-electrica-only-baby-cuidado-seguro-de-unas-para-bebe</t>
+          <t>https://www.solobabys.com/products/crema-protectora-happy-soft-250gr-cuidado-y-proteccion-para-bebe</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/limaelectrica_1000x_b8a0febc-3486-42a7-a3cf-8a61cc5b6601.webp?v=1774036791</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-01T022000.472.webp?v=1780298415</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
@@ -5948,11 +5944,11 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>10643572031798</v>
+        <v>10642900058422</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Set Manicure Baby Care</t>
+          <t>Lima Eléctrica Only Baby | Cuidado Seguro de Uñas para Bebé</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -5966,14 +5962,18 @@
         </is>
       </c>
       <c r="E103" s="3" t="n">
-        <v>25000</v>
+        <v>25500</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>35000</v>
-      </c>
-      <c r="G103" s="2" t="inlineStr"/>
+        <v>27000</v>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Rosa', 'Azul']</t>
+        </is>
+      </c>
       <c r="H103" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/set-manicure-baby-care</t>
+          <t>https://www.solobabys.com/products/lima-electrica-only-baby-cuidado-seguro-de-unas-para-bebe</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla-2026-03-27T143126.593_2c7a959d-f5cc-459d-81e2-3ea14b4df0ba.webp?v=1774640025</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/limaelectrica_1000x_b8a0febc-3486-42a7-a3cf-8a61cc5b6601.webp?v=1774036791</t>
         </is>
       </c>
       <c r="L103" s="2" t="n">
@@ -6001,11 +6001,11 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>10651062665526</v>
+        <v>10643572031798</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Cobija TG 08 burbuja Diseños surtidos</t>
+          <t>Set Manicure Baby Care</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -6015,11 +6015,11 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Cobijas y toallas, Baby shower, Más vendidos</t>
+          <t>Aseo y cuidado, Accesorios, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E104" s="3" t="n">
-        <v>24000</v>
+        <v>25000</v>
       </c>
       <c r="F104" s="3" t="n">
         <v>35000</v>
@@ -6035,16 +6035,16 @@
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/cobija-tg-08-burbuja-disenos-surtidos</t>
+          <t>https://www.solobabys.com/products/set-manicure-baby-care</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_-_2026-06-03T163734.732.webp?v=1780522748</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla-2026-03-27T143126.593_2c7a959d-f5cc-459d-81e2-3ea14b4df0ba.webp?v=1774640025</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
@@ -6054,11 +6054,11 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>10762511089974</v>
+        <v>10651062665526</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>MORDEDOR CON CADENA ONLY| HLW-040</t>
+          <t>Cobija TG 08 burbuja Diseños surtidos</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -6068,14 +6068,14 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Baby shower</t>
+          <t>Cobijas y toallas, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E105" s="3" t="n">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>32000</v>
+        <v>35000</v>
       </c>
       <c r="G105" s="2" t="inlineStr"/>
       <c r="H105" s="2" t="n">
@@ -6088,30 +6088,30 @@
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/mordedor-con-sujetador-para-bebe</t>
+          <t>https://www.solobabys.com/products/cobija-tg-08-burbuja-disenos-surtidos</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage2jul2026_07_37_12a.m.webp?v=1782995871</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_-_2026-06-03T163734.732.webp?v=1780522748</t>
         </is>
       </c>
       <c r="L105" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container{font-family:'Quicksand',sans-serif;max-width:480px;margin:0 auto;color:#4a5568;padding:26px;background:#fff;} .b-rating{display:flex;align-items:center;gap:8px;margin-bottom:12px;font-size:14px;font-weight:700;color:#c8d431;flex-wrap:wrap;} .b-rating-text</t>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>10651054637366</v>
+        <v>10762511089974</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Cobija vilu cinta estampada Diseños surtidos</t>
+          <t>MORDEDOR CON CADENA ONLY| HLW-040</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Cobijas y toallas, Baby shower, Más vendidos</t>
+          <t>Juguetes, Baby shower</t>
         </is>
       </c>
       <c r="E106" s="3" t="n">
@@ -6141,30 +6141,30 @@
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/cobija-vilu-cinta-estampada-disenos-surtidos</t>
+          <t>https://www.solobabys.com/products/mordedor-con-sujetador-para-bebe</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_-_2026-06-02T212801.807.webp?v=1780453770</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage2jul2026_07_37_12a.m.webp?v=1782995871</t>
         </is>
       </c>
       <c r="L106" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container{font-family:'Quicksand',sans-serif;max-width:480px;margin:0 auto;color:#4a5568;padding:26px;background:#fff;} .b-rating{display:flex;align-items:center;gap:8px;margin-bottom:12px;font-size:14px;font-weight:700;color:#c8d431;flex-wrap:wrap;} .b-rating-text</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>10721360019766</v>
+        <v>10651054637366</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Termo Plegable Infantil Balón | JS-8</t>
+          <t>Cobija vilu cinta estampada Diseños surtidos</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -6174,22 +6174,18 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Alimentación</t>
+          <t>Cobijas y toallas, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E107" s="3" t="n">
         <v>22000</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>31000</v>
-      </c>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Blanco', 'Verde', 'azul']</t>
-        </is>
-      </c>
+        <v>32000</v>
+      </c>
+      <c r="G107" s="2" t="inlineStr"/>
       <c r="H107" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
@@ -6198,12 +6194,12 @@
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/termo-plegable-infantil-balon-js-8</t>
+          <t>https://www.solobabys.com/products/cobija-vilu-cinta-estampada-disenos-surtidos</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_14.webp?v=1779414355</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_-_2026-06-02T212801.807.webp?v=1780453770</t>
         </is>
       </c>
       <c r="L107" s="2" t="n">
@@ -6217,11 +6213,11 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>10721353236790</v>
+        <v>10721360019766</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Termo Plegable Infantil | JS-9</t>
+          <t>Termo Plegable Infantil Balón | JS-8</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -6231,7 +6227,7 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Alimentación, Baby shower</t>
+          <t>Alimentación</t>
         </is>
       </c>
       <c r="E108" s="3" t="n">
@@ -6242,11 +6238,11 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Color: ['Púrpura', 'Rosa']</t>
+          <t>Color: ['Blanco', 'Verde', 'azul']</t>
         </is>
       </c>
       <c r="H108" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
@@ -6255,16 +6251,16 @@
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/termo-plegable-infantil-js-9</t>
+          <t>https://www.solobabys.com/products/termo-plegable-infantil-balon-js-8</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_8.webp?v=1779411444</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_14.webp?v=1779414355</t>
         </is>
       </c>
       <c r="L108" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
@@ -6274,11 +6270,11 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>10643064684854</v>
+        <v>10721353236790</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Vaso Amazing Baby | MON1035</t>
+          <t>Termo Plegable Infantil | JS-9</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -6292,14 +6288,14 @@
         </is>
       </c>
       <c r="E109" s="3" t="n">
-        <v>21000</v>
+        <v>22000</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>28000</v>
+        <v>31000</v>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Color: ['Azul', 'Rosa']</t>
+          <t>Color: ['Púrpura', 'Rosa']</t>
         </is>
       </c>
       <c r="H109" s="2" t="n">
@@ -6312,16 +6308,16 @@
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/vaso-amazing-baby-vaso-entrenador-con-asas</t>
+          <t>https://www.solobabys.com/products/termo-plegable-infantil-js-9</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/sbproductos_3_1.webp?v=1774046605</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_8.webp?v=1779411444</t>
         </is>
       </c>
       <c r="L109" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
@@ -6331,11 +6327,11 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>10642009358646</v>
+        <v>10643064684854</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Tapete Foamy Rompecabezas Infantil | Piso Didáctico para Bebé y Niños</t>
+          <t>Vaso Amazing Baby | MON1035</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -6345,22 +6341,22 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Baby shower</t>
+          <t>Alimentación, Baby shower</t>
         </is>
       </c>
       <c r="E110" s="3" t="n">
-        <v>20500</v>
+        <v>21000</v>
       </c>
       <c r="F110" s="3" t="n">
         <v>28000</v>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Color: ['Frutas', 'Números', 'Letras']</t>
+          <t>Color: ['Azul', 'Rosa']</t>
         </is>
       </c>
       <c r="H110" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
@@ -6369,16 +6365,16 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/tapete-foamy-rompecabezas-infantil-piso-didactico-para-bebe-y-ninos</t>
+          <t>https://www.solobabys.com/products/vaso-amazing-baby-vaso-entrenador-con-asas</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/D_NQ_NP_2X_812378-CBT91060493341_082025-F.webp?v=1773965161</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/sbproductos_3_1.webp?v=1774046605</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
@@ -6388,11 +6384,11 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>10729673720118</v>
+        <v>10642009358646</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Tetero Only 8 Onzas | A2DJ</t>
+          <t>Tapete Foamy Rompecabezas Infantil | Piso Didáctico para Bebé y Niños</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -6402,18 +6398,22 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Teteros</t>
+          <t>Juguetes, Baby shower</t>
         </is>
       </c>
       <c r="E111" s="3" t="n">
-        <v>19000</v>
+        <v>20500</v>
       </c>
       <c r="F111" s="3" t="n">
         <v>28000</v>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Frutas', 'Números', 'Letras']</t>
+        </is>
+      </c>
       <c r="H111" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
@@ -6422,16 +6422,16 @@
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/tetero-only-8-onzas-a2dj</t>
+          <t>https://www.solobabys.com/products/tapete-foamy-rompecabezas-infantil-piso-didactico-para-bebe-y-ninos</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_88.webp?v=1780097838</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/D_NQ_NP_2X_812378-CBT91060493341_082025-F.webp?v=1773965161</t>
         </is>
       </c>
       <c r="L111" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
@@ -6441,11 +6441,11 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>10651909718326</v>
+        <v>10729673720118</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Orinal infantil Praktiplas Pingüino</t>
+          <t>Tetero Only 8 Onzas | A2DJ</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -6455,7 +6455,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Bacinillas, Más vendidos</t>
+          <t>Teteros</t>
         </is>
       </c>
       <c r="E112" s="3" t="n">
@@ -6464,13 +6464,9 @@
       <c r="F112" s="3" t="n">
         <v>28000</v>
       </c>
-      <c r="G112" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Aguamarina', 'Negro']</t>
-        </is>
-      </c>
+      <c r="G112" s="2" t="inlineStr"/>
       <c r="H112" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
@@ -6479,12 +6475,12 @@
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/orinal-infantil-praktiplas-pinguino</t>
+          <t>https://www.solobabys.com/products/tetero-only-8-onzas-a2dj</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_51.webp?v=1779814860</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_88.webp?v=1780097838</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
@@ -6498,11 +6494,11 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>10649149767990</v>
+        <v>10651909718326</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Bolsas de almacenamiento de leche materna | ONBY-1</t>
+          <t>Orinal infantil Praktiplas Pingüino</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -6512,18 +6508,22 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Recién nacido, Lactancia, Baby shower</t>
+          <t>Bacinillas, Más vendidos</t>
         </is>
       </c>
       <c r="E113" s="3" t="n">
-        <v>18000</v>
+        <v>19000</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>26000</v>
-      </c>
-      <c r="G113" s="2" t="inlineStr"/>
+        <v>28000</v>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Aguamarina', 'Negro']</t>
+        </is>
+      </c>
       <c r="H113" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
@@ -6532,16 +6532,16 @@
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/bolsas-de-almacenamiento-de-leche-materna-250-ml-x-30-unidades</t>
+          <t>https://www.solobabys.com/products/orinal-infantil-praktiplas-pinguino</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_-_2026-06-02T205506.029.webp?v=1780451739</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_51.webp?v=1779814860</t>
         </is>
       </c>
       <c r="L113" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
@@ -6551,11 +6551,11 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>10642865127734</v>
+        <v>10649149767990</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Tetero Only Baby Natural 9oz / 260ml | Alimentación para Bebé</t>
+          <t>Bolsas de almacenamiento de leche materna | ONBY-1</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -6565,22 +6565,18 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Teteros, Baby shower, Más vendidos</t>
+          <t>Recién nacido, Lactancia, Baby shower</t>
         </is>
       </c>
       <c r="E114" s="3" t="n">
-        <v>17500</v>
+        <v>18000</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>23000</v>
-      </c>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Rosa', 'Azul', 'Transparente']</t>
-        </is>
-      </c>
+        <v>26000</v>
+      </c>
+      <c r="G114" s="2" t="inlineStr"/>
       <c r="H114" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
@@ -6589,12 +6585,12 @@
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/tetero-only-baby-natural-8oz-260ml-alimentacion-para-bebe</t>
+          <t>https://www.solobabys.com/products/bolsas-de-almacenamiento-de-leche-materna-250-ml-x-30-unidades</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_74.webp?v=1779927570</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_-_2026-06-02T205506.029.webp?v=1780451739</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
@@ -6608,11 +6604,11 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>10727775371574</v>
+        <v>10642865127734</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Cepillo Lava Tetero Only Baby A-71</t>
+          <t>Tetero Only Baby Natural 9oz / 260ml | Alimentación para Bebé</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -6622,20 +6618,22 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Teteros</t>
+          <t>Teteros, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E115" s="3" t="n">
         <v>17500</v>
       </c>
-      <c r="F115" s="3" t="n"/>
+      <c r="F115" s="3" t="n">
+        <v>23000</v>
+      </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Color: ['Azul', 'Rosa']</t>
+          <t>Color: ['Rosa', 'Azul', 'Transparente']</t>
         </is>
       </c>
       <c r="H115" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
@@ -6644,12 +6642,12 @@
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/cepillo-lava-tetero-only-baby-a-71</t>
+          <t>https://www.solobabys.com/products/tetero-only-baby-natural-8oz-260ml-alimentacion-para-bebe</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_71.webp?v=1779925711</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_74.webp?v=1779927570</t>
         </is>
       </c>
       <c r="L115" s="2" t="n">
@@ -6663,11 +6661,11 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>10642845761846</v>
+        <v>10727775371574</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Tetero Only Baby Natural 4oz / 125ml | Anticólicos con Asas</t>
+          <t>Cepillo Lava Tetero Only Baby A-71</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -6677,22 +6675,20 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Teteros, Baby shower, Más vendidos</t>
+          <t>Teteros</t>
         </is>
       </c>
       <c r="E116" s="3" t="n">
-        <v>17000</v>
-      </c>
-      <c r="F116" s="3" t="n">
-        <v>22000</v>
-      </c>
+        <v>17500</v>
+      </c>
+      <c r="F116" s="3" t="n"/>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Color: ['Rosa', 'Azul', 'Transparente']</t>
+          <t>Color: ['Azul', 'Rosa']</t>
         </is>
       </c>
       <c r="H116" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
@@ -6701,12 +6697,12 @@
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/tetero-only-baby-natural-4oz-125ml-anticolicos-con-asas</t>
+          <t>https://www.solobabys.com/products/cepillo-lava-tetero-only-baby-a-71</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/sbproductos_1_2.webp?v=1774025676</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_71.webp?v=1779925711</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
@@ -6720,11 +6716,11 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>10643479331126</v>
+        <v>10642845761846</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Copa recolectora de leche materna</t>
+          <t>Tetero Only Baby Natural 4oz / 125ml | Anticólicos con Asas</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -6734,18 +6730,22 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Recién nacido, Lactancia, Más vendidos</t>
+          <t>Teteros, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E117" s="3" t="n">
-        <v>16500</v>
+        <v>17000</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>24000</v>
-      </c>
-      <c r="G117" s="2" t="inlineStr"/>
+        <v>22000</v>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Rosa', 'Azul', 'Transparente']</t>
+        </is>
+      </c>
       <c r="H117" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
@@ -6754,12 +6754,12 @@
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/fular-cole-portabebe-ergonomico</t>
+          <t>https://www.solobabys.com/products/tetero-only-baby-natural-4oz-125ml-anticolicos-con-asas</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla_55.webp?v=1774162492</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/sbproductos_1_2.webp?v=1774025676</t>
         </is>
       </c>
       <c r="L117" s="2" t="n">
@@ -6773,11 +6773,11 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>10741795520822</v>
+        <v>10643479331126</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Lima eléctrica para Bebé | V168</t>
+          <t>Copa recolectora de leche materna</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -6787,14 +6787,14 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower, Más vendidos</t>
+          <t>Recién nacido, Lactancia, Más vendidos</t>
         </is>
       </c>
       <c r="E118" s="3" t="n">
-        <v>16000</v>
+        <v>16500</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>23000</v>
+        <v>24000</v>
       </c>
       <c r="G118" s="2" t="inlineStr"/>
       <c r="H118" s="2" t="n">
@@ -6807,12 +6807,12 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/cortaunas-electrico-para-bebe-v168</t>
+          <t>https://www.solobabys.com/products/fular-cole-portabebe-ergonomico</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-09T172638.946.webp?v=1781044015</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/Pantalla_55.webp?v=1774162492</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
@@ -6826,11 +6826,11 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>10643571147062</v>
+        <v>10741795520822</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Medias estilo española para bebé</t>
+          <t>Lima eléctrica para Bebé | V168</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -6840,14 +6840,14 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Ropa, Baby shower</t>
+          <t>Aseo y cuidado, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E119" s="3" t="n">
-        <v>14500</v>
+        <v>16000</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>20000</v>
+        <v>23000</v>
       </c>
       <c r="G119" s="2" t="inlineStr"/>
       <c r="H119" s="2" t="n">
@@ -6860,12 +6860,12 @@
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/medias-estilo-espanola-para-bebe</t>
+          <t>https://www.solobabys.com/products/cortaunas-electrico-para-bebe-v168</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_-_2026-08-14T185137.710.webp?v=1786751525</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-09T172638.946.webp?v=1781044015</t>
         </is>
       </c>
       <c r="L119" s="2" t="n">
@@ -6879,11 +6879,11 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>10730172449078</v>
+        <v>10643571147062</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Aspirador Nasal Boogy | 20931</t>
+          <t>Medias estilo española para bebé</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -6893,11 +6893,11 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower</t>
+          <t>Ropa, Baby shower</t>
         </is>
       </c>
       <c r="E120" s="3" t="n">
-        <v>14000</v>
+        <v>14500</v>
       </c>
       <c r="F120" s="3" t="n">
         <v>20000</v>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/aspirador-nasal-boogy-20931</t>
+          <t>https://www.solobabys.com/products/medias-estilo-espanola-para-bebe</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_99.webp?v=1780185614</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_-_2026-08-14T185137.710.webp?v=1786751525</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
@@ -6932,11 +6932,11 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>10650919108918</v>
+        <v>10730172449078</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Crema Protectora Happy Soft 60gr | Cuidado y Protección para Bebé</t>
+          <t>Aspirador Nasal Boogy | 20931</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -6950,10 +6950,10 @@
         </is>
       </c>
       <c r="E121" s="3" t="n">
-        <v>12500</v>
+        <v>14000</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>18000</v>
+        <v>20000</v>
       </c>
       <c r="G121" s="2" t="inlineStr"/>
       <c r="H121" s="2" t="n">
@@ -6966,16 +6966,16 @@
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/crema-protectora-happy-soft-60gr-cuidado-y-proteccion-para-bebe</t>
+          <t>https://www.solobabys.com/products/aspirador-nasal-boogy-20931</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-01T022221.997.webp?v=1780299053</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_99.webp?v=1780185614</t>
         </is>
       </c>
       <c r="L121" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
@@ -6985,11 +6985,11 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>10651924660534</v>
+        <v>10650919108918</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Bacín infantil Praktiplas Rana</t>
+          <t>Crema Protectora Happy Soft 60gr | Cuidado y Protección para Bebé</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -6999,22 +6999,18 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Bacinillas</t>
+          <t>Aseo y cuidado, Baby shower</t>
         </is>
       </c>
       <c r="E122" s="3" t="n">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>17500</v>
-      </c>
-      <c r="G122" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Aguamarina', 'Azul', 'fucsia']</t>
-        </is>
-      </c>
+        <v>18000</v>
+      </c>
+      <c r="G122" s="2" t="inlineStr"/>
       <c r="H122" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
@@ -7023,16 +7019,16 @@
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/bacin-infantil-praktiplas-rana</t>
+          <t>https://www.solobabys.com/products/crema-protectora-happy-soft-60gr-cuidado-y-proteccion-para-bebe</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_44.webp?v=1779577786</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-01T022221.997.webp?v=1780299053</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
@@ -7042,11 +7038,11 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>10762017669430</v>
+        <v>10651924660534</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Mordedor Control Silicona para Bebé</t>
+          <t>Bacín infantil Praktiplas Rana</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -7056,18 +7052,22 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Baby shower, Más vendidos</t>
+          <t>Bacinillas</t>
         </is>
       </c>
       <c r="E123" s="3" t="n">
-        <v>11000</v>
+        <v>12000</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>16000</v>
-      </c>
-      <c r="G123" s="2" t="inlineStr"/>
+        <v>17500</v>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Aguamarina', 'Azul', 'fucsia']</t>
+        </is>
+      </c>
       <c r="H123" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
@@ -7076,30 +7076,30 @@
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/mordedor-control-silicona-para-bebe</t>
+          <t>https://www.solobabys.com/products/bacin-infantil-praktiplas-rana</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/descarga_10.webp?v=1793227107</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_44.webp?v=1779577786</t>
         </is>
       </c>
       <c r="L123" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>```html @import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color</t>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>10736632987958</v>
+        <v>10762017669430</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Mordedor Only Baby Dino</t>
+          <t>Mordedor Control Silicona para Bebé</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Baby shower</t>
+          <t>Juguetes, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E124" s="3" t="n">
@@ -7129,30 +7129,30 @@
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/mordedor-only-baby-dino</t>
+          <t>https://www.solobabys.com/products/mordedor-control-silicona-para-bebe</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-05T183301.061.webp?v=1780702402</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/descarga_10.webp?v=1793227107</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
+          <t>```html @import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>10652006547766</v>
+        <v>10736632987958</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Rascaencias Figuras AB-27 | Alivio para la Dentición del Bebé</t>
+          <t>Mordedor Only Baby Dino</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -7182,16 +7182,16 @@
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/rascaencias-figuras-ab-27-alivio-para-la-denticion-del-bebe</t>
+          <t>https://www.solobabys.com/products/mordedor-only-baby-dino</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/D_NQ_NP_900595-MLA91560968768_092025-O_EmbellecedordeProducto.webp?v=1775076453</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-05T183301.061.webp?v=1780702402</t>
         </is>
       </c>
       <c r="L125" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
@@ -7201,11 +7201,11 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>10642154062134</v>
+        <v>10652006547766</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Tetero Only Baby Natural 2oz / 60ml | Alimentación para Bebé</t>
+          <t>Rascaencias Figuras AB-27 | Alivio para la Dentición del Bebé</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -7215,22 +7215,18 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Teteros, Baby shower</t>
+          <t>Juguetes, Baby shower</t>
         </is>
       </c>
       <c r="E126" s="3" t="n">
-        <v>10500</v>
+        <v>11000</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>14000</v>
-      </c>
-      <c r="G126" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Azul', 'Rosa', 'Transparente']</t>
-        </is>
-      </c>
+        <v>16000</v>
+      </c>
+      <c r="G126" s="2" t="inlineStr"/>
       <c r="H126" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
@@ -7239,30 +7235,30 @@
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/tetero-only-baby-natural-2oz-60ml-alimentacion-para-bebe</t>
+          <t>https://www.solobabys.com/products/rascaencias-figuras-ab-27-alivio-para-la-denticion-del-bebe</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_Image_5_may_2026_10_26_07_a.m..webp?v=1777995497</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/D_NQ_NP_900595-MLA91560968768_092025-O_EmbellecedordeProducto.webp?v=1775076453</t>
         </is>
       </c>
       <c r="L126" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #ffb80</t>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>10642902548790</v>
+        <v>10642154062134</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Guante Mordedor para Bebé | Alivio para Encías</t>
+          <t>Tetero Only Baby Natural 2oz / 60ml | Alimentación para Bebé</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -7272,18 +7268,18 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Accesorios, Baby shower, Más vendidos</t>
+          <t>Teteros, Baby shower</t>
         </is>
       </c>
       <c r="E127" s="3" t="n">
         <v>10500</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>15000</v>
+        <v>14000</v>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Color: ['Rosa', 'Azul', 'Verde']</t>
+          <t>Color: ['Azul', 'Rosa', 'Transparente']</t>
         </is>
       </c>
       <c r="H127" s="2" t="n">
@@ -7296,30 +7292,30 @@
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/guante-mordedor-para-bebe-alivio-para-encias</t>
+          <t>https://www.solobabys.com/products/tetero-only-baby-natural-2oz-60ml-alimentacion-para-bebe</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_64.webp?v=1779828393</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_Image_5_may_2026_10_26_07_a.m..webp?v=1777995497</t>
         </is>
       </c>
       <c r="L127" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #ffb80</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>10643478675766</v>
+        <v>10642902548790</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Pañitos Happy y Soft x100 | Limpieza Suave para Bebé</t>
+          <t>Guante Mordedor para Bebé | Alivio para Encías</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -7329,18 +7325,22 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower</t>
+          <t>Juguetes, Accesorios, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E128" s="3" t="n">
-        <v>10400</v>
+        <v>10500</v>
       </c>
       <c r="F128" s="3" t="n">
         <v>15000</v>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Rosa', 'Azul', 'Verde']</t>
+        </is>
+      </c>
       <c r="H128" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
@@ -7349,16 +7349,16 @@
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/panitos-happy-y-soft-x100-limpieza-suave-para-bebe</t>
+          <t>https://www.solobabys.com/products/guante-mordedor-para-bebe-alivio-para-encias</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/55.webp?v=1774123726</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_64.webp?v=1779828393</t>
         </is>
       </c>
       <c r="L128" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
@@ -7368,11 +7368,11 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>10651904344374</v>
+        <v>10643478675766</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Rascaencias Jirafa LW3 | Alivio para la Dentición del Bebé</t>
+          <t>Pañitos Happy y Soft x100 | Limpieza Suave para Bebé</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -7382,22 +7382,18 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Accesorios, Baby shower</t>
+          <t>Aseo y cuidado, Baby shower</t>
         </is>
       </c>
       <c r="E129" s="3" t="n">
-        <v>10000</v>
+        <v>10400</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>14000</v>
-      </c>
-      <c r="G129" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Amarillo', 'Rosa', 'Verde']</t>
-        </is>
-      </c>
+        <v>15000</v>
+      </c>
+      <c r="G129" s="2" t="inlineStr"/>
       <c r="H129" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
@@ -7406,16 +7402,16 @@
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/rascaencias-jirafa-lw3-alivio-para-la-denticion-del-bebe</t>
+          <t>https://www.solobabys.com/products/panitos-happy-y-soft-x100-limpieza-suave-para-bebe</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/1740126304665_1.webp?v=1775065667</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/55.webp?v=1774123726</t>
         </is>
       </c>
       <c r="L129" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
@@ -7425,11 +7421,11 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>10762342793526</v>
+        <v>10651904344374</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Babero Siliconado Ajustable</t>
+          <t>Rascaencias Jirafa LW3 | Alivio para la Dentición del Bebé</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -7439,18 +7435,22 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Alimentación, Baby shower</t>
+          <t>Juguetes, Accesorios, Baby shower</t>
         </is>
       </c>
       <c r="E130" s="3" t="n">
         <v>10000</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>14500</v>
-      </c>
-      <c r="G130" s="2" t="inlineStr"/>
+        <v>14000</v>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Amarillo', 'Rosa', 'Verde']</t>
+        </is>
+      </c>
       <c r="H130" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
@@ -7459,16 +7459,16 @@
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/babero-siliconado-ajustable</t>
+          <t>https://www.solobabys.com/products/rascaencias-jirafa-lw3-alivio-para-la-denticion-del-bebe</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage1jul2026_10_45_36p.m.webp?v=1782964027</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/1740126304665_1.webp?v=1775065667</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
@@ -7478,11 +7478,11 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>10762507878710</v>
+        <v>10762342793526</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Mordedor Control Only Baby</t>
+          <t>Babero Siliconado Ajustable</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -7492,11 +7492,11 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Juguetes, Baby shower, Más vendidos</t>
+          <t>Alimentación, Baby shower</t>
         </is>
       </c>
       <c r="E131" s="3" t="n">
-        <v>9900</v>
+        <v>10000</v>
       </c>
       <c r="F131" s="3" t="n">
         <v>14500</v>
@@ -7512,16 +7512,16 @@
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/mordedor-control-only-baby</t>
+          <t>https://www.solobabys.com/products/babero-siliconado-ajustable</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage2jul2026_07_10_28a.m.webp?v=1782994278</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage1jul2026_10_45_36p.m.webp?v=1782964027</t>
         </is>
       </c>
       <c r="L131" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
@@ -7531,11 +7531,11 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>10742260891958</v>
+        <v>10762507878710</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>CHUPA FRUTA ONLY BABY | C-40</t>
+          <t>Mordedor Control Only Baby</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -7545,14 +7545,14 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Alimentación, Más vendidos</t>
+          <t>Juguetes, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E132" s="3" t="n">
-        <v>9000</v>
+        <v>9900</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>13000</v>
+        <v>14500</v>
       </c>
       <c r="G132" s="2" t="inlineStr"/>
       <c r="H132" s="2" t="n">
@@ -7560,21 +7560,21 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/chupa-fruta-only-baby-c-40</t>
+          <t>https://www.solobabys.com/products/mordedor-control-only-baby</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-09T215325.108.webp?v=1781060037</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage2jul2026_07_10_28a.m.webp?v=1782994278</t>
         </is>
       </c>
       <c r="L132" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
@@ -7584,11 +7584,11 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>10762510303542</v>
+        <v>10742260891958</v>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Termómetro Digital Infantil</t>
+          <t>CHUPA FRUTA ONLY BABY | C-40</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -7598,14 +7598,14 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower, Más vendidos</t>
+          <t>Alimentación, Más vendidos</t>
         </is>
       </c>
       <c r="E133" s="3" t="n">
-        <v>8500</v>
+        <v>9000</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>12500</v>
+        <v>13000</v>
       </c>
       <c r="G133" s="2" t="inlineStr"/>
       <c r="H133" s="2" t="n">
@@ -7613,21 +7613,21 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/termometro-digital-infantil</t>
+          <t>https://www.solobabys.com/products/chupa-fruta-only-baby-c-40</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage2jul2026_07_22_20a.m.webp?v=1782994980</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-09T215325.108.webp?v=1781060037</t>
         </is>
       </c>
       <c r="L133" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
@@ -7637,11 +7637,11 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>10642922602806</v>
+        <v>10762510303542</v>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Vajilla Love With para Bebé | 939BB</t>
+          <t>Termómetro Digital Infantil</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -7651,22 +7651,18 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Alimentación, Baby shower</t>
+          <t>Aseo y cuidado, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E134" s="3" t="n">
-        <v>7500</v>
+        <v>8500</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>9000</v>
-      </c>
-      <c r="G134" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Verde', 'Naranja', 'Azul', 'Aguamarina']</t>
-        </is>
-      </c>
+        <v>12500</v>
+      </c>
+      <c r="G134" s="2" t="inlineStr"/>
       <c r="H134" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
@@ -7675,12 +7671,12 @@
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/vajilla-love-with-para-bebe-plato-infantil-con-diseno-divertido</t>
+          <t>https://www.solobabys.com/products/termometro-digital-infantil</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/39.webp?v=1774040907</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPTImage2jul2026_07_22_20a.m.webp?v=1782994980</t>
         </is>
       </c>
       <c r="L134" s="2" t="n">
@@ -7694,11 +7690,11 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>10726877331766</v>
+        <v>10642922602806</v>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Cepillo Dental Siliconado 360° para Bebés</t>
+          <t>Vajilla Love With para Bebé | 939BB</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -7708,16 +7704,22 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Más vendidos</t>
+          <t>Alimentación, Baby shower</t>
         </is>
       </c>
       <c r="E135" s="3" t="n">
         <v>7500</v>
       </c>
-      <c r="F135" s="3" t="n"/>
-      <c r="G135" s="2" t="inlineStr"/>
+      <c r="F135" s="3" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Verde', 'Naranja', 'Azul', 'Aguamarina']</t>
+        </is>
+      </c>
       <c r="H135" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
@@ -7726,16 +7728,16 @@
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/cepillo-dental-siliconado-360-para-bebes</t>
+          <t>https://www.solobabys.com/products/vajilla-love-with-para-bebe-plato-infantil-con-diseno-divertido</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_62.webp?v=1779825817</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/39.webp?v=1774040907</t>
         </is>
       </c>
       <c r="L135" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
@@ -7745,11 +7747,11 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>10643440664886</v>
+        <v>10726877331766</v>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Aspirador Nasal Only Baby | HENFZ11</t>
+          <t>Cepillo Dental Siliconado 360° para Bebés</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -7759,22 +7761,16 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower</t>
+          <t>Aseo y cuidado, Más vendidos</t>
         </is>
       </c>
       <c r="E136" s="3" t="n">
-        <v>6500</v>
-      </c>
-      <c r="F136" s="3" t="n">
-        <v>7000</v>
-      </c>
-      <c r="G136" s="2" t="inlineStr">
-        <is>
-          <t>Color: ['Azul', 'Rosa']</t>
-        </is>
-      </c>
+        <v>7500</v>
+      </c>
+      <c r="F136" s="3" t="n"/>
+      <c r="G136" s="2" t="inlineStr"/>
       <c r="H136" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
@@ -7783,16 +7779,16 @@
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/aspirador-nasal-only-baby-limpieza-suave-para-bebe</t>
+          <t>https://www.solobabys.com/products/cepillo-dental-siliconado-360-para-bebes</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/aspirador-nasal-azul-para-bebe.webp?v=1774108168</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_62.webp?v=1779825817</t>
         </is>
       </c>
       <c r="L136" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
@@ -7802,11 +7798,11 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>10728210792758</v>
+        <v>10643440664886</v>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Set Manicure Bebé | JJ250347</t>
+          <t>Aspirador Nasal Only Baby | HENFZ11</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -7816,18 +7812,22 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado</t>
+          <t>Aseo y cuidado, Baby shower</t>
         </is>
       </c>
       <c r="E137" s="3" t="n">
         <v>6500</v>
       </c>
       <c r="F137" s="3" t="n">
-        <v>9300</v>
-      </c>
-      <c r="G137" s="2" t="inlineStr"/>
+        <v>7000</v>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>Color: ['Azul', 'Rosa']</t>
+        </is>
+      </c>
       <c r="H137" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
@@ -7836,16 +7836,16 @@
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/set-manicure-bebe-jj250347</t>
+          <t>https://www.solobabys.com/products/aspirador-nasal-only-baby-limpieza-suave-para-bebe</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_81.webp?v=1780001979</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/aspirador-nasal-azul-para-bebe.webp?v=1774108168</t>
         </is>
       </c>
       <c r="L137" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
@@ -7855,11 +7855,11 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>10743245766966</v>
+        <v>10728210792758</v>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Cepillo Lengua Only Baby | FZ-121</t>
+          <t>Set Manicure Bebé | JJ250347</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -7869,14 +7869,14 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower, Más vendidos</t>
+          <t>Aseo y cuidado</t>
         </is>
       </c>
       <c r="E138" s="3" t="n">
-        <v>6000</v>
+        <v>6500</v>
       </c>
       <c r="F138" s="3" t="n">
-        <v>8600</v>
+        <v>9300</v>
       </c>
       <c r="G138" s="2" t="inlineStr"/>
       <c r="H138" s="2" t="n">
@@ -7889,16 +7889,16 @@
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>https://www.solobabys.com/products/cepillo-lengua-only-baby-fz-121</t>
+          <t>https://www.solobabys.com/products/set-manicure-bebe-jj250347</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-10T193401.800.webp?v=1781138064</t>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT_81.webp?v=1780001979</t>
         </is>
       </c>
       <c r="L138" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
@@ -7908,11 +7908,11 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>10643473727798</v>
+        <v>10743245766966</v>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Pañitos Happy y Soft x40 | Limpieza Suave para Bebé</t>
+          <t>Cepillo Lengua Only Baby | FZ-121</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -7922,14 +7922,14 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Aseo y cuidado, Baby shower</t>
+          <t>Aseo y cuidado, Baby shower, Más vendidos</t>
         </is>
       </c>
       <c r="E139" s="3" t="n">
-        <v>4700</v>
+        <v>6000</v>
       </c>
       <c r="F139" s="3" t="n">
-        <v>6800</v>
+        <v>8600</v>
       </c>
       <c r="G139" s="2" t="inlineStr"/>
       <c r="H139" s="2" t="n">
@@ -7942,25 +7942,78 @@
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
+          <t>https://www.solobabys.com/products/cepillo-lengua-only-baby-fz-121</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/ChatGPT-2026-06-10T193401.800.webp?v=1781138064</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>10643473727798</v>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Pañitos Happy y Soft x40 | Limpieza Suave para Bebé</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Sin categoría</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Aseo y cuidado, Baby shower</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="n">
+        <v>4700</v>
+      </c>
+      <c r="F140" s="3" t="n">
+        <v>6800</v>
+      </c>
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
           <t>https://www.solobabys.com/products/panitos-happy-y-soft-x40-limpieza-suave-para-bebe</t>
         </is>
       </c>
-      <c r="K139" s="2" t="inlineStr">
+      <c r="K140" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0967/4584/9142/files/53.webp?v=1774121918</t>
         </is>
       </c>
-      <c r="L139" s="2" t="n">
+      <c r="L140" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M139" s="2" t="inlineStr">
+      <c r="M140" s="2" t="inlineStr">
         <is>
           <t>@import url('https://fonts.googleapis.com/css2?family=Fraunces:wght@700&amp;family=Quicksand:wght@400;600;700&amp;display=swap'); .birtz-clean-container { font-family: 'Quicksand', sans-serif; max-width: 480px; margin: 0 auto; color: #4a5568; padding: 26px; background: #ffffff; } .b-rating { display: flex; align-items: center; gap: 8px; margin-bottom: 12px; font-size: 14px; font-weight: 700; color: #c8d43</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M139"/>
+  <autoFilter ref="A1:M140"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8006,7 +8059,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C3" s="5" t="n"/>
       <c r="D3" s="5" t="n"/>
@@ -8018,7 +8071,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5">
@@ -8029,7 +8082,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30 12:46</t>
+          <t>2026-10-30 18:40</t>
         </is>
       </c>
     </row>
@@ -8110,7 +8163,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -1709,7 +1709,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5">
@@ -8082,7 +8082,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30 18:40</t>
+          <t>2026-10-31 00:51</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -8082,7 +8082,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-31 00:51</t>
+          <t>2026-10-31 06:44</t>
         </is>
       </c>
     </row>

--- a/Solobabys_Catalogo.xlsx
+++ b/Solobabys_Catalogo.xlsx
@@ -8082,7 +8082,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-31 06:44</t>
+          <t>2026-10-31 12:41</t>
         </is>
       </c>
     </row>
